--- a/database/event/2713/event_2713_evp_summary.xlsx
+++ b/database/event/2713/event_2713_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.462</v>
+        <v>8.107900000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>2.2495</v>
+        <v>2.4442</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5931</v>
+        <v>2.7863</v>
       </c>
       <c r="E2" t="n">
-        <v>7.462</v>
+        <v>8.107900000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6772</v>
+        <v>3.3231</v>
       </c>
       <c r="G2" t="n">
         <v>4.7848</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6772</v>
+        <v>3.3231</v>
       </c>
       <c r="I2" t="n">
-        <v>2.17</v>
+        <v>2.6935</v>
       </c>
       <c r="J2" t="n">
         <v>4.7848</v>
@@ -529,7 +529,7 @@
         <v>147</v>
       </c>
       <c r="M2" t="n">
-        <v>6.9548</v>
+        <v>7.478299999999999</v>
       </c>
       <c r="N2" t="n">
         <v>227</v>
@@ -548,7 +548,7 @@
         <v>1.8889</v>
       </c>
       <c r="D3" t="n">
-        <v>2.11</v>
+        <v>2.0525</v>
       </c>
       <c r="E3" t="n">
         <v>6.266</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.6336</v>
+        <v>5.9272</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6983</v>
+        <v>1.7868</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8545</v>
+        <v>1.9175</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6336</v>
+        <v>5.9272</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5423</v>
+        <v>2.8358</v>
       </c>
       <c r="G4" t="n">
         <v>3.0914</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5423</v>
+        <v>2.8358</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0606</v>
+        <v>2.2985</v>
       </c>
       <c r="J4" t="n">
         <v>3.0914</v>
@@ -621,7 +621,7 @@
         <v>188</v>
       </c>
       <c r="M4" t="n">
-        <v>5.152</v>
+        <v>5.389900000000001</v>
       </c>
       <c r="N4" t="n">
         <v>288</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.2614</v>
+        <v>5.5674</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5861</v>
+        <v>1.6783</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7041</v>
+        <v>1.7741</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2614</v>
+        <v>5.5674</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8207</v>
+        <v>3.1267</v>
       </c>
       <c r="G5" t="n">
         <v>2.4407</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8207</v>
+        <v>3.1267</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2862</v>
+        <v>2.5343</v>
       </c>
       <c r="J5" t="n">
         <v>2.4407</v>
@@ -667,7 +667,7 @@
         <v>147</v>
       </c>
       <c r="M5" t="n">
-        <v>4.726900000000001</v>
+        <v>4.975</v>
       </c>
       <c r="N5" t="n">
         <v>227</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.7804</v>
+        <v>5.4878</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4411</v>
+        <v>1.6543</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5098</v>
+        <v>1.7424</v>
       </c>
       <c r="E6" t="n">
-        <v>4.7804</v>
+        <v>5.4878</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1736</v>
+        <v>2.4477</v>
       </c>
       <c r="G6" t="n">
-        <v>4.954</v>
+        <v>3.0401</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1736</v>
+        <v>2.4477</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1407</v>
+        <v>1.9839</v>
       </c>
       <c r="J6" t="n">
-        <v>4.954</v>
+        <v>3.0401</v>
       </c>
       <c r="K6" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L6" t="n">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="M6" t="n">
-        <v>4.8133</v>
+        <v>5.024</v>
       </c>
       <c r="N6" t="n">
-        <v>227</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.7602</v>
+        <v>4.8765</v>
       </c>
       <c r="C7" t="n">
-        <v>1.435</v>
+        <v>1.4701</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5017</v>
+        <v>1.4989</v>
       </c>
       <c r="E7" t="n">
-        <v>4.7602</v>
+        <v>4.8765</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7201</v>
+        <v>-0.0775</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0401</v>
+        <v>4.954</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7201</v>
+        <v>-0.0775</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3942</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>3.0401</v>
+        <v>4.954</v>
       </c>
       <c r="K7" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L7" t="n">
-        <v>188</v>
+        <v>147</v>
       </c>
       <c r="M7" t="n">
-        <v>4.4343</v>
+        <v>4.8912</v>
       </c>
       <c r="N7" t="n">
-        <v>288</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8">
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.1376</v>
+        <v>4.4878</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2473</v>
+        <v>1.3529</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2501</v>
+        <v>1.344</v>
       </c>
       <c r="E8" t="n">
-        <v>4.1376</v>
+        <v>4.4878</v>
       </c>
       <c r="F8" t="n">
-        <v>4.4273</v>
+        <v>4.7775</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2897</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2515</v>
+        <v>6.6605</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2565</v>
+        <v>5.3985</v>
       </c>
       <c r="J8" t="n">
         <v>-0.2897</v>
@@ -805,7 +805,7 @@
         <v>40</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9668</v>
+        <v>5.1088</v>
       </c>
       <c r="N8" t="n">
         <v>180</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4468</v>
+        <v>4.3116</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0391</v>
+        <v>1.2998</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9711</v>
+        <v>1.2738</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4468</v>
+        <v>4.3116</v>
       </c>
       <c r="F9" t="n">
-        <v>3.3607</v>
+        <v>4.2255</v>
       </c>
       <c r="G9" t="n">
         <v>0.0861</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3607</v>
+        <v>4.4396</v>
       </c>
       <c r="I9" t="n">
-        <v>2.7239</v>
+        <v>3.5984</v>
       </c>
       <c r="J9" t="n">
         <v>0.0861</v>
@@ -851,7 +851,7 @@
         <v>81</v>
       </c>
       <c r="M9" t="n">
-        <v>2.81</v>
+        <v>3.6845</v>
       </c>
       <c r="N9" t="n">
         <v>172</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.44</v>
+        <v>4.0724</v>
       </c>
       <c r="C10" t="n">
-        <v>1.037</v>
+        <v>1.2277</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9683</v>
+        <v>1.1785</v>
       </c>
       <c r="E10" t="n">
-        <v>3.44</v>
+        <v>4.0724</v>
       </c>
       <c r="F10" t="n">
-        <v>3.6281</v>
+        <v>4.2605</v>
       </c>
       <c r="G10" t="n">
         <v>-0.1881</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6281</v>
+        <v>4.5805</v>
       </c>
       <c r="I10" t="n">
-        <v>2.9407</v>
+        <v>3.7126</v>
       </c>
       <c r="J10" t="n">
         <v>-0.1881</v>
@@ -897,7 +897,7 @@
         <v>81</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7526</v>
+        <v>3.5245</v>
       </c>
       <c r="N10" t="n">
         <v>172</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1236</v>
+        <v>3.3717</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9416</v>
+        <v>1.0164</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8405</v>
+        <v>0.8994</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1236</v>
+        <v>3.3717</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6105</v>
+        <v>2.8586</v>
       </c>
       <c r="G11" t="n">
         <v>0.5131</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6105</v>
+        <v>2.8586</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1159</v>
+        <v>2.317</v>
       </c>
       <c r="J11" t="n">
         <v>0.5131</v>
@@ -943,7 +943,7 @@
         <v>81</v>
       </c>
       <c r="M11" t="n">
-        <v>2.629</v>
+        <v>2.8301</v>
       </c>
       <c r="N11" t="n">
         <v>172</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.3832</v>
+        <v>3.005</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7184</v>
+        <v>0.9059</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5414</v>
+        <v>0.7533</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3832</v>
+        <v>3.005</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7016</v>
+        <v>3.3234</v>
       </c>
       <c r="G12" t="n">
         <v>-0.3184</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7016</v>
+        <v>3.3234</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1897</v>
+        <v>2.6937</v>
       </c>
       <c r="J12" t="n">
         <v>-0.3184</v>
@@ -989,7 +989,7 @@
         <v>81</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8713</v>
+        <v>2.3753</v>
       </c>
       <c r="N12" t="n">
         <v>172</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1878</v>
+        <v>2.8389</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6595</v>
+        <v>0.8558</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4625</v>
+        <v>0.6871</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1878</v>
+        <v>2.8389</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0755</v>
+        <v>2.7266</v>
       </c>
       <c r="G13" t="n">
         <v>0.1123</v>
       </c>
       <c r="H13" t="n">
-        <v>2.0755</v>
+        <v>2.7266</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6822</v>
+        <v>2.21</v>
       </c>
       <c r="J13" t="n">
         <v>0.1123</v>
@@ -1035,7 +1035,7 @@
         <v>40</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7945</v>
+        <v>2.3223</v>
       </c>
       <c r="N13" t="n">
         <v>180</v>
@@ -1044,219 +1044,219 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.9089</v>
+        <v>2.3983</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5755</v>
+        <v>0.723</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3498</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9089</v>
+        <v>2.3983</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2748</v>
+        <v>2.3983</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3659</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2748</v>
+        <v>2.3983</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8437</v>
+        <v>2.3983</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3659</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="L14" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4778</v>
+        <v>2.3983</v>
       </c>
       <c r="N14" t="n">
-        <v>172</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.5949</v>
+        <v>2.0044</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4808</v>
+        <v>0.6042</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2229</v>
+        <v>0.3546</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5949</v>
+        <v>2.0044</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5949</v>
+        <v>2.3703</v>
       </c>
       <c r="G15" t="n">
-        <v>-1</v>
+        <v>-0.3659</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5949</v>
+        <v>2.3703</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1032</v>
+        <v>1.9212</v>
       </c>
       <c r="J15" t="n">
-        <v>-1</v>
+        <v>-0.3659</v>
       </c>
       <c r="K15" t="n">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="L15" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1032</v>
+        <v>1.5553</v>
       </c>
       <c r="N15" t="n">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.3668</v>
+        <v>1.8206</v>
       </c>
       <c r="C16" t="n">
-        <v>0.412</v>
+        <v>0.5488</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1308</v>
+        <v>0.2814</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3668</v>
+        <v>1.8206</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5426</v>
+        <v>2.8206</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1758</v>
+        <v>-1</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5426</v>
+        <v>2.8206</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2503</v>
+        <v>2.2862</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1758</v>
+        <v>-1</v>
       </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="L16" t="n">
-        <v>188</v>
+        <v>40</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0745</v>
+        <v>1.2862</v>
       </c>
       <c r="N16" t="n">
-        <v>288</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.0629</v>
+        <v>1.5868</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3204</v>
+        <v>0.4784</v>
       </c>
       <c r="D17" t="n">
-        <v>0.008</v>
+        <v>0.1883</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0629</v>
+        <v>1.5868</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0629</v>
+        <v>1.6103</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.0235</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0629</v>
+        <v>1.6103</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0629</v>
+        <v>1.3052</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.0235</v>
       </c>
       <c r="K17" t="n">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0629</v>
+        <v>1.2817</v>
       </c>
       <c r="N17" t="n">
-        <v>142</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0415</v>
+        <v>1.3669</v>
       </c>
       <c r="C18" t="n">
-        <v>0.314</v>
+        <v>0.4121</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.1007</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0415</v>
+        <v>1.3669</v>
       </c>
       <c r="F18" t="n">
-        <v>1.065</v>
+        <v>1.5427</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0235</v>
+        <v>-0.1758</v>
       </c>
       <c r="H18" t="n">
-        <v>1.065</v>
+        <v>1.5427</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8632</v>
+        <v>1.2504</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0235</v>
+        <v>-0.1758</v>
       </c>
       <c r="K18" t="n">
         <v>100</v>
@@ -1265,7 +1265,7 @@
         <v>188</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8397</v>
+        <v>1.0746</v>
       </c>
       <c r="N18" t="n">
         <v>288</v>
@@ -1274,139 +1274,139 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.959</v>
+        <v>1.0629</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2891</v>
+        <v>0.3204</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0339</v>
+        <v>-0.0205</v>
       </c>
       <c r="E19" t="n">
-        <v>0.959</v>
+        <v>1.0629</v>
       </c>
       <c r="F19" t="n">
-        <v>0.959</v>
+        <v>1.0629</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.959</v>
+        <v>1.0629</v>
       </c>
       <c r="I19" t="n">
-        <v>0.959</v>
+        <v>1.0629</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.959</v>
+        <v>1.0629</v>
       </c>
       <c r="N19" t="n">
-        <v>117</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>USTILO</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7108</v>
+        <v>0.9656</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2143</v>
+        <v>0.2911</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1342</v>
+        <v>-0.0592</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7108</v>
+        <v>0.9656</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7108</v>
+        <v>0.9656</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7108</v>
+        <v>0.9656</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7108</v>
+        <v>0.9656</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7108</v>
+        <v>0.9656</v>
       </c>
       <c r="N20" t="n">
-        <v>142</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5971</v>
+        <v>0.7108</v>
       </c>
       <c r="C21" t="n">
-        <v>0.18</v>
+        <v>0.2143</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1801</v>
+        <v>-0.1607</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5971</v>
+        <v>0.7108</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4072</v>
+        <v>0.7108</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8101</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4072</v>
+        <v>0.7108</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1405</v>
+        <v>0.7108</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8101</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="L21" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3304</v>
+        <v>0.7108</v>
       </c>
       <c r="N21" t="n">
-        <v>227</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2849</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0859</v>
+        <v>0.1959</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3063</v>
+        <v>-0.1851</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2849</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2604</v>
+        <v>1.6252</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9755</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2604</v>
+        <v>1.6252</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0216</v>
+        <v>1.3173</v>
       </c>
       <c r="J22" t="n">
         <v>-0.9755</v>
@@ -1449,7 +1449,7 @@
         <v>40</v>
       </c>
       <c r="M22" t="n">
-        <v>0.04610000000000003</v>
+        <v>0.3417999999999999</v>
       </c>
       <c r="N22" t="n">
         <v>180</v>
@@ -1458,47 +1458,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>aumaN</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2706</v>
+        <v>0.6077</v>
       </c>
       <c r="C23" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.1832</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.312</v>
+        <v>-0.2018</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2706</v>
+        <v>0.6077</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2706</v>
+        <v>1.4178</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.8101</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2706</v>
+        <v>1.4178</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2706</v>
+        <v>1.1492</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.8101</v>
       </c>
       <c r="K23" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2706</v>
+        <v>0.3391</v>
       </c>
       <c r="N23" t="n">
-        <v>67</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2447</v>
+        <v>0.4345</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0738</v>
+        <v>0.131</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3225</v>
+        <v>-0.2708</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2447</v>
+        <v>0.4345</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2447</v>
+        <v>0.4345</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2447</v>
+        <v>0.4345</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2447</v>
+        <v>0.4345</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2447</v>
+        <v>0.4345</v>
       </c>
       <c r="N24" t="n">
         <v>117</v>
@@ -1550,47 +1550,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>USTILO</t>
+          <t>aumaN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0503</v>
+        <v>0.385</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0152</v>
+        <v>0.1161</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.401</v>
+        <v>-0.2905</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0503</v>
+        <v>0.385</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0503</v>
+        <v>0.385</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0503</v>
+        <v>0.385</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0503</v>
+        <v>0.385</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0503</v>
+        <v>0.385</v>
       </c>
       <c r="N25" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1344</v>
+        <v>0.253</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0405</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4757</v>
+        <v>-0.3431</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1344</v>
+        <v>0.253</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6983</v>
+        <v>2.0857</v>
       </c>
       <c r="G26" t="n">
         <v>-1.8327</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6983</v>
+        <v>2.0857</v>
       </c>
       <c r="I26" t="n">
-        <v>1.3765</v>
+        <v>1.6905</v>
       </c>
       <c r="J26" t="n">
         <v>-1.8327</v>
@@ -1633,7 +1633,7 @@
         <v>188</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.4561999999999999</v>
+        <v>-0.1422000000000001</v>
       </c>
       <c r="N26" t="n">
         <v>288</v>
@@ -1652,7 +1652,7 @@
         <v>-0.045</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4817</v>
+        <v>-0.5034</v>
       </c>
       <c r="E27" t="n">
         <v>-0.1493</v>
@@ -1698,7 +1698,7 @@
         <v>-0.053</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4923</v>
+        <v>-0.5139</v>
       </c>
       <c r="E28" t="n">
         <v>-0.1757</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2501</v>
+        <v>-0.1854</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.0559</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5224</v>
+        <v>-0.5178</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2501</v>
+        <v>-0.1854</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2501</v>
+        <v>-0.1854</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2501</v>
+        <v>-0.1854</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2501</v>
+        <v>-0.1854</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2501</v>
+        <v>-0.1854</v>
       </c>
       <c r="N29" t="n">
         <v>81</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.7437</v>
+        <v>-0.7433</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2242</v>
+        <v>-0.2241</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7218</v>
+        <v>-0.74</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.7437</v>
+        <v>-0.7433</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.7437</v>
+        <v>-0.7433</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7437</v>
+        <v>-0.7433</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7437</v>
+        <v>-0.7433</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.7437</v>
+        <v>-0.7433</v>
       </c>
       <c r="N30" t="n">
         <v>142</v>
@@ -1836,7 +1836,7 @@
         <v>-0.2805</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7972</v>
+        <v>-0.8146</v>
       </c>
       <c r="E31" t="n">
         <v>-0.9304</v>
@@ -1872,78 +1872,78 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>zhokiNg</t>
+          <t>Nifty</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.0121</v>
+        <v>-0.9813</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3051</v>
+        <v>-0.2958</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8302</v>
+        <v>-0.8349</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.0121</v>
+        <v>-0.9813</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.0121</v>
+        <v>-0.9813</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.0121</v>
+        <v>-0.9813</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.0121</v>
+        <v>-0.9813</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.0121</v>
+        <v>-0.9813</v>
       </c>
       <c r="N32" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>JeXeN</t>
+          <t>zhokiNg</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.0252</v>
+        <v>-1.0121</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3091</v>
+        <v>-0.3051</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8355</v>
+        <v>-0.8471</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.0252</v>
+        <v>-1.0121</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.0252</v>
+        <v>-1.0121</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.0252</v>
+        <v>-1.0121</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.0252</v>
+        <v>-1.0121</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.0252</v>
+        <v>-1.0121</v>
       </c>
       <c r="N33" t="n">
         <v>67</v>
@@ -1964,47 +1964,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nifty</t>
+          <t>JeXeN</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.0304</v>
+        <v>-1.0252</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3106</v>
+        <v>-0.3091</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8376</v>
+        <v>-0.8524</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.0304</v>
+        <v>-1.0252</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.0304</v>
+        <v>-1.0252</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.0304</v>
+        <v>-1.0252</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.0304</v>
+        <v>-1.0252</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.0304</v>
+        <v>-1.0252</v>
       </c>
       <c r="N34" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35">
@@ -2020,7 +2020,7 @@
         <v>-0.3288</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.862</v>
+        <v>-0.8784</v>
       </c>
       <c r="E35" t="n">
         <v>-1.0907</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2504</v>
+        <v>-1.1018</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3769</v>
+        <v>-0.3321</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9265</v>
+        <v>-0.8829</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2504</v>
+        <v>-1.1018</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.2504</v>
+        <v>-0.1018</v>
       </c>
       <c r="G36" t="n">
         <v>-1</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.2504</v>
+        <v>-0.1018</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.203</v>
+        <v>-0.0825</v>
       </c>
       <c r="J36" t="n">
         <v>-1</v>
@@ -2093,7 +2093,7 @@
         <v>40</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.203</v>
+        <v>-1.0825</v>
       </c>
       <c r="N36" t="n">
         <v>180</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3894</v>
+        <v>-1.2927</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4188</v>
+        <v>-0.3897</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9826</v>
+        <v>-0.9589</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3894</v>
+        <v>-1.2927</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.3894</v>
+        <v>-1.2927</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.3894</v>
+        <v>-1.2927</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.3894</v>
+        <v>-1.2927</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.3894</v>
+        <v>-1.2927</v>
       </c>
       <c r="N37" t="n">
         <v>81</v>
@@ -2148,139 +2148,139 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>advent</t>
+          <t>tucks</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.9198</v>
+        <v>-1.6347</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5787</v>
+        <v>-0.4928</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1969</v>
+        <v>-1.0952</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.9198</v>
+        <v>-1.6347</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.9198</v>
+        <v>-1.6347</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.9198</v>
+        <v>-1.6347</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.9198</v>
+        <v>-1.6347</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.9198</v>
+        <v>-1.6347</v>
       </c>
       <c r="N38" t="n">
-        <v>67</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>advent</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.007</v>
+        <v>-1.9198</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.605</v>
+        <v>-0.5787</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2321</v>
+        <v>-1.2088</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.007</v>
+        <v>-1.9198</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.007</v>
+        <v>-1.9198</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.007</v>
+        <v>-1.9198</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.007</v>
+        <v>-1.9198</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.007</v>
+        <v>-1.9198</v>
       </c>
       <c r="N39" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>tucks</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.072</v>
+        <v>-2.007</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6246</v>
+        <v>-0.605</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2584</v>
+        <v>-1.2435</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.072</v>
+        <v>-2.007</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.072</v>
+        <v>-2.007</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.072</v>
+        <v>-2.007</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.072</v>
+        <v>-2.007</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.072</v>
+        <v>-2.007</v>
       </c>
       <c r="N40" t="n">
-        <v>117</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41">
@@ -2296,7 +2296,7 @@
         <v>-0.7133</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3772</v>
+        <v>-1.3866</v>
       </c>
       <c r="E41" t="n">
         <v>-2.3661</v>

--- a/database/event/2713/event_2713_evp_summary.xlsx
+++ b/database/event/2713/event_2713_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.107900000000001</v>
+        <v>7.1788</v>
       </c>
       <c r="C2" t="n">
-        <v>2.4442</v>
+        <v>2.1641</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7863</v>
+        <v>2.6029</v>
       </c>
       <c r="E2" t="n">
-        <v>8.107900000000001</v>
+        <v>7.1788</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3231</v>
+        <v>2.9168</v>
       </c>
       <c r="G2" t="n">
-        <v>4.7848</v>
+        <v>4.262</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3231</v>
+        <v>4.7905</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6935</v>
+        <v>2.4909</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7848</v>
+        <v>4.262</v>
       </c>
       <c r="K2" t="n">
         <v>80</v>
@@ -529,7 +529,7 @@
         <v>147</v>
       </c>
       <c r="M2" t="n">
-        <v>7.478299999999999</v>
+        <v>6.752899999999999</v>
       </c>
       <c r="N2" t="n">
         <v>227</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.266</v>
+        <v>6.2729</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8889</v>
+        <v>1.891</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0525</v>
+        <v>2.1939</v>
       </c>
       <c r="E3" t="n">
-        <v>6.266</v>
+        <v>6.2729</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6205000000000001</v>
+        <v>1.2316</v>
       </c>
       <c r="G3" t="n">
-        <v>5.6456</v>
+        <v>5.0412</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6205000000000001</v>
+        <v>1.2316</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5029</v>
+        <v>0.6404</v>
       </c>
       <c r="J3" t="n">
-        <v>5.6456</v>
+        <v>5.0412</v>
       </c>
       <c r="K3" t="n">
         <v>80</v>
@@ -575,7 +575,7 @@
         <v>147</v>
       </c>
       <c r="M3" t="n">
-        <v>6.1485</v>
+        <v>5.6816</v>
       </c>
       <c r="N3" t="n">
         <v>227</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.9272</v>
+        <v>5.7022</v>
       </c>
       <c r="C4" t="n">
-        <v>1.7868</v>
+        <v>1.719</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9175</v>
+        <v>1.9362</v>
       </c>
       <c r="E4" t="n">
-        <v>5.9272</v>
+        <v>5.7022</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8358</v>
+        <v>2.8866</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0914</v>
+        <v>2.8156</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8358</v>
+        <v>4.6843</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2985</v>
+        <v>2.4356</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0914</v>
+        <v>2.8156</v>
       </c>
       <c r="K4" t="n">
         <v>100</v>
@@ -621,7 +621,7 @@
         <v>188</v>
       </c>
       <c r="M4" t="n">
-        <v>5.389900000000001</v>
+        <v>5.2512</v>
       </c>
       <c r="N4" t="n">
         <v>288</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.5674</v>
+        <v>5.3492</v>
       </c>
       <c r="C5" t="n">
-        <v>1.6783</v>
+        <v>1.6126</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7741</v>
+        <v>1.7769</v>
       </c>
       <c r="E5" t="n">
-        <v>5.5674</v>
+        <v>5.3492</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1267</v>
+        <v>2.9456</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4407</v>
+        <v>2.4036</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1267</v>
+        <v>4.892</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5343</v>
+        <v>2.5436</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4407</v>
+        <v>2.4036</v>
       </c>
       <c r="K5" t="n">
         <v>80</v>
@@ -667,7 +667,7 @@
         <v>147</v>
       </c>
       <c r="M5" t="n">
-        <v>4.975</v>
+        <v>4.9472</v>
       </c>
       <c r="N5" t="n">
         <v>227</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.4878</v>
+        <v>5.3245</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6543</v>
+        <v>1.6051</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7424</v>
+        <v>1.7657</v>
       </c>
       <c r="E6" t="n">
-        <v>5.4878</v>
+        <v>5.3245</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4477</v>
+        <v>2.6953</v>
       </c>
       <c r="G6" t="n">
-        <v>3.0401</v>
+        <v>2.6292</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4477</v>
+        <v>4.0101</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9839</v>
+        <v>2.0851</v>
       </c>
       <c r="J6" t="n">
-        <v>3.0401</v>
+        <v>2.6292</v>
       </c>
       <c r="K6" t="n">
         <v>100</v>
@@ -713,7 +713,7 @@
         <v>188</v>
       </c>
       <c r="M6" t="n">
-        <v>5.024</v>
+        <v>4.7143</v>
       </c>
       <c r="N6" t="n">
         <v>288</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.8765</v>
+        <v>4.5893</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4701</v>
+        <v>1.3835</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4989</v>
+        <v>1.4338</v>
       </c>
       <c r="E7" t="n">
-        <v>4.8765</v>
+        <v>4.5893</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0775</v>
+        <v>0.1789</v>
       </c>
       <c r="G7" t="n">
-        <v>4.954</v>
+        <v>4.4104</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0775</v>
+        <v>0.1789</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.06279999999999999</v>
+        <v>0.093</v>
       </c>
       <c r="J7" t="n">
-        <v>4.954</v>
+        <v>4.4104</v>
       </c>
       <c r="K7" t="n">
         <v>80</v>
@@ -759,7 +759,7 @@
         <v>147</v>
       </c>
       <c r="M7" t="n">
-        <v>4.8912</v>
+        <v>4.5034</v>
       </c>
       <c r="N7" t="n">
         <v>227</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.4878</v>
+        <v>4.0462</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3529</v>
+        <v>1.2198</v>
       </c>
       <c r="D8" t="n">
-        <v>1.344</v>
+        <v>1.1886</v>
       </c>
       <c r="E8" t="n">
-        <v>4.4878</v>
+        <v>4.0462</v>
       </c>
       <c r="F8" t="n">
-        <v>4.7775</v>
+        <v>4.2641</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2897</v>
+        <v>-0.2179</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6605</v>
+        <v>9.537699999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>5.3985</v>
+        <v>4.9592</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2897</v>
+        <v>-0.2179</v>
       </c>
       <c r="K8" t="n">
         <v>140</v>
@@ -805,7 +805,7 @@
         <v>40</v>
       </c>
       <c r="M8" t="n">
-        <v>5.1088</v>
+        <v>4.7413</v>
       </c>
       <c r="N8" t="n">
         <v>180</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.3116</v>
+        <v>3.7481</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2998</v>
+        <v>1.1299</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2738</v>
+        <v>1.0541</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3116</v>
+        <v>3.7481</v>
       </c>
       <c r="F9" t="n">
-        <v>4.2255</v>
+        <v>3.4897</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0861</v>
+        <v>0.2584</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4396</v>
+        <v>6.8094</v>
       </c>
       <c r="I9" t="n">
-        <v>3.5984</v>
+        <v>3.5406</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0861</v>
+        <v>0.2584</v>
       </c>
       <c r="K9" t="n">
         <v>91</v>
@@ -851,7 +851,7 @@
         <v>81</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6845</v>
+        <v>3.799</v>
       </c>
       <c r="N9" t="n">
         <v>172</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.0724</v>
+        <v>3.5453</v>
       </c>
       <c r="C10" t="n">
-        <v>1.2277</v>
+        <v>1.0688</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1785</v>
+        <v>0.9625</v>
       </c>
       <c r="E10" t="n">
-        <v>4.0724</v>
+        <v>3.5453</v>
       </c>
       <c r="F10" t="n">
-        <v>4.2605</v>
+        <v>3.475</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1881</v>
+        <v>0.0703</v>
       </c>
       <c r="H10" t="n">
-        <v>4.5805</v>
+        <v>6.7576</v>
       </c>
       <c r="I10" t="n">
-        <v>3.7126</v>
+        <v>3.5136</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1881</v>
+        <v>0.0703</v>
       </c>
       <c r="K10" t="n">
         <v>91</v>
@@ -897,7 +897,7 @@
         <v>81</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5245</v>
+        <v>3.5839</v>
       </c>
       <c r="N10" t="n">
         <v>172</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3717</v>
+        <v>3.3271</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0164</v>
+        <v>1.003</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8994</v>
+        <v>0.864</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3717</v>
+        <v>3.3271</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8586</v>
+        <v>2.9685</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5131</v>
+        <v>0.3586</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8586</v>
+        <v>4.9729</v>
       </c>
       <c r="I11" t="n">
-        <v>2.317</v>
+        <v>2.5857</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5131</v>
+        <v>0.3586</v>
       </c>
       <c r="K11" t="n">
         <v>91</v>
@@ -943,7 +943,7 @@
         <v>81</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8301</v>
+        <v>2.9443</v>
       </c>
       <c r="N11" t="n">
         <v>172</v>
@@ -952,265 +952,265 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.005</v>
+        <v>2.9431</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9059</v>
+        <v>0.8872</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7533</v>
+        <v>0.6906</v>
       </c>
       <c r="E12" t="n">
-        <v>3.005</v>
+        <v>2.9431</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3234</v>
+        <v>2.8894</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3184</v>
+        <v>0.0537</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3234</v>
+        <v>4.6943</v>
       </c>
       <c r="I12" t="n">
-        <v>2.6937</v>
+        <v>2.4408</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3184</v>
+        <v>0.0537</v>
       </c>
       <c r="K12" t="n">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="L12" t="n">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3753</v>
+        <v>2.4945</v>
       </c>
       <c r="N12" t="n">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8389</v>
+        <v>2.8847</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8558</v>
+        <v>0.8696</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6871</v>
+        <v>0.6643</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8389</v>
+        <v>2.8847</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7266</v>
+        <v>3.0293</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1123</v>
+        <v>-0.1446</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7266</v>
+        <v>5.1872</v>
       </c>
       <c r="I13" t="n">
-        <v>2.21</v>
+        <v>2.6971</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1123</v>
+        <v>-0.1446</v>
       </c>
       <c r="K13" t="n">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="L13" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3223</v>
+        <v>2.5525</v>
       </c>
       <c r="N13" t="n">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3983</v>
+        <v>2.6401</v>
       </c>
       <c r="C14" t="n">
-        <v>0.723</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3983</v>
+        <v>2.6401</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3983</v>
+        <v>2.8182</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.1781</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3983</v>
+        <v>4.4433</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3983</v>
+        <v>2.3103</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.1781</v>
       </c>
       <c r="K14" t="n">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3983</v>
+        <v>2.1322</v>
       </c>
       <c r="N14" t="n">
-        <v>117</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.0044</v>
+        <v>2.4186</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6042</v>
+        <v>0.7291</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3546</v>
+        <v>0.4539</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0044</v>
+        <v>2.4186</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3703</v>
+        <v>2.3239</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3659</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3703</v>
+        <v>2.7016</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9212</v>
+        <v>1.4047</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3659</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="L15" t="n">
-        <v>81</v>
+        <v>188</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5553</v>
+        <v>1.4994</v>
       </c>
       <c r="N15" t="n">
-        <v>172</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8206</v>
+        <v>2.316</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5488</v>
+        <v>0.6982</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2814</v>
+        <v>0.4075</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8206</v>
+        <v>2.316</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8206</v>
+        <v>2.316</v>
       </c>
       <c r="G16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8206</v>
+        <v>2.316</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2862</v>
+        <v>2.316</v>
       </c>
       <c r="J16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="L16" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2862</v>
+        <v>2.316</v>
       </c>
       <c r="N16" t="n">
-        <v>180</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5868</v>
+        <v>2.1445</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4784</v>
+        <v>0.6465</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1883</v>
+        <v>0.3301</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5868</v>
+        <v>2.1445</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6103</v>
+        <v>2.3985</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0235</v>
+        <v>-0.254</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6103</v>
+        <v>2.9647</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3052</v>
+        <v>1.5415</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0235</v>
+        <v>-0.254</v>
       </c>
       <c r="K17" t="n">
         <v>100</v>
@@ -1219,7 +1219,7 @@
         <v>188</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2817</v>
+        <v>1.2875</v>
       </c>
       <c r="N17" t="n">
         <v>288</v>
@@ -1228,277 +1228,277 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3669</v>
+        <v>2.0326</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4121</v>
+        <v>0.6127</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1007</v>
+        <v>0.2796</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3669</v>
+        <v>2.0326</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5427</v>
+        <v>3.0326</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1758</v>
+        <v>-1</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5427</v>
+        <v>5.1987</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2504</v>
+        <v>2.7031</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1758</v>
+        <v>-1</v>
       </c>
       <c r="K18" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="L18" t="n">
-        <v>188</v>
+        <v>40</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0746</v>
+        <v>1.7031</v>
       </c>
       <c r="N18" t="n">
-        <v>288</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0629</v>
+        <v>1.8258</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3204</v>
+        <v>0.5504</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0205</v>
+        <v>0.1862</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0629</v>
+        <v>1.8258</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0629</v>
+        <v>2.5401</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.7143</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0629</v>
+        <v>3.4634</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0629</v>
+        <v>1.8008</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.7143</v>
       </c>
       <c r="K19" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0629</v>
+        <v>1.0865</v>
       </c>
       <c r="N19" t="n">
-        <v>142</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>USTILO</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9656</v>
+        <v>1.7155</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2911</v>
+        <v>0.5171</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0592</v>
+        <v>0.1364</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9656</v>
+        <v>1.7155</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9656</v>
+        <v>2.274</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.5585</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9656</v>
+        <v>2.526</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9656</v>
+        <v>1.3134</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.5585</v>
       </c>
       <c r="K20" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9656</v>
+        <v>0.7548999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>81</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7108</v>
+        <v>1.1817</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2143</v>
+        <v>0.3562</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1607</v>
+        <v>-0.1045</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7108</v>
+        <v>1.1817</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7108</v>
+        <v>2.587</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-1.4053</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7108</v>
+        <v>3.6288</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7108</v>
+        <v>1.8868</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-1.4053</v>
       </c>
       <c r="K21" t="n">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7108</v>
+        <v>0.4815</v>
       </c>
       <c r="N21" t="n">
-        <v>142</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6497000000000001</v>
+        <v>1.0454</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1959</v>
+        <v>0.3151</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1851</v>
+        <v>-0.1661</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6497000000000001</v>
+        <v>1.0454</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6252</v>
+        <v>1.0454</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9755</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.6252</v>
+        <v>1.0454</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3173</v>
+        <v>1.0454</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9755</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="L22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3417999999999999</v>
+        <v>1.0454</v>
       </c>
       <c r="N22" t="n">
-        <v>180</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>USTILO</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6077</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1832</v>
+        <v>0.2828</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2018</v>
+        <v>-0.2146</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6077</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4178</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8101</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.4178</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1492</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8101</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L23" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3391</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>227</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4345</v>
+        <v>0.8193</v>
       </c>
       <c r="C24" t="n">
-        <v>0.131</v>
+        <v>0.247</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2708</v>
+        <v>-0.2681</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4345</v>
+        <v>0.8193</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4345</v>
+        <v>0.8193</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4345</v>
+        <v>0.8193</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4345</v>
+        <v>0.8193</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4345</v>
+        <v>0.8193</v>
       </c>
       <c r="N24" t="n">
         <v>117</v>
@@ -1550,170 +1550,170 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>aumaN</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.385</v>
+        <v>0.8048</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1161</v>
+        <v>0.2426</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2905</v>
+        <v>-0.2747</v>
       </c>
       <c r="E25" t="n">
-        <v>0.385</v>
+        <v>0.8048</v>
       </c>
       <c r="F25" t="n">
-        <v>0.385</v>
+        <v>0.8048</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.385</v>
+        <v>0.8048</v>
       </c>
       <c r="I25" t="n">
-        <v>0.385</v>
+        <v>0.8048</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>67</v>
+        <v>142</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.385</v>
+        <v>0.8048</v>
       </c>
       <c r="N25" t="n">
-        <v>67</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>aumaN</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.253</v>
+        <v>0.7297</v>
       </c>
       <c r="C26" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3431</v>
+        <v>-0.3086</v>
       </c>
       <c r="E26" t="n">
-        <v>0.253</v>
+        <v>0.7297</v>
       </c>
       <c r="F26" t="n">
-        <v>2.0857</v>
+        <v>0.7297</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.8327</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.0857</v>
+        <v>0.7297</v>
       </c>
       <c r="I26" t="n">
-        <v>1.6905</v>
+        <v>0.7297</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.8327</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="L26" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1422000000000001</v>
+        <v>0.7297</v>
       </c>
       <c r="N26" t="n">
-        <v>288</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1493</v>
+        <v>0.1168</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.045</v>
+        <v>0.0352</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5034</v>
+        <v>-0.5853</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1493</v>
+        <v>0.1168</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1493</v>
+        <v>0.1168</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1493</v>
+        <v>0.1168</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1493</v>
+        <v>0.1168</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1493</v>
+        <v>0.1168</v>
       </c>
       <c r="N27" t="n">
-        <v>142</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1757</v>
+        <v>0.098</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.053</v>
+        <v>0.0295</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5139</v>
+        <v>-0.5938</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1757</v>
+        <v>0.098</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1757</v>
+        <v>0.098</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1757</v>
+        <v>0.098</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1757</v>
+        <v>0.098</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1757</v>
+        <v>0.098</v>
       </c>
       <c r="N28" t="n">
         <v>142</v>
@@ -1734,47 +1734,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1854</v>
+        <v>-0.066</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0559</v>
+        <v>-0.0199</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5178</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1854</v>
+        <v>-0.066</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1854</v>
+        <v>-0.066</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1854</v>
+        <v>-0.066</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1854</v>
+        <v>-0.066</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1854</v>
+        <v>-0.066</v>
       </c>
       <c r="N29" t="n">
-        <v>81</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.7433</v>
+        <v>-0.1663</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2241</v>
+        <v>-0.0501</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.74</v>
+        <v>-0.7131</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.7433</v>
+        <v>-0.1663</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.7433</v>
+        <v>-0.1663</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7433</v>
+        <v>-0.1663</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7433</v>
+        <v>-0.1663</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.7433</v>
+        <v>-0.1663</v>
       </c>
       <c r="N30" t="n">
         <v>142</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.9304</v>
+        <v>-0.3343</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2805</v>
+        <v>-0.1008</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8146</v>
+        <v>-0.7889</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.9304</v>
+        <v>-0.3343</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.9304</v>
+        <v>-0.3343</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.9304</v>
+        <v>-0.3343</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.9304</v>
+        <v>-0.3343</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.9304</v>
+        <v>-0.3343</v>
       </c>
       <c r="N31" t="n">
         <v>117</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.9813</v>
+        <v>-0.3568</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2958</v>
+        <v>-0.1076</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8349</v>
+        <v>-0.7991</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.9813</v>
+        <v>-0.3568</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.9813</v>
+        <v>-0.3568</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.9813</v>
+        <v>-0.3568</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.9813</v>
+        <v>-0.3568</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.9813</v>
+        <v>-0.3568</v>
       </c>
       <c r="N32" t="n">
         <v>81</v>
@@ -1918,124 +1918,124 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>zhokiNg</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.0121</v>
+        <v>-0.5755</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3051</v>
+        <v>-0.1735</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8471</v>
+        <v>-0.8978</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.0121</v>
+        <v>-0.5755</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.0121</v>
+        <v>-0.5755</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.0121</v>
+        <v>-0.5755</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.0121</v>
+        <v>-0.5755</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.0121</v>
+        <v>-0.5755</v>
       </c>
       <c r="N33" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JeXeN</t>
+          <t>hazed</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.0252</v>
+        <v>-0.5827</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3091</v>
+        <v>-0.1757</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8524</v>
+        <v>-0.9011</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.0252</v>
+        <v>-0.5827</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.0252</v>
+        <v>0.4173</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.0252</v>
+        <v>0.4173</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.0252</v>
+        <v>0.217</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K34" t="n">
-        <v>67</v>
+        <v>140</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.0252</v>
+        <v>-0.783</v>
       </c>
       <c r="N34" t="n">
-        <v>67</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>zhokiNg</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0907</v>
+        <v>-0.6182</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3288</v>
+        <v>-0.1864</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8784</v>
+        <v>-0.9171</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.0907</v>
+        <v>-0.6182</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.0907</v>
+        <v>-0.6182</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.0907</v>
+        <v>-0.6182</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.0907</v>
+        <v>-0.6182</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.0907</v>
+        <v>-0.6182</v>
       </c>
       <c r="N35" t="n">
         <v>67</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>hazed</t>
+          <t>JeXeN</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1018</v>
+        <v>-0.7215</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3321</v>
+        <v>-0.2175</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8829</v>
+        <v>-0.9637</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1018</v>
+        <v>-0.7215</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.1018</v>
+        <v>-0.7215</v>
       </c>
       <c r="G36" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.1018</v>
+        <v>-0.7215</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0825</v>
+        <v>-0.7215</v>
       </c>
       <c r="J36" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>140</v>
+        <v>67</v>
       </c>
       <c r="L36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.0825</v>
+        <v>-0.7215</v>
       </c>
       <c r="N36" t="n">
-        <v>180</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2927</v>
+        <v>-0.7595</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3897</v>
+        <v>-0.229</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9589</v>
+        <v>-0.9809</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2927</v>
+        <v>-0.7595</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2927</v>
+        <v>-0.7595</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2927</v>
+        <v>-0.7595</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.2927</v>
+        <v>-0.7595</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2927</v>
+        <v>-0.7595</v>
       </c>
       <c r="N37" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.6347</v>
+        <v>-1.2414</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4928</v>
+        <v>-0.3742</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0952</v>
+        <v>-1.1984</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.6347</v>
+        <v>-1.2414</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.6347</v>
+        <v>-1.2414</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.6347</v>
+        <v>-1.2414</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.6347</v>
+        <v>-1.2414</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.6347</v>
+        <v>-1.2414</v>
       </c>
       <c r="N38" t="n">
         <v>117</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.9198</v>
+        <v>-1.2871</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5787</v>
+        <v>-0.388</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2088</v>
+        <v>-1.2191</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.9198</v>
+        <v>-1.2871</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.9198</v>
+        <v>-1.2871</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.9198</v>
+        <v>-1.2871</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.9198</v>
+        <v>-1.2871</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.9198</v>
+        <v>-1.2871</v>
       </c>
       <c r="N39" t="n">
         <v>67</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.007</v>
+        <v>-1.5182</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.605</v>
+        <v>-0.4577</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2435</v>
+        <v>-1.3234</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.007</v>
+        <v>-1.5182</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.007</v>
+        <v>-1.5182</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.007</v>
+        <v>-1.5182</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.007</v>
+        <v>-1.5182</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.007</v>
+        <v>-1.5182</v>
       </c>
       <c r="N40" t="n">
         <v>81</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.3661</v>
+        <v>-1.9271</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.7133</v>
+        <v>-0.5809</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3866</v>
+        <v>-1.508</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.3661</v>
+        <v>-1.9271</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.3661</v>
+        <v>-1.9271</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.3661</v>
+        <v>-1.9271</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.3661</v>
+        <v>-1.9271</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.3661</v>
+        <v>-1.9271</v>
       </c>
       <c r="N41" t="n">
         <v>117</v>
@@ -2429,10 +2429,10 @@
         <v>1.47</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1526</v>
+        <v>1.0987</v>
       </c>
       <c r="J2" t="n">
-        <v>32.2728</v>
+        <v>30.7636</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.24</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6301</v>
+        <v>0.6505</v>
       </c>
       <c r="J3" t="n">
-        <v>17.6428</v>
+        <v>18.214</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.14</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3398</v>
+        <v>0.4072</v>
       </c>
       <c r="J4" t="n">
-        <v>9.5144</v>
+        <v>11.4016</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.14</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3398</v>
+        <v>0.4072</v>
       </c>
       <c r="J5" t="n">
-        <v>9.5144</v>
+        <v>11.4016</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2276</v>
+        <v>0.2983</v>
       </c>
       <c r="J6" t="n">
-        <v>6.3728</v>
+        <v>8.352399999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.15</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3464</v>
+        <v>0.3804</v>
       </c>
       <c r="J7" t="n">
-        <v>9.699199999999999</v>
+        <v>10.6512</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.9</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1756</v>
+        <v>-0.1242</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.9168</v>
+        <v>-3.4776</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.87</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2395</v>
+        <v>-0.1555</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.706</v>
+        <v>-4.354</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3396</v>
+        <v>-0.2166</v>
       </c>
       <c r="J10" t="n">
-        <v>-9.508800000000001</v>
+        <v>-6.0648</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.76</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4147</v>
+        <v>-0.2661</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.6116</v>
+        <v>-7.4508</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.71</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5841</v>
+        <v>1.3816</v>
       </c>
       <c r="J12" t="n">
-        <v>36.4343</v>
+        <v>31.7768</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.44</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0595</v>
+        <v>1.0474</v>
       </c>
       <c r="J13" t="n">
-        <v>24.3685</v>
+        <v>24.0902</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.31</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7652</v>
+        <v>0.7976</v>
       </c>
       <c r="J14" t="n">
-        <v>17.5996</v>
+        <v>18.3448</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.98</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2492</v>
+        <v>-0.1642</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.7316</v>
+        <v>-3.7766</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.96</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3201</v>
+        <v>-0.2365</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.3623</v>
+        <v>-5.4395</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.46</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7508</v>
+        <v>0.9371</v>
       </c>
       <c r="J17" t="n">
-        <v>17.2684</v>
+        <v>21.5533</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.097</v>
+        <v>-0.0799</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.231</v>
+        <v>-1.8377</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.92</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1381</v>
+        <v>-0.1032</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.1763</v>
+        <v>-2.3736</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.7</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5007</v>
+        <v>-0.3249</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.5161</v>
+        <v>-7.4727</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.51</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7401</v>
+        <v>-0.501</v>
       </c>
       <c r="J21" t="n">
-        <v>-17.0223</v>
+        <v>-11.523</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.27</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4972</v>
+        <v>0.4465</v>
       </c>
       <c r="J22" t="n">
-        <v>14.4188</v>
+        <v>12.9485</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.18</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3715</v>
+        <v>0.3196</v>
       </c>
       <c r="J23" t="n">
-        <v>10.7735</v>
+        <v>9.2684</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.87</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2623</v>
+        <v>-0.1614</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.6067</v>
+        <v>-4.6806</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.75</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4431</v>
+        <v>-0.2826</v>
       </c>
       <c r="J25" t="n">
-        <v>-12.8499</v>
+        <v>-8.195399999999999</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5241</v>
+        <v>-0.3401</v>
       </c>
       <c r="J26" t="n">
-        <v>-15.1989</v>
+        <v>-9.8629</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.59</v>
       </c>
       <c r="I27" t="n">
-        <v>0.834</v>
+        <v>0.7491</v>
       </c>
       <c r="J27" t="n">
-        <v>24.186</v>
+        <v>21.7239</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.26</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4352</v>
+        <v>0.3684</v>
       </c>
       <c r="J28" t="n">
-        <v>12.6208</v>
+        <v>10.6836</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.01</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0101</v>
+        <v>0.0165</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.2929</v>
+        <v>0.4785</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.99</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.079</v>
+        <v>-0.0295</v>
       </c>
       <c r="J30" t="n">
-        <v>-2.291</v>
+        <v>-0.8555</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.63</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6223</v>
+        <v>-0.4112</v>
       </c>
       <c r="J31" t="n">
-        <v>-18.0467</v>
+        <v>-11.9248</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.6</v>
       </c>
       <c r="I32" t="n">
-        <v>1.3821</v>
+        <v>1.2491</v>
       </c>
       <c r="J32" t="n">
-        <v>37.3167</v>
+        <v>33.7257</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.6</v>
       </c>
       <c r="I33" t="n">
-        <v>1.3821</v>
+        <v>1.2491</v>
       </c>
       <c r="J33" t="n">
-        <v>37.3167</v>
+        <v>33.7257</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.25</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5985</v>
+        <v>0.6655</v>
       </c>
       <c r="J34" t="n">
-        <v>16.1595</v>
+        <v>17.9685</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.17</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3919</v>
+        <v>0.4723</v>
       </c>
       <c r="J35" t="n">
-        <v>10.5813</v>
+        <v>12.7521</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.75</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8604000000000001</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>-23.2308</v>
+        <v>-22.086</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.29</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5562</v>
+        <v>0.6634</v>
       </c>
       <c r="J37" t="n">
-        <v>15.0174</v>
+        <v>17.9118</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.99</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0333</v>
+        <v>-0.0041</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8991</v>
+        <v>-0.1107</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.75</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4187</v>
+        <v>-0.2713</v>
       </c>
       <c r="J39" t="n">
-        <v>-11.3049</v>
+        <v>-7.3251</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.7</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4899</v>
+        <v>-0.3194</v>
       </c>
       <c r="J40" t="n">
-        <v>-13.2273</v>
+        <v>-8.623799999999999</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.59</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6351</v>
+        <v>-0.4227</v>
       </c>
       <c r="J41" t="n">
-        <v>-17.1477</v>
+        <v>-11.4129</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.61</v>
       </c>
       <c r="I42" t="n">
-        <v>1.3965</v>
+        <v>0.9855</v>
       </c>
       <c r="J42" t="n">
-        <v>40.4985</v>
+        <v>28.5795</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.44</v>
       </c>
       <c r="I43" t="n">
-        <v>1.0575</v>
+        <v>0.7738</v>
       </c>
       <c r="J43" t="n">
-        <v>30.6675</v>
+        <v>22.4402</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.37</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9049</v>
+        <v>0.6843</v>
       </c>
       <c r="J44" t="n">
-        <v>26.2421</v>
+        <v>19.8447</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.22</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5147</v>
+        <v>0.4868</v>
       </c>
       <c r="J45" t="n">
-        <v>14.9263</v>
+        <v>14.1172</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.78</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7948</v>
+        <v>-0.745</v>
       </c>
       <c r="J46" t="n">
-        <v>-23.0492</v>
+        <v>-21.605</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.34</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6032</v>
+        <v>0.5662</v>
       </c>
       <c r="J47" t="n">
-        <v>17.4928</v>
+        <v>16.4198</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.93</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1199</v>
+        <v>-0.0921</v>
       </c>
       <c r="J48" t="n">
-        <v>-3.4771</v>
+        <v>-2.6709</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.9</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1888</v>
+        <v>-0.125</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.4752</v>
+        <v>-3.625</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.74</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4466</v>
+        <v>-0.287</v>
       </c>
       <c r="J50" t="n">
-        <v>-12.9514</v>
+        <v>-8.323</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.64</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5806</v>
+        <v>-0.382</v>
       </c>
       <c r="J51" t="n">
-        <v>-16.8374</v>
+        <v>-11.078</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.33</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.466</v>
       </c>
       <c r="J52" t="n">
-        <v>16.2891</v>
+        <v>12.582</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.84</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2815</v>
+        <v>-0.1839</v>
       </c>
       <c r="J53" t="n">
-        <v>-7.6005</v>
+        <v>-4.9653</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.8</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3471</v>
+        <v>-0.2239</v>
       </c>
       <c r="J54" t="n">
-        <v>-9.371700000000001</v>
+        <v>-6.0453</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.8</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3471</v>
+        <v>-0.2239</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.371700000000001</v>
+        <v>-6.0453</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.61</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6121</v>
+        <v>-0.4057</v>
       </c>
       <c r="J56" t="n">
-        <v>-16.5267</v>
+        <v>-10.9539</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.68</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8994</v>
+        <v>0.6179</v>
       </c>
       <c r="J57" t="n">
-        <v>24.2838</v>
+        <v>16.6833</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.23</v>
       </c>
       <c r="I58" t="n">
-        <v>0.353</v>
+        <v>0.3159</v>
       </c>
       <c r="J58" t="n">
-        <v>9.531000000000001</v>
+        <v>8.529299999999999</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.17</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2479</v>
+        <v>0.2449</v>
       </c>
       <c r="J59" t="n">
-        <v>6.6933</v>
+        <v>6.6123</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.12</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1675</v>
+        <v>0.1795</v>
       </c>
       <c r="J60" t="n">
-        <v>4.5225</v>
+        <v>4.8465</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.82</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3925</v>
+        <v>-0.2401</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.5975</v>
+        <v>-6.4827</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.41</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0379</v>
+        <v>0.7516</v>
       </c>
       <c r="J62" t="n">
-        <v>25.9475</v>
+        <v>18.79</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.36</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9297</v>
+        <v>0.6856</v>
       </c>
       <c r="J63" t="n">
-        <v>23.2425</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.2</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5314</v>
+        <v>0.4674</v>
       </c>
       <c r="J64" t="n">
-        <v>13.285</v>
+        <v>11.685</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.11</v>
       </c>
       <c r="I65" t="n">
-        <v>0.2661</v>
+        <v>0.3281</v>
       </c>
       <c r="J65" t="n">
-        <v>6.6525</v>
+        <v>8.202500000000001</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.91</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4477</v>
+        <v>-0.3737</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.1925</v>
+        <v>-9.342499999999999</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.11</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2848</v>
+        <v>0.3005</v>
       </c>
       <c r="J67" t="n">
-        <v>7.12</v>
+        <v>7.5125</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.0785</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.27</v>
+        <v>-1.9625</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.89</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1975</v>
+        <v>-0.1343</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.9375</v>
+        <v>-3.3575</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.77</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3988</v>
+        <v>-0.2558</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.970000000000001</v>
+        <v>-6.395</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.76</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4135</v>
+        <v>-0.2655</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.3375</v>
+        <v>-6.6375</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>2.07</v>
       </c>
       <c r="I72" t="n">
-        <v>1.907</v>
+        <v>1.4387</v>
       </c>
       <c r="J72" t="n">
-        <v>32.419</v>
+        <v>24.4579</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.79</v>
       </c>
       <c r="I73" t="n">
-        <v>1.58</v>
+        <v>1.1341</v>
       </c>
       <c r="J73" t="n">
-        <v>26.86</v>
+        <v>19.2797</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.68</v>
       </c>
       <c r="I74" t="n">
-        <v>1.3708</v>
+        <v>1.0126</v>
       </c>
       <c r="J74" t="n">
-        <v>23.3036</v>
+        <v>17.2142</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.53</v>
       </c>
       <c r="I75" t="n">
-        <v>1.0441</v>
+        <v>0.8442</v>
       </c>
       <c r="J75" t="n">
-        <v>17.7497</v>
+        <v>14.3514</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.09</v>
       </c>
       <c r="I76" t="n">
-        <v>0.0847</v>
+        <v>0.1827</v>
       </c>
       <c r="J76" t="n">
-        <v>1.4399</v>
+        <v>3.1059</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.89</v>
       </c>
       <c r="I77" t="n">
-        <v>0.045</v>
+        <v>0.0299</v>
       </c>
       <c r="J77" t="n">
-        <v>0.765</v>
+        <v>0.5083</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.59</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.4262</v>
+        <v>-0.3494</v>
       </c>
       <c r="J78" t="n">
-        <v>-7.2454</v>
+        <v>-5.9398</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.473</v>
+        <v>-0.3809</v>
       </c>
       <c r="J79" t="n">
-        <v>-8.041</v>
+        <v>-6.4753</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.16</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.0918</v>
+        <v>-0.7769</v>
       </c>
       <c r="J80" t="n">
-        <v>-18.5606</v>
+        <v>-13.2073</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.15</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.1044</v>
+        <v>-0.7874</v>
       </c>
       <c r="J81" t="n">
-        <v>-18.7748</v>
+        <v>-13.3858</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.77</v>
       </c>
       <c r="I82" t="n">
-        <v>1.675</v>
+        <v>1.1719</v>
       </c>
       <c r="J82" t="n">
-        <v>38.525</v>
+        <v>26.9537</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.53</v>
       </c>
       <c r="I83" t="n">
-        <v>1.229</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>28.267</v>
+        <v>20.2768</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.21</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4764</v>
+        <v>0.4694</v>
       </c>
       <c r="J84" t="n">
-        <v>10.9572</v>
+        <v>10.7962</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.07</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1052</v>
+        <v>0.1887</v>
       </c>
       <c r="J85" t="n">
-        <v>2.4196</v>
+        <v>4.3401</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.97</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2942</v>
+        <v>-0.2084</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.7666</v>
+        <v>-4.7932</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.03</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1833</v>
+        <v>0.163</v>
       </c>
       <c r="J87" t="n">
-        <v>4.2159</v>
+        <v>3.749</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.99</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0673</v>
+        <v>0.0238</v>
       </c>
       <c r="J88" t="n">
-        <v>1.5479</v>
+        <v>0.5474</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.64</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.5493</v>
+        <v>-0.3649</v>
       </c>
       <c r="J89" t="n">
-        <v>-12.6339</v>
+        <v>-8.3927</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.64</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5493</v>
+        <v>-0.3649</v>
       </c>
       <c r="J90" t="n">
-        <v>-12.6339</v>
+        <v>-8.3927</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.62</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5766</v>
+        <v>-0.3837</v>
       </c>
       <c r="J91" t="n">
-        <v>-13.2618</v>
+        <v>-8.825100000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.84</v>
       </c>
       <c r="I92" t="n">
-        <v>1.7813</v>
+        <v>1.516</v>
       </c>
       <c r="J92" t="n">
-        <v>46.3138</v>
+        <v>39.416</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.59</v>
       </c>
       <c r="I93" t="n">
-        <v>1.3253</v>
+        <v>1.2199</v>
       </c>
       <c r="J93" t="n">
-        <v>34.4578</v>
+        <v>31.7174</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.3</v>
       </c>
       <c r="I94" t="n">
-        <v>0.6718</v>
+        <v>0.7644</v>
       </c>
       <c r="J94" t="n">
-        <v>17.4668</v>
+        <v>19.8744</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.17</v>
       </c>
       <c r="I95" t="n">
-        <v>0.3585</v>
+        <v>0.4542</v>
       </c>
       <c r="J95" t="n">
-        <v>9.321</v>
+        <v>11.8092</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.88</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5681</v>
+        <v>-0.4959</v>
       </c>
       <c r="J96" t="n">
-        <v>-14.7706</v>
+        <v>-12.8934</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.02</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1832</v>
+        <v>0.1621</v>
       </c>
       <c r="J97" t="n">
-        <v>4.7632</v>
+        <v>4.2146</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.9</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.0905</v>
+        <v>-0.097</v>
       </c>
       <c r="J98" t="n">
-        <v>-2.353</v>
+        <v>-2.522</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.84</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1916</v>
+        <v>-0.1649</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.9816</v>
+        <v>-4.2874</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.5</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.7206</v>
+        <v>-0.4881</v>
       </c>
       <c r="J100" t="n">
-        <v>-18.7356</v>
+        <v>-12.6906</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.41</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8318</v>
+        <v>-0.5716</v>
       </c>
       <c r="J101" t="n">
-        <v>-21.6268</v>
+        <v>-14.8616</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>0.58</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.4284</v>
+        <v>-0.3524</v>
       </c>
       <c r="J102" t="n">
-        <v>-8.1396</v>
+        <v>-6.6956</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.53</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.507</v>
+        <v>-0.4053</v>
       </c>
       <c r="J103" t="n">
-        <v>-9.632999999999999</v>
+        <v>-7.7007</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.44</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.6811</v>
+        <v>-0.4902</v>
       </c>
       <c r="J104" t="n">
-        <v>-12.9409</v>
+        <v>-9.313800000000001</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.44</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.6811</v>
+        <v>-0.4902</v>
       </c>
       <c r="J105" t="n">
-        <v>-12.9409</v>
+        <v>-9.313800000000001</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.27</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.9437</v>
+        <v>-0.6586</v>
       </c>
       <c r="J106" t="n">
-        <v>-17.9303</v>
+        <v>-12.5134</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.96</v>
       </c>
       <c r="I107" t="n">
-        <v>1.8757</v>
+        <v>1.5951</v>
       </c>
       <c r="J107" t="n">
-        <v>35.6383</v>
+        <v>30.3069</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.81</v>
       </c>
       <c r="I108" t="n">
-        <v>1.6194</v>
+        <v>1.4309</v>
       </c>
       <c r="J108" t="n">
-        <v>30.7686</v>
+        <v>27.1871</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.59</v>
       </c>
       <c r="I109" t="n">
-        <v>1.1711</v>
+        <v>1.1878</v>
       </c>
       <c r="J109" t="n">
-        <v>22.2509</v>
+        <v>22.5682</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.41</v>
       </c>
       <c r="I110" t="n">
-        <v>0.805</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="J110" t="n">
-        <v>15.295</v>
+        <v>18.0709</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.35</v>
       </c>
       <c r="I111" t="n">
-        <v>0.6817</v>
+        <v>0.8242</v>
       </c>
       <c r="J111" t="n">
-        <v>12.9523</v>
+        <v>15.6598</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.49</v>
       </c>
       <c r="I112" t="n">
-        <v>1.1346</v>
+        <v>1.101</v>
       </c>
       <c r="J112" t="n">
-        <v>24.9612</v>
+        <v>24.222</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.41</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9638</v>
+        <v>0.9918</v>
       </c>
       <c r="J113" t="n">
-        <v>21.2036</v>
+        <v>21.8196</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.35</v>
       </c>
       <c r="I114" t="n">
-        <v>0.8212</v>
+        <v>0.8749</v>
       </c>
       <c r="J114" t="n">
-        <v>18.0664</v>
+        <v>19.2478</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.23</v>
       </c>
       <c r="I115" t="n">
-        <v>0.5127</v>
+        <v>0.6062</v>
       </c>
       <c r="J115" t="n">
-        <v>11.2794</v>
+        <v>13.3364</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.21</v>
       </c>
       <c r="I116" t="n">
-        <v>0.4641</v>
+        <v>0.5579</v>
       </c>
       <c r="J116" t="n">
-        <v>10.2102</v>
+        <v>12.2738</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.07</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2766</v>
+        <v>0.2834</v>
       </c>
       <c r="J117" t="n">
-        <v>6.0852</v>
+        <v>6.2348</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.97</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0357</v>
+        <v>-0.0095</v>
       </c>
       <c r="J118" t="n">
-        <v>0.7854</v>
+        <v>-0.209</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.71</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.4318</v>
+        <v>-0.2938</v>
       </c>
       <c r="J119" t="n">
-        <v>-9.499599999999999</v>
+        <v>-6.4636</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.55</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.6597</v>
+        <v>-0.4436</v>
       </c>
       <c r="J120" t="n">
-        <v>-14.5134</v>
+        <v>-9.7592</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.44</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7981</v>
+        <v>-0.5457</v>
       </c>
       <c r="J121" t="n">
-        <v>-17.5582</v>
+        <v>-12.0054</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.41</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.7837</v>
       </c>
       <c r="J122" t="n">
-        <v>18.6064</v>
+        <v>22.7273</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.18</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3367</v>
+        <v>0.3876</v>
       </c>
       <c r="J123" t="n">
-        <v>9.7643</v>
+        <v>11.2404</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.07</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1512</v>
+        <v>0.1742</v>
       </c>
       <c r="J124" t="n">
-        <v>4.3848</v>
+        <v>5.0518</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.04</v>
       </c>
       <c r="I125" t="n">
-        <v>0.0801</v>
+        <v>0.1092</v>
       </c>
       <c r="J125" t="n">
-        <v>2.3229</v>
+        <v>3.1668</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.55</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7116</v>
+        <v>-0.4793</v>
       </c>
       <c r="J126" t="n">
-        <v>-20.6364</v>
+        <v>-13.8997</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.55</v>
       </c>
       <c r="I127" t="n">
-        <v>1.35</v>
+        <v>1.2216</v>
       </c>
       <c r="J127" t="n">
-        <v>39.15</v>
+        <v>35.4264</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.36</v>
       </c>
       <c r="I128" t="n">
-        <v>0.9595</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="J128" t="n">
-        <v>27.8255</v>
+        <v>27.4949</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.2</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5793</v>
+        <v>0.5713</v>
       </c>
       <c r="J129" t="n">
-        <v>16.7997</v>
+        <v>16.5677</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.03</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0404</v>
+        <v>0.099</v>
       </c>
       <c r="J130" t="n">
-        <v>1.1716</v>
+        <v>2.871</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.57</v>
       </c>
       <c r="I131" t="n">
-        <v>-1.2148</v>
+        <v>-1.2193</v>
       </c>
       <c r="J131" t="n">
-        <v>-35.2292</v>
+        <v>-35.3597</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.45</v>
       </c>
       <c r="I132" t="n">
-        <v>1.185</v>
+        <v>1.1106</v>
       </c>
       <c r="J132" t="n">
-        <v>33.18</v>
+        <v>31.0968</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.12</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4022</v>
+        <v>0.3819</v>
       </c>
       <c r="J133" t="n">
-        <v>11.2616</v>
+        <v>10.6932</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.06</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1893</v>
+        <v>0.2129</v>
       </c>
       <c r="J134" t="n">
-        <v>5.3004</v>
+        <v>5.9612</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1893</v>
+        <v>0.2129</v>
       </c>
       <c r="J135" t="n">
-        <v>5.3004</v>
+        <v>5.9612</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.9492</v>
+        <v>-0.9192</v>
       </c>
       <c r="J136" t="n">
-        <v>-26.5776</v>
+        <v>-25.7376</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.14</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3073</v>
+        <v>0.3372</v>
       </c>
       <c r="J137" t="n">
-        <v>8.6044</v>
+        <v>9.441599999999999</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1</v>
       </c>
       <c r="I138" t="n">
-        <v>0.0252</v>
+        <v>0.0057</v>
       </c>
       <c r="J138" t="n">
-        <v>0.7056</v>
+        <v>0.1596</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.99</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0109</v>
+        <v>-0.0178</v>
       </c>
       <c r="J139" t="n">
-        <v>-0.3052</v>
+        <v>-0.4984</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1383</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J140" t="n">
-        <v>-3.8724</v>
+        <v>-2.366</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.74</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4592</v>
+        <v>-0.2935</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.8576</v>
+        <v>-8.218</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.09</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2192</v>
+        <v>0.2314</v>
       </c>
       <c r="J142" t="n">
-        <v>7.672</v>
+        <v>8.099</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0793</v>
+        <v>0.0699</v>
       </c>
       <c r="J143" t="n">
-        <v>2.7755</v>
+        <v>2.4465</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1</v>
       </c>
       <c r="I144" t="n">
-        <v>0.0168</v>
+        <v>0.0029</v>
       </c>
       <c r="J144" t="n">
-        <v>0.588</v>
+        <v>0.1015</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.99</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0202</v>
+        <v>-0.0192</v>
       </c>
       <c r="J145" t="n">
-        <v>-0.707</v>
+        <v>-0.672</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.79</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3928</v>
+        <v>-0.2464</v>
       </c>
       <c r="J146" t="n">
-        <v>-13.748</v>
+        <v>-8.624000000000001</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.4</v>
       </c>
       <c r="I147" t="n">
-        <v>1.0499</v>
+        <v>1.0237</v>
       </c>
       <c r="J147" t="n">
-        <v>36.7465</v>
+        <v>35.8295</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.22</v>
       </c>
       <c r="I148" t="n">
-        <v>0.6364</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="J148" t="n">
-        <v>22.274</v>
+        <v>21.7875</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.18</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5309</v>
+        <v>0.5236</v>
       </c>
       <c r="J149" t="n">
-        <v>18.5815</v>
+        <v>18.326</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.03</v>
       </c>
       <c r="I150" t="n">
-        <v>0.0444</v>
+        <v>0.101</v>
       </c>
       <c r="J150" t="n">
-        <v>1.554</v>
+        <v>3.535</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.84</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6141</v>
+        <v>-0.5533</v>
       </c>
       <c r="J151" t="n">
-        <v>-21.4935</v>
+        <v>-19.3655</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>2.08</v>
       </c>
       <c r="I152" t="n">
-        <v>2.0274</v>
+        <v>1.7421</v>
       </c>
       <c r="J152" t="n">
-        <v>40.548</v>
+        <v>34.842</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.62</v>
       </c>
       <c r="I153" t="n">
-        <v>1.2982</v>
+        <v>1.2281</v>
       </c>
       <c r="J153" t="n">
-        <v>25.964</v>
+        <v>24.562</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.46</v>
       </c>
       <c r="I154" t="n">
-        <v>0.9389</v>
+        <v>1.0426</v>
       </c>
       <c r="J154" t="n">
-        <v>18.778</v>
+        <v>20.852</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.29</v>
       </c>
       <c r="I155" t="n">
-        <v>0.5778</v>
+        <v>0.7054</v>
       </c>
       <c r="J155" t="n">
-        <v>11.556</v>
+        <v>14.108</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.25</v>
       </c>
       <c r="I156" t="n">
-        <v>0.4896</v>
+        <v>0.6122</v>
       </c>
       <c r="J156" t="n">
-        <v>9.792</v>
+        <v>12.244</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>0.87</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.0378</v>
+        <v>-0.0593</v>
       </c>
       <c r="J157" t="n">
-        <v>-0.756</v>
+        <v>-1.186</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.57</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.3911</v>
       </c>
       <c r="J158" t="n">
-        <v>-10.192</v>
+        <v>-7.822</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.48</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.6788999999999999</v>
+        <v>-0.4717</v>
       </c>
       <c r="J159" t="n">
-        <v>-13.578</v>
+        <v>-9.433999999999999</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.45</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.7241</v>
+        <v>-0.5</v>
       </c>
       <c r="J160" t="n">
-        <v>-14.482</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.33</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.8893</v>
+        <v>-0.6165</v>
       </c>
       <c r="J161" t="n">
-        <v>-17.786</v>
+        <v>-12.33</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.04</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2172</v>
+        <v>0.2055</v>
       </c>
       <c r="J162" t="n">
-        <v>4.5612</v>
+        <v>4.3155</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.82</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.2349</v>
+        <v>-0.1899</v>
       </c>
       <c r="J163" t="n">
-        <v>-4.9329</v>
+        <v>-3.9879</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.67</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.4961</v>
+        <v>-0.3322</v>
       </c>
       <c r="J164" t="n">
-        <v>-10.4181</v>
+        <v>-6.9762</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.64</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.5394</v>
+        <v>-0.3603</v>
       </c>
       <c r="J165" t="n">
-        <v>-11.3274</v>
+        <v>-7.5663</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.6</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5948</v>
+        <v>-0.3978</v>
       </c>
       <c r="J166" t="n">
-        <v>-12.4908</v>
+        <v>-8.3538</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.99</v>
       </c>
       <c r="I167" t="n">
-        <v>1.9787</v>
+        <v>1.6793</v>
       </c>
       <c r="J167" t="n">
-        <v>41.5527</v>
+        <v>35.2653</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.37</v>
       </c>
       <c r="I168" t="n">
-        <v>0.8197</v>
+        <v>0.9103</v>
       </c>
       <c r="J168" t="n">
-        <v>17.2137</v>
+        <v>19.1163</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.35</v>
       </c>
       <c r="I169" t="n">
-        <v>0.7713</v>
+        <v>0.8681</v>
       </c>
       <c r="J169" t="n">
-        <v>16.1973</v>
+        <v>18.2301</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.34</v>
       </c>
       <c r="I170" t="n">
-        <v>0.7476</v>
+        <v>0.8465</v>
       </c>
       <c r="J170" t="n">
-        <v>15.6996</v>
+        <v>17.7765</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.9</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5225</v>
+        <v>-0.4463</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.9725</v>
+        <v>-9.372299999999999</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.06</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2846</v>
+        <v>0.297</v>
       </c>
       <c r="J172" t="n">
-        <v>6.5458</v>
+        <v>6.831</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.71</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.383</v>
+        <v>-0.2877</v>
       </c>
       <c r="J173" t="n">
-        <v>-8.808999999999999</v>
+        <v>-6.6171</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.7</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.4017</v>
+        <v>-0.2968</v>
       </c>
       <c r="J174" t="n">
-        <v>-9.239100000000001</v>
+        <v>-6.8264</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.53</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.6701</v>
+        <v>-0.4534</v>
       </c>
       <c r="J175" t="n">
-        <v>-15.4123</v>
+        <v>-10.4282</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.46</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.7613</v>
+        <v>-0.5189</v>
       </c>
       <c r="J176" t="n">
-        <v>-17.5099</v>
+        <v>-11.9347</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.92</v>
       </c>
       <c r="I177" t="n">
-        <v>1.884</v>
+        <v>1.5905</v>
       </c>
       <c r="J177" t="n">
-        <v>43.332</v>
+        <v>36.5815</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.36</v>
       </c>
       <c r="I178" t="n">
-        <v>0.7745</v>
+        <v>0.8834</v>
       </c>
       <c r="J178" t="n">
-        <v>17.8135</v>
+        <v>20.3182</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.35</v>
       </c>
       <c r="I179" t="n">
-        <v>0.7518</v>
+        <v>0.8618</v>
       </c>
       <c r="J179" t="n">
-        <v>17.2914</v>
+        <v>19.8214</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.26</v>
       </c>
       <c r="I180" t="n">
-        <v>0.5479000000000001</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="J180" t="n">
-        <v>12.6017</v>
+        <v>15.1524</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.24</v>
       </c>
       <c r="I181" t="n">
-        <v>0.5018</v>
+        <v>0.6116</v>
       </c>
       <c r="J181" t="n">
-        <v>11.5414</v>
+        <v>14.0668</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>2.03</v>
       </c>
       <c r="I182" t="n">
-        <v>2.0332</v>
+        <v>1.7474</v>
       </c>
       <c r="J182" t="n">
-        <v>42.6972</v>
+        <v>36.6954</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.55</v>
       </c>
       <c r="I183" t="n">
-        <v>1.2657</v>
+        <v>1.1788</v>
       </c>
       <c r="J183" t="n">
-        <v>26.5797</v>
+        <v>24.7548</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.27</v>
       </c>
       <c r="I184" t="n">
-        <v>0.6217</v>
+        <v>0.7039</v>
       </c>
       <c r="J184" t="n">
-        <v>13.0557</v>
+        <v>14.7819</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.21</v>
       </c>
       <c r="I185" t="n">
-        <v>0.4737</v>
+        <v>0.5626</v>
       </c>
       <c r="J185" t="n">
-        <v>9.947699999999999</v>
+        <v>11.8146</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.52</v>
       </c>
       <c r="I186" t="n">
-        <v>-1.3365</v>
+        <v>-1.3634</v>
       </c>
       <c r="J186" t="n">
-        <v>-28.0665</v>
+        <v>-28.6314</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.98</v>
       </c>
       <c r="I187" t="n">
-        <v>0.0362</v>
+        <v>-0.007</v>
       </c>
       <c r="J187" t="n">
-        <v>0.7602</v>
+        <v>-0.147</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.82</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2601</v>
+        <v>-0.1963</v>
       </c>
       <c r="J188" t="n">
-        <v>-5.4621</v>
+        <v>-4.1223</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.77</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3598</v>
+        <v>-0.2436</v>
       </c>
       <c r="J189" t="n">
-        <v>-7.5558</v>
+        <v>-5.1156</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.76</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3766</v>
+        <v>-0.2531</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.9086</v>
+        <v>-5.3151</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.66</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.526</v>
+        <v>-0.3481</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.046</v>
+        <v>-7.3101</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.32</v>
       </c>
       <c r="I192" t="n">
-        <v>0.8717</v>
+        <v>0.8591</v>
       </c>
       <c r="J192" t="n">
-        <v>26.151</v>
+        <v>25.773</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.25</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7075</v>
+        <v>0.6934</v>
       </c>
       <c r="J193" t="n">
-        <v>21.225</v>
+        <v>20.802</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.1</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2709</v>
+        <v>0.316</v>
       </c>
       <c r="J194" t="n">
-        <v>8.127000000000001</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.03</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0414</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="J195" t="n">
-        <v>1.242</v>
+        <v>2.985</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.099</v>
+        <v>-0.0333</v>
       </c>
       <c r="J196" t="n">
-        <v>-2.97</v>
+        <v>-0.999</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.16</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3381</v>
+        <v>0.376</v>
       </c>
       <c r="J197" t="n">
-        <v>10.143</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.16</v>
       </c>
       <c r="I198" t="n">
-        <v>0.3381</v>
+        <v>0.376</v>
       </c>
       <c r="J198" t="n">
-        <v>10.143</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.02</v>
       </c>
       <c r="I199" t="n">
-        <v>0.0867</v>
+        <v>0.0733</v>
       </c>
       <c r="J199" t="n">
-        <v>2.601</v>
+        <v>2.199</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.95</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1166</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="J200" t="n">
-        <v>-3.498</v>
+        <v>-2.172</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.52</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.736</v>
+        <v>-0.4979</v>
       </c>
       <c r="J201" t="n">
-        <v>-22.08</v>
+        <v>-14.937</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.99</v>
       </c>
       <c r="I202" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0353</v>
       </c>
       <c r="J202" t="n">
-        <v>1.8672</v>
+        <v>0.8472</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.89</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.12</v>
+        <v>-0.1148</v>
       </c>
       <c r="J203" t="n">
-        <v>-2.88</v>
+        <v>-2.7552</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.72</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.422</v>
+        <v>-0.2861</v>
       </c>
       <c r="J204" t="n">
-        <v>-10.128</v>
+        <v>-6.8664</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.64</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.5415</v>
+        <v>-0.3613</v>
       </c>
       <c r="J205" t="n">
-        <v>-12.996</v>
+        <v>-8.671200000000001</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6498</v>
+        <v>-0.4361</v>
       </c>
       <c r="J206" t="n">
-        <v>-15.5952</v>
+        <v>-10.4664</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.53</v>
       </c>
       <c r="I207" t="n">
-        <v>1.2119</v>
+        <v>1.1488</v>
       </c>
       <c r="J207" t="n">
-        <v>29.0856</v>
+        <v>27.5712</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.51</v>
       </c>
       <c r="I208" t="n">
-        <v>1.1716</v>
+        <v>1.1243</v>
       </c>
       <c r="J208" t="n">
-        <v>28.1184</v>
+        <v>26.9832</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.46</v>
       </c>
       <c r="I209" t="n">
-        <v>1.068</v>
+        <v>1.0626</v>
       </c>
       <c r="J209" t="n">
-        <v>25.632</v>
+        <v>25.5024</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.26</v>
       </c>
       <c r="I210" t="n">
-        <v>0.5813</v>
+        <v>0.6751</v>
       </c>
       <c r="J210" t="n">
-        <v>13.9512</v>
+        <v>16.2024</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.97</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3034</v>
+        <v>-0.2165</v>
       </c>
       <c r="J211" t="n">
-        <v>-7.2816</v>
+        <v>-5.196</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.87</v>
       </c>
       <c r="I212" t="n">
-        <v>1.7819</v>
+        <v>1.522</v>
       </c>
       <c r="J212" t="n">
-        <v>35.638</v>
+        <v>30.44</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.64</v>
       </c>
       <c r="I213" t="n">
-        <v>1.3656</v>
+        <v>1.2587</v>
       </c>
       <c r="J213" t="n">
-        <v>27.312</v>
+        <v>25.174</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.55</v>
       </c>
       <c r="I214" t="n">
-        <v>1.1864</v>
+        <v>1.1538</v>
       </c>
       <c r="J214" t="n">
-        <v>23.728</v>
+        <v>23.076</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.24</v>
       </c>
       <c r="I215" t="n">
-        <v>0.4843</v>
+        <v>0.6005</v>
       </c>
       <c r="J215" t="n">
-        <v>9.686</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.1</v>
       </c>
       <c r="I216" t="n">
-        <v>0.1428</v>
+        <v>0.24</v>
       </c>
       <c r="J216" t="n">
-        <v>2.856</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.83</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.1517</v>
+        <v>-0.1458</v>
       </c>
       <c r="J217" t="n">
-        <v>-3.034</v>
+        <v>-2.916</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.75</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.2774</v>
+        <v>-0.2336</v>
       </c>
       <c r="J218" t="n">
-        <v>-5.548</v>
+        <v>-4.672</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.71</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3398</v>
+        <v>-0.2748</v>
       </c>
       <c r="J219" t="n">
-        <v>-6.796</v>
+        <v>-5.496</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.5</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.6879999999999999</v>
+        <v>-0.4695</v>
       </c>
       <c r="J220" t="n">
-        <v>-13.76</v>
+        <v>-9.390000000000001</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.33</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.9086</v>
+        <v>-0.6309</v>
       </c>
       <c r="J221" t="n">
-        <v>-18.172</v>
+        <v>-12.618</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.61</v>
       </c>
       <c r="I222" t="n">
-        <v>1.3538</v>
+        <v>1.2399</v>
       </c>
       <c r="J222" t="n">
-        <v>28.4298</v>
+        <v>26.0379</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.48</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0936</v>
+        <v>1.0828</v>
       </c>
       <c r="J223" t="n">
-        <v>22.9656</v>
+        <v>22.7388</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.43</v>
       </c>
       <c r="I224" t="n">
-        <v>0.985</v>
+        <v>1.0173</v>
       </c>
       <c r="J224" t="n">
-        <v>20.685</v>
+        <v>21.3633</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.37</v>
       </c>
       <c r="I225" t="n">
-        <v>0.8299</v>
+        <v>0.9118000000000001</v>
       </c>
       <c r="J225" t="n">
-        <v>17.4279</v>
+        <v>19.1478</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.1765</v>
+        <v>-0.0902</v>
       </c>
       <c r="J226" t="n">
-        <v>-3.7065</v>
+        <v>-1.8942</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.89</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.0818</v>
+        <v>-0.0939</v>
       </c>
       <c r="J227" t="n">
-        <v>-1.7178</v>
+        <v>-1.9719</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.76</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.2926</v>
+        <v>-0.237</v>
       </c>
       <c r="J228" t="n">
-        <v>-6.1446</v>
+        <v>-4.977</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.67</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.4554</v>
+        <v>-0.3217</v>
       </c>
       <c r="J229" t="n">
-        <v>-9.5634</v>
+        <v>-6.7557</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.57</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.6111</v>
+        <v>-0.4139</v>
       </c>
       <c r="J230" t="n">
-        <v>-12.8331</v>
+        <v>-8.6919</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.51</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6932</v>
+        <v>-0.4701</v>
       </c>
       <c r="J231" t="n">
-        <v>-14.5572</v>
+        <v>-9.8721</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.76</v>
       </c>
       <c r="I232" t="n">
-        <v>1.6353</v>
+        <v>1.4196</v>
       </c>
       <c r="J232" t="n">
-        <v>35.9766</v>
+        <v>31.2312</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.37</v>
       </c>
       <c r="I233" t="n">
-        <v>0.845</v>
+        <v>0.9127</v>
       </c>
       <c r="J233" t="n">
-        <v>18.59</v>
+        <v>20.0794</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.31</v>
       </c>
       <c r="I234" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.7845</v>
       </c>
       <c r="J234" t="n">
-        <v>15.158</v>
+        <v>17.259</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.29</v>
       </c>
       <c r="I235" t="n">
-        <v>0.6418</v>
+        <v>0.7396</v>
       </c>
       <c r="J235" t="n">
-        <v>14.1196</v>
+        <v>16.2712</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.11</v>
       </c>
       <c r="I236" t="n">
-        <v>0.1997</v>
+        <v>0.2918</v>
       </c>
       <c r="J236" t="n">
-        <v>4.3934</v>
+        <v>6.4196</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.51</v>
       </c>
       <c r="I237" t="n">
-        <v>0.8466</v>
+        <v>1.0547</v>
       </c>
       <c r="J237" t="n">
-        <v>18.6252</v>
+        <v>23.2034</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.77</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.3683</v>
+        <v>-0.2455</v>
       </c>
       <c r="J238" t="n">
-        <v>-8.102600000000001</v>
+        <v>-5.401</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.7</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.4746</v>
+        <v>-0.3125</v>
       </c>
       <c r="J239" t="n">
-        <v>-10.4412</v>
+        <v>-6.875</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.55</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.6752</v>
+        <v>-0.4532</v>
       </c>
       <c r="J240" t="n">
-        <v>-14.8544</v>
+        <v>-9.9704</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.54</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.6878</v>
+        <v>-0.4624</v>
       </c>
       <c r="J241" t="n">
-        <v>-15.1316</v>
+        <v>-10.1728</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.19</v>
       </c>
       <c r="I242" t="n">
-        <v>0.6227</v>
+        <v>0.5816</v>
       </c>
       <c r="J242" t="n">
-        <v>29.8896</v>
+        <v>27.9168</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.06</v>
       </c>
       <c r="I243" t="n">
-        <v>0.2444</v>
+        <v>0.2205</v>
       </c>
       <c r="J243" t="n">
-        <v>11.7312</v>
+        <v>10.584</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.02</v>
       </c>
       <c r="I244" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0882</v>
       </c>
       <c r="J244" t="n">
-        <v>3.5232</v>
+        <v>4.2336</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.95</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2561</v>
+        <v>-0.2057</v>
       </c>
       <c r="J245" t="n">
-        <v>-12.2928</v>
+        <v>-9.8736</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2896</v>
+        <v>-0.2377</v>
       </c>
       <c r="J246" t="n">
-        <v>-13.9008</v>
+        <v>-11.4096</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.22</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4004</v>
+        <v>0.4645</v>
       </c>
       <c r="J247" t="n">
-        <v>19.2192</v>
+        <v>22.296</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.18</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3424</v>
+        <v>0.3918</v>
       </c>
       <c r="J248" t="n">
-        <v>16.4352</v>
+        <v>18.8064</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.06</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1395</v>
+        <v>0.1554</v>
       </c>
       <c r="J249" t="n">
-        <v>6.696</v>
+        <v>7.4592</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.93</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1856</v>
+        <v>-0.1037</v>
       </c>
       <c r="J250" t="n">
-        <v>-8.908799999999999</v>
+        <v>-4.9776</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.78</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4192</v>
+        <v>-0.2628</v>
       </c>
       <c r="J251" t="n">
-        <v>-20.1216</v>
+        <v>-12.6144</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2713/event_2713_evp_summary.xlsx
+++ b/database/event/2713/event_2713_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.1788</v>
+        <v>7.3497</v>
       </c>
       <c r="C2" t="n">
-        <v>2.1641</v>
+        <v>2.2156</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6029</v>
+        <v>2.7215</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1788</v>
+        <v>7.3497</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9168</v>
+        <v>2.8495</v>
       </c>
       <c r="G2" t="n">
-        <v>4.262</v>
+        <v>4.5002</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7905</v>
+        <v>4.5073</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4909</v>
+        <v>2.4339</v>
       </c>
       <c r="J2" t="n">
-        <v>4.262</v>
+        <v>4.5002</v>
       </c>
       <c r="K2" t="n">
         <v>80</v>
@@ -529,7 +529,7 @@
         <v>147</v>
       </c>
       <c r="M2" t="n">
-        <v>6.752899999999999</v>
+        <v>6.934100000000001</v>
       </c>
       <c r="N2" t="n">
         <v>227</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.2729</v>
+        <v>6.4943</v>
       </c>
       <c r="C3" t="n">
-        <v>1.891</v>
+        <v>1.9578</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1939</v>
+        <v>2.3321</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2729</v>
+        <v>6.4943</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2316</v>
+        <v>1.2291</v>
       </c>
       <c r="G3" t="n">
-        <v>5.0412</v>
+        <v>5.2652</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2316</v>
+        <v>1.2291</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6404</v>
+        <v>0.6637</v>
       </c>
       <c r="J3" t="n">
-        <v>5.0412</v>
+        <v>5.2652</v>
       </c>
       <c r="K3" t="n">
         <v>80</v>
@@ -575,7 +575,7 @@
         <v>147</v>
       </c>
       <c r="M3" t="n">
-        <v>5.6816</v>
+        <v>5.928900000000001</v>
       </c>
       <c r="N3" t="n">
         <v>227</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7022</v>
+        <v>5.7138</v>
       </c>
       <c r="C4" t="n">
-        <v>1.719</v>
+        <v>1.7225</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9362</v>
+        <v>1.9768</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7022</v>
+        <v>5.7138</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8866</v>
+        <v>2.7923</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8156</v>
+        <v>2.9215</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6843</v>
+        <v>4.3186</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4356</v>
+        <v>2.332</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8156</v>
+        <v>2.9215</v>
       </c>
       <c r="K4" t="n">
         <v>100</v>
@@ -621,7 +621,7 @@
         <v>188</v>
       </c>
       <c r="M4" t="n">
-        <v>5.2512</v>
+        <v>5.2535</v>
       </c>
       <c r="N4" t="n">
         <v>288</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.3492</v>
+        <v>5.3507</v>
       </c>
       <c r="C5" t="n">
-        <v>1.6126</v>
+        <v>1.613</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7769</v>
+        <v>1.8115</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3492</v>
+        <v>5.3507</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9456</v>
+        <v>2.633</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4036</v>
+        <v>2.7177</v>
       </c>
       <c r="H5" t="n">
-        <v>4.892</v>
+        <v>3.793</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5436</v>
+        <v>2.0482</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4036</v>
+        <v>2.7177</v>
       </c>
       <c r="K5" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="M5" t="n">
-        <v>4.9472</v>
+        <v>4.7659</v>
       </c>
       <c r="N5" t="n">
-        <v>227</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.3245</v>
+        <v>5.3491</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6051</v>
+        <v>1.6125</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7657</v>
+        <v>1.8108</v>
       </c>
       <c r="E6" t="n">
-        <v>5.3245</v>
+        <v>5.3491</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6953</v>
+        <v>2.8513</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6292</v>
+        <v>2.4978</v>
       </c>
       <c r="H6" t="n">
-        <v>4.0101</v>
+        <v>4.5132</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0851</v>
+        <v>2.4371</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6292</v>
+        <v>2.4978</v>
       </c>
       <c r="K6" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L6" t="n">
-        <v>188</v>
+        <v>147</v>
       </c>
       <c r="M6" t="n">
-        <v>4.7143</v>
+        <v>4.9349</v>
       </c>
       <c r="N6" t="n">
-        <v>288</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.5893</v>
+        <v>4.8965</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3835</v>
+        <v>1.4761</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4338</v>
+        <v>1.6048</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5893</v>
+        <v>4.8965</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1789</v>
+        <v>0.2485</v>
       </c>
       <c r="G7" t="n">
-        <v>4.4104</v>
+        <v>4.6479</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1789</v>
+        <v>0.2485</v>
       </c>
       <c r="I7" t="n">
-        <v>0.093</v>
+        <v>0.1342</v>
       </c>
       <c r="J7" t="n">
-        <v>4.4104</v>
+        <v>4.6479</v>
       </c>
       <c r="K7" t="n">
         <v>80</v>
@@ -759,7 +759,7 @@
         <v>147</v>
       </c>
       <c r="M7" t="n">
-        <v>4.5034</v>
+        <v>4.7821</v>
       </c>
       <c r="N7" t="n">
         <v>227</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.0462</v>
+        <v>4.041</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2198</v>
+        <v>1.2182</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1886</v>
+        <v>1.2153</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0462</v>
+        <v>4.041</v>
       </c>
       <c r="F8" t="n">
-        <v>4.2641</v>
+        <v>4.295</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2179</v>
+        <v>-0.254</v>
       </c>
       <c r="H8" t="n">
-        <v>9.537699999999999</v>
+        <v>9.2766</v>
       </c>
       <c r="I8" t="n">
-        <v>4.9592</v>
+        <v>5.0093</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2179</v>
+        <v>-0.254</v>
       </c>
       <c r="K8" t="n">
         <v>140</v>
@@ -805,7 +805,7 @@
         <v>40</v>
       </c>
       <c r="M8" t="n">
-        <v>4.7413</v>
+        <v>4.7553</v>
       </c>
       <c r="N8" t="n">
         <v>180</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7481</v>
+        <v>3.7033</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1299</v>
+        <v>1.1164</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0541</v>
+        <v>1.0616</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7481</v>
+        <v>3.7033</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4897</v>
+        <v>3.4457</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2584</v>
+        <v>0.2576</v>
       </c>
       <c r="H9" t="n">
-        <v>6.8094</v>
+        <v>6.4745</v>
       </c>
       <c r="I9" t="n">
-        <v>3.5406</v>
+        <v>3.4962</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2584</v>
+        <v>0.2576</v>
       </c>
       <c r="K9" t="n">
         <v>91</v>
@@ -851,7 +851,7 @@
         <v>81</v>
       </c>
       <c r="M9" t="n">
-        <v>3.799</v>
+        <v>3.7538</v>
       </c>
       <c r="N9" t="n">
         <v>172</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5453</v>
+        <v>3.5202</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0688</v>
+        <v>1.0612</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9625</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5453</v>
+        <v>3.5202</v>
       </c>
       <c r="F10" t="n">
-        <v>3.475</v>
+        <v>3.4157</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0703</v>
+        <v>0.1045</v>
       </c>
       <c r="H10" t="n">
-        <v>6.7576</v>
+        <v>6.3755</v>
       </c>
       <c r="I10" t="n">
-        <v>3.5136</v>
+        <v>3.4427</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0703</v>
+        <v>0.1045</v>
       </c>
       <c r="K10" t="n">
         <v>91</v>
@@ -897,7 +897,7 @@
         <v>81</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5839</v>
+        <v>3.5472</v>
       </c>
       <c r="N10" t="n">
         <v>172</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3271</v>
+        <v>3.2956</v>
       </c>
       <c r="C11" t="n">
-        <v>1.003</v>
+        <v>0.9935</v>
       </c>
       <c r="D11" t="n">
-        <v>0.864</v>
+        <v>0.876</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3271</v>
+        <v>3.2956</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9685</v>
+        <v>2.8771</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3586</v>
+        <v>0.4185</v>
       </c>
       <c r="H11" t="n">
-        <v>4.9729</v>
+        <v>4.5986</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5857</v>
+        <v>2.4832</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3586</v>
+        <v>0.4185</v>
       </c>
       <c r="K11" t="n">
         <v>91</v>
@@ -943,7 +943,7 @@
         <v>81</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9443</v>
+        <v>2.9017</v>
       </c>
       <c r="N11" t="n">
         <v>172</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9431</v>
+        <v>2.8554</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8872</v>
+        <v>0.8608</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6906</v>
+        <v>0.6756</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9431</v>
+        <v>2.8554</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8894</v>
+        <v>3.0073</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0537</v>
+        <v>-0.1519</v>
       </c>
       <c r="H12" t="n">
-        <v>4.6943</v>
+        <v>5.028</v>
       </c>
       <c r="I12" t="n">
-        <v>2.4408</v>
+        <v>2.7151</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0537</v>
+        <v>-0.1519</v>
       </c>
       <c r="K12" t="n">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="L12" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="M12" t="n">
-        <v>2.4945</v>
+        <v>2.5632</v>
       </c>
       <c r="N12" t="n">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8847</v>
+        <v>2.7993</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8696</v>
+        <v>0.8439</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6643</v>
+        <v>0.6501</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8847</v>
+        <v>2.7993</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0293</v>
+        <v>2.8289</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1446</v>
+        <v>-0.0296</v>
       </c>
       <c r="H13" t="n">
-        <v>5.1872</v>
+        <v>4.4393</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6971</v>
+        <v>2.3972</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1446</v>
+        <v>-0.0296</v>
       </c>
       <c r="K13" t="n">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="L13" t="n">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="M13" t="n">
-        <v>2.5525</v>
+        <v>2.3676</v>
       </c>
       <c r="N13" t="n">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6401</v>
+        <v>2.5325</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.7634</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.5286</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6401</v>
+        <v>2.5325</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8182</v>
+        <v>2.7214</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1781</v>
+        <v>-0.1889</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4433</v>
+        <v>4.0847</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3103</v>
+        <v>2.2057</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1781</v>
+        <v>-0.1889</v>
       </c>
       <c r="K14" t="n">
         <v>91</v>
@@ -1081,7 +1081,7 @@
         <v>81</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1322</v>
+        <v>2.0168</v>
       </c>
       <c r="N14" t="n">
         <v>172</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.4186</v>
+        <v>2.3794</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7291</v>
+        <v>0.7173</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4539</v>
+        <v>0.4589</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4186</v>
+        <v>2.3794</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3239</v>
+        <v>2.2448</v>
       </c>
       <c r="G15" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.1346</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7016</v>
+        <v>2.5123</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4047</v>
+        <v>1.3566</v>
       </c>
       <c r="J15" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.1346</v>
       </c>
       <c r="K15" t="n">
         <v>100</v>
@@ -1127,7 +1127,7 @@
         <v>188</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4994</v>
+        <v>1.4912</v>
       </c>
       <c r="N15" t="n">
         <v>288</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.316</v>
+        <v>2.2914</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6982</v>
+        <v>0.6908</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4075</v>
+        <v>0.4189</v>
       </c>
       <c r="E16" t="n">
-        <v>2.316</v>
+        <v>2.2914</v>
       </c>
       <c r="F16" t="n">
-        <v>2.316</v>
+        <v>2.2914</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.316</v>
+        <v>2.2914</v>
       </c>
       <c r="I16" t="n">
-        <v>2.316</v>
+        <v>2.2914</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.316</v>
+        <v>2.2914</v>
       </c>
       <c r="N16" t="n">
         <v>117</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1445</v>
+        <v>2.1731</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6465</v>
+        <v>0.6551</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3301</v>
+        <v>0.365</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1445</v>
+        <v>2.1731</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3985</v>
+        <v>2.3111</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.254</v>
+        <v>-0.138</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9647</v>
+        <v>2.731</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5415</v>
+        <v>1.4747</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.254</v>
+        <v>-0.138</v>
       </c>
       <c r="K17" t="n">
         <v>100</v>
@@ -1219,7 +1219,7 @@
         <v>188</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2875</v>
+        <v>1.3367</v>
       </c>
       <c r="N17" t="n">
         <v>288</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.0326</v>
+        <v>1.9369</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6127</v>
+        <v>0.5839</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2796</v>
+        <v>0.2575</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0326</v>
+        <v>1.9369</v>
       </c>
       <c r="F18" t="n">
-        <v>3.0326</v>
+        <v>2.9369</v>
       </c>
       <c r="G18" t="n">
         <v>-1</v>
       </c>
       <c r="H18" t="n">
-        <v>5.1987</v>
+        <v>4.7956</v>
       </c>
       <c r="I18" t="n">
-        <v>2.7031</v>
+        <v>2.5896</v>
       </c>
       <c r="J18" t="n">
         <v>-1</v>
@@ -1265,7 +1265,7 @@
         <v>40</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7031</v>
+        <v>1.5896</v>
       </c>
       <c r="N18" t="n">
         <v>180</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8258</v>
+        <v>1.7808</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5504</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1862</v>
+        <v>0.1865</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8258</v>
+        <v>1.7808</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5401</v>
+        <v>2.2076</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7143</v>
+        <v>-0.4268</v>
       </c>
       <c r="H19" t="n">
-        <v>3.4634</v>
+        <v>2.3895</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8008</v>
+        <v>1.2903</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7143</v>
+        <v>-0.4268</v>
       </c>
       <c r="K19" t="n">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="L19" t="n">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0865</v>
+        <v>0.8634999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>180</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.7155</v>
+        <v>1.6933</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5171</v>
+        <v>0.5105</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1364</v>
+        <v>0.1466</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7155</v>
+        <v>1.6933</v>
       </c>
       <c r="F20" t="n">
-        <v>2.274</v>
+        <v>2.4502</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5585</v>
+        <v>-0.7569</v>
       </c>
       <c r="H20" t="n">
-        <v>2.526</v>
+        <v>3.19</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3134</v>
+        <v>1.7226</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5585</v>
+        <v>-0.7569</v>
       </c>
       <c r="K20" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="L20" t="n">
-        <v>147</v>
+        <v>40</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7548999999999999</v>
+        <v>0.9656999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>227</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21">
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1817</v>
+        <v>1.0605</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3562</v>
+        <v>0.3197</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1045</v>
+        <v>-0.1414</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1817</v>
+        <v>1.0605</v>
       </c>
       <c r="F21" t="n">
-        <v>2.587</v>
+        <v>2.5116</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4053</v>
+        <v>-1.4511</v>
       </c>
       <c r="H21" t="n">
-        <v>3.6288</v>
+        <v>3.3926</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8868</v>
+        <v>1.832</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4053</v>
+        <v>-1.4511</v>
       </c>
       <c r="K21" t="n">
         <v>100</v>
@@ -1403,7 +1403,7 @@
         <v>188</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4815</v>
+        <v>0.3809</v>
       </c>
       <c r="N21" t="n">
         <v>288</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0454</v>
+        <v>1.0245</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3151</v>
+        <v>0.3088</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1661</v>
+        <v>-0.1578</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0454</v>
+        <v>1.0245</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0454</v>
+        <v>1.0245</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0454</v>
+        <v>1.0245</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0454</v>
+        <v>1.0245</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0454</v>
+        <v>1.0245</v>
       </c>
       <c r="N22" t="n">
         <v>142</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9329</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2828</v>
+        <v>0.2812</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2146</v>
+        <v>-0.1995</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9329</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9329</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9329</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9329</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9329</v>
       </c>
       <c r="N23" t="n">
         <v>81</v>
@@ -1504,93 +1504,93 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>aliStair</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8193</v>
+        <v>0.8253</v>
       </c>
       <c r="C24" t="n">
-        <v>0.247</v>
+        <v>0.2488</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2681</v>
+        <v>-0.2485</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8193</v>
+        <v>0.8253</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8193</v>
+        <v>0.8253</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8193</v>
+        <v>0.8253</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8193</v>
+        <v>0.8253</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8193</v>
+        <v>0.8253</v>
       </c>
       <c r="N24" t="n">
-        <v>117</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>aliStair</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8048</v>
+        <v>0.7016</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2426</v>
+        <v>0.2115</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2747</v>
+        <v>-0.3048</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8048</v>
+        <v>0.7016</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8048</v>
+        <v>0.7016</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8048</v>
+        <v>0.7016</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8048</v>
+        <v>0.7016</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8048</v>
+        <v>0.7016</v>
       </c>
       <c r="N25" t="n">
-        <v>142</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7297</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="C26" t="n">
-        <v>0.22</v>
+        <v>0.1904</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3086</v>
+        <v>-0.3367</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7297</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7297</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7297</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7297</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7297</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="N26" t="n">
         <v>67</v>
@@ -1642,93 +1642,93 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1168</v>
+        <v>0.089</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0352</v>
+        <v>0.0268</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5853</v>
+        <v>-0.5837</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1168</v>
+        <v>0.089</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1168</v>
+        <v>0.089</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1168</v>
+        <v>0.089</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1168</v>
+        <v>0.089</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1168</v>
+        <v>0.089</v>
       </c>
       <c r="N27" t="n">
-        <v>81</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.098</v>
+        <v>0.0002</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0295</v>
+        <v>0.0001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5938</v>
+        <v>-0.6241</v>
       </c>
       <c r="E28" t="n">
-        <v>0.098</v>
+        <v>0.0002</v>
       </c>
       <c r="F28" t="n">
-        <v>0.098</v>
+        <v>0.0002</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.098</v>
+        <v>0.0002</v>
       </c>
       <c r="I28" t="n">
-        <v>0.098</v>
+        <v>0.0002</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.098</v>
+        <v>0.0002</v>
       </c>
       <c r="N28" t="n">
-        <v>142</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.066</v>
+        <v>-0.0587</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0199</v>
+        <v>-0.0177</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6677999999999999</v>
+        <v>-0.6509</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.066</v>
+        <v>-0.0587</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.066</v>
+        <v>-0.0587</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.066</v>
+        <v>-0.0587</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.066</v>
+        <v>-0.0587</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.066</v>
+        <v>-0.0587</v>
       </c>
       <c r="N29" t="n">
         <v>142</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1663</v>
+        <v>-0.2187</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0501</v>
+        <v>-0.0659</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7131</v>
+        <v>-0.7238</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1663</v>
+        <v>-0.2187</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1663</v>
+        <v>-0.2187</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1663</v>
+        <v>-0.2187</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1663</v>
+        <v>-0.2187</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1663</v>
+        <v>-0.2187</v>
       </c>
       <c r="N30" t="n">
         <v>142</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3343</v>
+        <v>-0.3903</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1008</v>
+        <v>-0.1177</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7889</v>
+        <v>-0.8018999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3343</v>
+        <v>-0.3903</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3343</v>
+        <v>-0.3903</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3343</v>
+        <v>-0.3903</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3343</v>
+        <v>-0.3903</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3343</v>
+        <v>-0.3903</v>
       </c>
       <c r="N31" t="n">
         <v>117</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3568</v>
+        <v>-0.4475</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1076</v>
+        <v>-0.1349</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7991</v>
+        <v>-0.8279</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3568</v>
+        <v>-0.4475</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3568</v>
+        <v>-0.4475</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3568</v>
+        <v>-0.4475</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3568</v>
+        <v>-0.4475</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3568</v>
+        <v>-0.4475</v>
       </c>
       <c r="N32" t="n">
         <v>81</v>
@@ -1918,93 +1918,93 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>hazed</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5755</v>
+        <v>-0.6131</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1735</v>
+        <v>-0.1848</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8978</v>
+        <v>-0.9033</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5755</v>
+        <v>-0.6131</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5755</v>
+        <v>0.3869</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5755</v>
+        <v>0.3869</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5755</v>
+        <v>0.2089</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K33" t="n">
-        <v>81</v>
+        <v>140</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5755</v>
+        <v>-0.7911</v>
       </c>
       <c r="N33" t="n">
-        <v>81</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>hazed</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5827</v>
+        <v>-0.6469</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1757</v>
+        <v>-0.195</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9011</v>
+        <v>-0.9187</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5827</v>
+        <v>-0.6469</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4173</v>
+        <v>-0.6469</v>
       </c>
       <c r="G34" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.4173</v>
+        <v>-0.6469</v>
       </c>
       <c r="I34" t="n">
-        <v>0.217</v>
+        <v>-0.6469</v>
       </c>
       <c r="J34" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="L34" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.783</v>
+        <v>-0.6469</v>
       </c>
       <c r="N34" t="n">
-        <v>180</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6182</v>
+        <v>-0.6597</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1864</v>
+        <v>-0.1989</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9171</v>
+        <v>-0.9245</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6182</v>
+        <v>-0.6597</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6182</v>
+        <v>-0.6597</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6182</v>
+        <v>-0.6597</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6182</v>
+        <v>-0.6597</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6182</v>
+        <v>-0.6597</v>
       </c>
       <c r="N35" t="n">
         <v>67</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7215</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2175</v>
+        <v>-0.2347</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9637</v>
+        <v>-0.9787</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7215</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7215</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7215</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7215</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7215</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="N36" t="n">
         <v>67</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7595</v>
+        <v>-0.8136</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.229</v>
+        <v>-0.2453</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9809</v>
+        <v>-0.9946</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7595</v>
+        <v>-0.8136</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7595</v>
+        <v>-0.8136</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7595</v>
+        <v>-0.8136</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7595</v>
+        <v>-0.8136</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7595</v>
+        <v>-0.8136</v>
       </c>
       <c r="N37" t="n">
         <v>67</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2414</v>
+        <v>-1.2043</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3742</v>
+        <v>-0.363</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1984</v>
+        <v>-1.1724</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2414</v>
+        <v>-1.2043</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2414</v>
+        <v>-1.2043</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2414</v>
+        <v>-1.2043</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2414</v>
+        <v>-1.2043</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2414</v>
+        <v>-1.2043</v>
       </c>
       <c r="N38" t="n">
         <v>117</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2871</v>
+        <v>-1.3248</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.388</v>
+        <v>-0.3994</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2191</v>
+        <v>-1.2273</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2871</v>
+        <v>-1.3248</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2871</v>
+        <v>-1.3248</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2871</v>
+        <v>-1.3248</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2871</v>
+        <v>-1.3248</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2871</v>
+        <v>-1.3248</v>
       </c>
       <c r="N39" t="n">
         <v>67</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.5182</v>
+        <v>-1.541</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4577</v>
+        <v>-0.4645</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3234</v>
+        <v>-1.3257</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.5182</v>
+        <v>-1.541</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.5182</v>
+        <v>-1.541</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.5182</v>
+        <v>-1.541</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.5182</v>
+        <v>-1.541</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.5182</v>
+        <v>-1.541</v>
       </c>
       <c r="N40" t="n">
         <v>81</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.9271</v>
+        <v>-1.8509</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5809</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.508</v>
+        <v>-1.4668</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.9271</v>
+        <v>-1.8509</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.9271</v>
+        <v>-1.8509</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.9271</v>
+        <v>-1.8509</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.9271</v>
+        <v>-1.8509</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.9271</v>
+        <v>-1.8509</v>
       </c>
       <c r="N41" t="n">
         <v>117</v>
@@ -2429,10 +2429,10 @@
         <v>1.47</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0987</v>
+        <v>1.0786</v>
       </c>
       <c r="J2" t="n">
-        <v>30.7636</v>
+        <v>30.2008</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.24</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6505</v>
+        <v>0.6271</v>
       </c>
       <c r="J3" t="n">
-        <v>18.214</v>
+        <v>17.5588</v>
       </c>
     </row>
     <row r="4">
@@ -2589,10 +2589,10 @@
         <v>1.1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2983</v>
+        <v>0.3073</v>
       </c>
       <c r="J6" t="n">
-        <v>8.352399999999999</v>
+        <v>8.6044</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.15</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3804</v>
+        <v>0.3721</v>
       </c>
       <c r="J7" t="n">
-        <v>10.6512</v>
+        <v>10.4188</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.9</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1242</v>
+        <v>-0.1393</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.4776</v>
+        <v>-3.9004</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.87</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1555</v>
+        <v>-0.1714</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.354</v>
+        <v>-4.7992</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2166</v>
+        <v>-0.2329</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.0648</v>
+        <v>-6.5212</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.76</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2661</v>
+        <v>-0.2816</v>
       </c>
       <c r="J11" t="n">
-        <v>-7.4508</v>
+        <v>-7.8848</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.71</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3816</v>
+        <v>1.486</v>
       </c>
       <c r="J12" t="n">
-        <v>31.7768</v>
+        <v>34.178</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.44</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0474</v>
+        <v>1.008</v>
       </c>
       <c r="J13" t="n">
-        <v>24.0902</v>
+        <v>23.184</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.31</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7976</v>
+        <v>0.7601</v>
       </c>
       <c r="J14" t="n">
-        <v>18.3448</v>
+        <v>17.4823</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.98</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1642</v>
+        <v>-0.1485</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.7766</v>
+        <v>-3.4155</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.96</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2365</v>
+        <v>-0.219</v>
       </c>
       <c r="J16" t="n">
-        <v>-5.4395</v>
+        <v>-5.037</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.46</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9371</v>
+        <v>0.8783</v>
       </c>
       <c r="J17" t="n">
-        <v>21.5533</v>
+        <v>20.2009</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0799</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.8377</v>
+        <v>-2.1344</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.92</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1032</v>
+        <v>-0.1172</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.3736</v>
+        <v>-2.6956</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.7</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3249</v>
+        <v>-0.3388</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.4727</v>
+        <v>-7.7924</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.51</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.501</v>
+        <v>-0.507</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.523</v>
+        <v>-11.661</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.27</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4465</v>
+        <v>0.4413</v>
       </c>
       <c r="J22" t="n">
-        <v>12.9485</v>
+        <v>12.7977</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.18</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3196</v>
+        <v>0.322</v>
       </c>
       <c r="J23" t="n">
-        <v>9.2684</v>
+        <v>9.337999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.87</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1614</v>
+        <v>-0.1759</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.6806</v>
+        <v>-5.1011</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.75</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2826</v>
+        <v>-0.2965</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.195399999999999</v>
+        <v>-8.5985</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3401</v>
+        <v>-0.3525</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.8629</v>
+        <v>-10.2225</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.59</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7491</v>
+        <v>0.7372</v>
       </c>
       <c r="J27" t="n">
-        <v>21.7239</v>
+        <v>21.3788</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.26</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3684</v>
+        <v>0.3802</v>
       </c>
       <c r="J28" t="n">
-        <v>10.6836</v>
+        <v>11.0258</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.01</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0165</v>
+        <v>0.0245</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4785</v>
+        <v>0.7105</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.99</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0295</v>
+        <v>-0.0321</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.8555</v>
+        <v>-0.9308999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.63</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4112</v>
+        <v>-0.4183</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.9248</v>
+        <v>-12.1307</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.6</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2491</v>
+        <v>1.2998</v>
       </c>
       <c r="J32" t="n">
-        <v>33.7257</v>
+        <v>35.0946</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.6</v>
       </c>
       <c r="I33" t="n">
-        <v>1.2491</v>
+        <v>1.2998</v>
       </c>
       <c r="J33" t="n">
-        <v>33.7257</v>
+        <v>35.0946</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.25</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6655</v>
+        <v>0.6423</v>
       </c>
       <c r="J34" t="n">
-        <v>17.9685</v>
+        <v>17.3421</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.17</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4723</v>
+        <v>0.469</v>
       </c>
       <c r="J35" t="n">
-        <v>12.7521</v>
+        <v>12.663</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.75</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8179999999999999</v>
+        <v>-0.7488</v>
       </c>
       <c r="J36" t="n">
-        <v>-22.086</v>
+        <v>-20.2176</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.29</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6634</v>
+        <v>0.6286</v>
       </c>
       <c r="J37" t="n">
-        <v>17.9118</v>
+        <v>16.9722</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.99</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0041</v>
+        <v>-0.0126</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.1107</v>
+        <v>-0.3402</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.75</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2713</v>
+        <v>-0.2877</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.3251</v>
+        <v>-7.7679</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.7</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3194</v>
+        <v>-0.3345</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.623799999999999</v>
+        <v>-9.031499999999999</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.59</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4227</v>
+        <v>-0.4336</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.4129</v>
+        <v>-11.7072</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.61</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9855</v>
+        <v>1.0866</v>
       </c>
       <c r="J42" t="n">
-        <v>28.5795</v>
+        <v>31.5114</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.44</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7738</v>
+        <v>0.8591</v>
       </c>
       <c r="J43" t="n">
-        <v>22.4402</v>
+        <v>24.9139</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.37</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6843</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>19.8447</v>
+        <v>22.0864</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.22</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4868</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>14.1172</v>
+        <v>15.7122</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.78</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.745</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>-21.605</v>
+        <v>-19.836</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.34</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5662</v>
+        <v>0.6252</v>
       </c>
       <c r="J47" t="n">
-        <v>16.4198</v>
+        <v>18.1308</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.93</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0921</v>
+        <v>-0.1055</v>
       </c>
       <c r="J48" t="n">
-        <v>-2.6709</v>
+        <v>-3.0595</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.9</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.125</v>
+        <v>-0.1398</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.625</v>
+        <v>-4.0542</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.74</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.287</v>
+        <v>-0.3019</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.323</v>
+        <v>-8.755100000000001</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.64</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.382</v>
+        <v>-0.3938</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.078</v>
+        <v>-11.4202</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.33</v>
       </c>
       <c r="I52" t="n">
-        <v>0.466</v>
+        <v>0.5133</v>
       </c>
       <c r="J52" t="n">
-        <v>12.582</v>
+        <v>13.8591</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.84</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1839</v>
+        <v>-0.2007</v>
       </c>
       <c r="J53" t="n">
-        <v>-4.9653</v>
+        <v>-5.4189</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.8</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2239</v>
+        <v>-0.2406</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.0453</v>
+        <v>-6.4962</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.8</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2239</v>
+        <v>-0.2406</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.0453</v>
+        <v>-6.4962</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.61</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4057</v>
+        <v>-0.4171</v>
       </c>
       <c r="J56" t="n">
-        <v>-10.9539</v>
+        <v>-11.2617</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.68</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6179</v>
+        <v>0.7081</v>
       </c>
       <c r="J57" t="n">
-        <v>16.6833</v>
+        <v>19.1187</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.23</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3159</v>
+        <v>0.3336</v>
       </c>
       <c r="J58" t="n">
-        <v>8.529299999999999</v>
+        <v>9.007199999999999</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.17</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2449</v>
+        <v>0.2628</v>
       </c>
       <c r="J59" t="n">
-        <v>6.6123</v>
+        <v>7.0956</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.12</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1795</v>
+        <v>0.1978</v>
       </c>
       <c r="J60" t="n">
-        <v>4.8465</v>
+        <v>5.3406</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.82</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2401</v>
+        <v>-0.2491</v>
       </c>
       <c r="J61" t="n">
-        <v>-6.4827</v>
+        <v>-6.7257</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.41</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7516</v>
+        <v>0.8316</v>
       </c>
       <c r="J62" t="n">
-        <v>18.79</v>
+        <v>20.79</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.36</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6856</v>
+        <v>0.7598</v>
       </c>
       <c r="J63" t="n">
-        <v>17.14</v>
+        <v>18.995</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.2</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4674</v>
+        <v>0.5175</v>
       </c>
       <c r="J64" t="n">
-        <v>11.685</v>
+        <v>12.9375</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.11</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3281</v>
+        <v>0.3363</v>
       </c>
       <c r="J65" t="n">
-        <v>8.202500000000001</v>
+        <v>8.407500000000001</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.91</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3737</v>
+        <v>-0.3528</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.342499999999999</v>
+        <v>-8.82</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.11</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3005</v>
+        <v>0.2967</v>
       </c>
       <c r="J67" t="n">
-        <v>7.5125</v>
+        <v>7.4175</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0785</v>
+        <v>-0.0917</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.9625</v>
+        <v>-2.2925</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.89</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1343</v>
+        <v>-0.1498</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.3575</v>
+        <v>-3.745</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.77</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2558</v>
+        <v>-0.2716</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.395</v>
+        <v>-6.79</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.76</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2655</v>
+        <v>-0.2812</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.6375</v>
+        <v>-7.03</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>2.07</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4387</v>
+        <v>1.577</v>
       </c>
       <c r="J72" t="n">
-        <v>24.4579</v>
+        <v>26.809</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.79</v>
       </c>
       <c r="I73" t="n">
-        <v>1.1341</v>
+        <v>1.256</v>
       </c>
       <c r="J73" t="n">
-        <v>19.2797</v>
+        <v>21.352</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.68</v>
       </c>
       <c r="I74" t="n">
-        <v>1.0126</v>
+        <v>1.1262</v>
       </c>
       <c r="J74" t="n">
-        <v>17.2142</v>
+        <v>19.1454</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.53</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8442</v>
+        <v>0.9442</v>
       </c>
       <c r="J75" t="n">
-        <v>14.3514</v>
+        <v>16.0514</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.09</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1827</v>
+        <v>0.2199</v>
       </c>
       <c r="J76" t="n">
-        <v>3.1059</v>
+        <v>3.7383</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.89</v>
       </c>
       <c r="I77" t="n">
-        <v>0.0299</v>
+        <v>-0.0309</v>
       </c>
       <c r="J77" t="n">
-        <v>0.5083</v>
+        <v>-0.5253</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.59</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.3494</v>
+        <v>-0.3766</v>
       </c>
       <c r="J78" t="n">
-        <v>-5.9398</v>
+        <v>-6.4022</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3809</v>
+        <v>-0.4059</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.4753</v>
+        <v>-6.9003</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.16</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.7769</v>
+        <v>-0.7681</v>
       </c>
       <c r="J80" t="n">
-        <v>-13.2073</v>
+        <v>-13.0577</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.15</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7874</v>
+        <v>-0.7775</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.3858</v>
+        <v>-13.2175</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.77</v>
       </c>
       <c r="I82" t="n">
-        <v>1.1719</v>
+        <v>1.2852</v>
       </c>
       <c r="J82" t="n">
-        <v>26.9537</v>
+        <v>29.5596</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.53</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8816000000000001</v>
+        <v>0.9765</v>
       </c>
       <c r="J83" t="n">
-        <v>20.2768</v>
+        <v>22.4595</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.21</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4694</v>
+        <v>0.5231</v>
       </c>
       <c r="J84" t="n">
-        <v>10.7962</v>
+        <v>12.0313</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.07</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1887</v>
+        <v>0.2104</v>
       </c>
       <c r="J85" t="n">
-        <v>4.3401</v>
+        <v>4.8392</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.97</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2084</v>
+        <v>-0.19</v>
       </c>
       <c r="J86" t="n">
-        <v>-4.7932</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.03</v>
       </c>
       <c r="I87" t="n">
-        <v>0.163</v>
+        <v>0.1519</v>
       </c>
       <c r="J87" t="n">
-        <v>3.749</v>
+        <v>3.4937</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.99</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0238</v>
+        <v>0.0013</v>
       </c>
       <c r="J88" t="n">
-        <v>0.5474</v>
+        <v>0.0299</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.64</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3649</v>
+        <v>-0.3803</v>
       </c>
       <c r="J89" t="n">
-        <v>-8.3927</v>
+        <v>-8.7469</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.64</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3649</v>
+        <v>-0.3803</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.3927</v>
+        <v>-8.7469</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.62</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3837</v>
+        <v>-0.3982</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.825100000000001</v>
+        <v>-9.1586</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.84</v>
       </c>
       <c r="I92" t="n">
-        <v>1.516</v>
+        <v>1.5085</v>
       </c>
       <c r="J92" t="n">
-        <v>39.416</v>
+        <v>39.221</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.59</v>
       </c>
       <c r="I93" t="n">
-        <v>1.2199</v>
+        <v>1.1947</v>
       </c>
       <c r="J93" t="n">
-        <v>31.7174</v>
+        <v>31.0622</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.3</v>
       </c>
       <c r="I94" t="n">
-        <v>0.7644</v>
+        <v>0.7331</v>
       </c>
       <c r="J94" t="n">
-        <v>19.8744</v>
+        <v>19.0606</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.17</v>
       </c>
       <c r="I95" t="n">
-        <v>0.4542</v>
+        <v>0.4564</v>
       </c>
       <c r="J95" t="n">
-        <v>11.8092</v>
+        <v>11.8664</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.88</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4959</v>
+        <v>-0.4573</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.8934</v>
+        <v>-11.8898</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.02</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1621</v>
+        <v>0.1436</v>
       </c>
       <c r="J97" t="n">
-        <v>4.2146</v>
+        <v>3.7336</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.9</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.097</v>
+        <v>-0.1182</v>
       </c>
       <c r="J98" t="n">
-        <v>-2.522</v>
+        <v>-3.0732</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.84</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1649</v>
+        <v>-0.1862</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.2874</v>
+        <v>-4.8412</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.5</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4881</v>
+        <v>-0.4982</v>
       </c>
       <c r="J100" t="n">
-        <v>-12.6906</v>
+        <v>-12.9532</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.41</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5716</v>
+        <v>-0.5760999999999999</v>
       </c>
       <c r="J101" t="n">
-        <v>-14.8616</v>
+        <v>-14.9786</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>0.58</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.3524</v>
+        <v>-0.3805</v>
       </c>
       <c r="J102" t="n">
-        <v>-6.6956</v>
+        <v>-7.2295</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.53</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.4053</v>
+        <v>-0.4295</v>
       </c>
       <c r="J103" t="n">
-        <v>-7.7007</v>
+        <v>-8.160500000000001</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.44</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.4902</v>
+        <v>-0.5084</v>
       </c>
       <c r="J104" t="n">
-        <v>-9.313800000000001</v>
+        <v>-9.659599999999999</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.44</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4902</v>
+        <v>-0.5084</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.313800000000001</v>
+        <v>-9.659599999999999</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.27</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6586</v>
+        <v>-0.662</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.5134</v>
+        <v>-12.578</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.96</v>
       </c>
       <c r="I107" t="n">
-        <v>1.5951</v>
+        <v>1.601</v>
       </c>
       <c r="J107" t="n">
-        <v>30.3069</v>
+        <v>30.419</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.81</v>
       </c>
       <c r="I108" t="n">
-        <v>1.4309</v>
+        <v>1.4276</v>
       </c>
       <c r="J108" t="n">
-        <v>27.1871</v>
+        <v>27.1244</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.59</v>
       </c>
       <c r="I109" t="n">
-        <v>1.1878</v>
+        <v>1.167</v>
       </c>
       <c r="J109" t="n">
-        <v>22.5682</v>
+        <v>22.173</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.41</v>
       </c>
       <c r="I110" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.9087</v>
       </c>
       <c r="J110" t="n">
-        <v>18.0709</v>
+        <v>17.2653</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.35</v>
       </c>
       <c r="I111" t="n">
-        <v>0.8242</v>
+        <v>0.7953</v>
       </c>
       <c r="J111" t="n">
-        <v>15.6598</v>
+        <v>15.1107</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.49</v>
       </c>
       <c r="I112" t="n">
-        <v>1.101</v>
+        <v>1.0659</v>
       </c>
       <c r="J112" t="n">
-        <v>24.222</v>
+        <v>23.4498</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.41</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9918</v>
+        <v>0.9409</v>
       </c>
       <c r="J113" t="n">
-        <v>21.8196</v>
+        <v>20.6998</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.35</v>
       </c>
       <c r="I114" t="n">
-        <v>0.8749</v>
+        <v>0.8303</v>
       </c>
       <c r="J114" t="n">
-        <v>19.2478</v>
+        <v>18.2666</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.23</v>
       </c>
       <c r="I115" t="n">
-        <v>0.6062</v>
+        <v>0.592</v>
       </c>
       <c r="J115" t="n">
-        <v>13.3364</v>
+        <v>13.024</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.21</v>
       </c>
       <c r="I116" t="n">
-        <v>0.5579</v>
+        <v>0.5488</v>
       </c>
       <c r="J116" t="n">
-        <v>12.2738</v>
+        <v>12.0736</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.07</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2834</v>
+        <v>0.2648</v>
       </c>
       <c r="J117" t="n">
-        <v>6.2348</v>
+        <v>5.8256</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.97</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0095</v>
+        <v>-0.0268</v>
       </c>
       <c r="J118" t="n">
-        <v>-0.209</v>
+        <v>-0.5896</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.71</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2938</v>
+        <v>-0.3128</v>
       </c>
       <c r="J119" t="n">
-        <v>-6.4636</v>
+        <v>-6.8816</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.55</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4436</v>
+        <v>-0.4561</v>
       </c>
       <c r="J120" t="n">
-        <v>-9.7592</v>
+        <v>-10.0342</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.44</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5457</v>
+        <v>-0.5518</v>
       </c>
       <c r="J121" t="n">
-        <v>-12.0054</v>
+        <v>-12.1396</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.41</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7837</v>
+        <v>0.7508</v>
       </c>
       <c r="J122" t="n">
-        <v>22.7273</v>
+        <v>21.7732</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.18</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3876</v>
+        <v>0.3891</v>
       </c>
       <c r="J123" t="n">
-        <v>11.2404</v>
+        <v>11.2839</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.07</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1742</v>
+        <v>0.1849</v>
       </c>
       <c r="J124" t="n">
-        <v>5.0518</v>
+        <v>5.3621</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.04</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1092</v>
+        <v>0.1198</v>
       </c>
       <c r="J125" t="n">
-        <v>3.1668</v>
+        <v>3.4742</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.55</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4793</v>
+        <v>-0.4842</v>
       </c>
       <c r="J126" t="n">
-        <v>-13.8997</v>
+        <v>-14.0418</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.55</v>
       </c>
       <c r="I127" t="n">
-        <v>1.2216</v>
+        <v>1.1869</v>
       </c>
       <c r="J127" t="n">
-        <v>35.4264</v>
+        <v>34.4201</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.36</v>
       </c>
       <c r="I128" t="n">
-        <v>0.9481000000000001</v>
+        <v>0.8869</v>
       </c>
       <c r="J128" t="n">
-        <v>27.4949</v>
+        <v>25.7201</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.2</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5713</v>
+        <v>0.5528</v>
       </c>
       <c r="J129" t="n">
-        <v>16.5677</v>
+        <v>16.0312</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.03</v>
       </c>
       <c r="I130" t="n">
-        <v>0.099</v>
+        <v>0.1143</v>
       </c>
       <c r="J130" t="n">
-        <v>2.871</v>
+        <v>3.3147</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.57</v>
       </c>
       <c r="I131" t="n">
-        <v>-1.2193</v>
+        <v>-1.1014</v>
       </c>
       <c r="J131" t="n">
-        <v>-35.3597</v>
+        <v>-31.9406</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.45</v>
       </c>
       <c r="I132" t="n">
-        <v>1.1106</v>
+        <v>1.0641</v>
       </c>
       <c r="J132" t="n">
-        <v>31.0968</v>
+        <v>29.7948</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.12</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3819</v>
+        <v>0.3775</v>
       </c>
       <c r="J133" t="n">
-        <v>10.6932</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.06</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2129</v>
+        <v>0.2195</v>
       </c>
       <c r="J134" t="n">
-        <v>5.9612</v>
+        <v>6.146</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2129</v>
+        <v>0.2195</v>
       </c>
       <c r="J135" t="n">
-        <v>5.9612</v>
+        <v>6.146</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.9192</v>
+        <v>-0.8452</v>
       </c>
       <c r="J136" t="n">
-        <v>-25.7376</v>
+        <v>-23.6656</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.14</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3372</v>
+        <v>0.3364</v>
       </c>
       <c r="J137" t="n">
-        <v>9.441599999999999</v>
+        <v>9.4192</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1</v>
       </c>
       <c r="I138" t="n">
-        <v>0.0057</v>
+        <v>0.0041</v>
       </c>
       <c r="J138" t="n">
-        <v>0.1596</v>
+        <v>0.1148</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.99</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0178</v>
+        <v>-0.0232</v>
       </c>
       <c r="J139" t="n">
-        <v>-0.4984</v>
+        <v>-0.6496</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="J140" t="n">
-        <v>-2.366</v>
+        <v>-2.6936</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.74</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2935</v>
+        <v>-0.3069</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.218</v>
+        <v>-8.5932</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.09</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2314</v>
+        <v>0.2367</v>
       </c>
       <c r="J142" t="n">
-        <v>8.099</v>
+        <v>8.2845</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0699</v>
+        <v>0.0762</v>
       </c>
       <c r="J143" t="n">
-        <v>2.4465</v>
+        <v>2.667</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1</v>
       </c>
       <c r="I144" t="n">
-        <v>0.0029</v>
+        <v>0.002</v>
       </c>
       <c r="J144" t="n">
-        <v>0.1015</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.99</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0192</v>
+        <v>-0.0243</v>
       </c>
       <c r="J145" t="n">
-        <v>-0.672</v>
+        <v>-0.8505</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.79</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2464</v>
+        <v>-0.2603</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.624000000000001</v>
+        <v>-9.1105</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.4</v>
       </c>
       <c r="I147" t="n">
-        <v>1.0237</v>
+        <v>0.9656</v>
       </c>
       <c r="J147" t="n">
-        <v>35.8295</v>
+        <v>33.796</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.22</v>
       </c>
       <c r="I148" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.5981</v>
       </c>
       <c r="J148" t="n">
-        <v>21.7875</v>
+        <v>20.9335</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.18</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5236</v>
+        <v>0.5095</v>
       </c>
       <c r="J149" t="n">
-        <v>18.326</v>
+        <v>17.8325</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.03</v>
       </c>
       <c r="I150" t="n">
-        <v>0.101</v>
+        <v>0.1157</v>
       </c>
       <c r="J150" t="n">
-        <v>3.535</v>
+        <v>4.0495</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.84</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5533</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="J151" t="n">
-        <v>-19.3655</v>
+        <v>-18.1895</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>2.08</v>
       </c>
       <c r="I152" t="n">
-        <v>1.7421</v>
+        <v>1.7522</v>
       </c>
       <c r="J152" t="n">
-        <v>34.842</v>
+        <v>35.044</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.62</v>
       </c>
       <c r="I153" t="n">
-        <v>1.2281</v>
+        <v>1.2089</v>
       </c>
       <c r="J153" t="n">
-        <v>24.562</v>
+        <v>24.178</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.46</v>
       </c>
       <c r="I154" t="n">
-        <v>1.0426</v>
+        <v>1.003</v>
       </c>
       <c r="J154" t="n">
-        <v>20.852</v>
+        <v>20.06</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.29</v>
       </c>
       <c r="I155" t="n">
-        <v>0.7054</v>
+        <v>0.6879</v>
       </c>
       <c r="J155" t="n">
-        <v>14.108</v>
+        <v>13.758</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.25</v>
       </c>
       <c r="I156" t="n">
-        <v>0.6122</v>
+        <v>0.6054</v>
       </c>
       <c r="J156" t="n">
-        <v>12.244</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>0.87</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.0593</v>
+        <v>-0.0959</v>
       </c>
       <c r="J157" t="n">
-        <v>-1.186</v>
+        <v>-1.918</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.57</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.3911</v>
+        <v>-0.4122</v>
       </c>
       <c r="J158" t="n">
-        <v>-7.822</v>
+        <v>-8.244</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.48</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.4717</v>
+        <v>-0.4882</v>
       </c>
       <c r="J159" t="n">
-        <v>-9.433999999999999</v>
+        <v>-9.763999999999999</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.45</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.5</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="J160" t="n">
-        <v>-10</v>
+        <v>-10.292</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.33</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.6165</v>
+        <v>-0.6217</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.33</v>
+        <v>-12.434</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.04</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2055</v>
+        <v>0.1901</v>
       </c>
       <c r="J162" t="n">
-        <v>4.3155</v>
+        <v>3.9921</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.82</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1899</v>
+        <v>-0.2101</v>
       </c>
       <c r="J163" t="n">
-        <v>-3.9879</v>
+        <v>-4.4121</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.67</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.3322</v>
+        <v>-0.3497</v>
       </c>
       <c r="J164" t="n">
-        <v>-6.9762</v>
+        <v>-7.3437</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.64</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3603</v>
+        <v>-0.3768</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.5663</v>
+        <v>-7.9128</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.6</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3978</v>
+        <v>-0.4125</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.3538</v>
+        <v>-8.6625</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.99</v>
       </c>
       <c r="I167" t="n">
-        <v>1.6793</v>
+        <v>1.6809</v>
       </c>
       <c r="J167" t="n">
-        <v>35.2653</v>
+        <v>35.2989</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.37</v>
       </c>
       <c r="I168" t="n">
-        <v>0.9103</v>
+        <v>0.8631</v>
       </c>
       <c r="J168" t="n">
-        <v>19.1163</v>
+        <v>18.1251</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.35</v>
       </c>
       <c r="I169" t="n">
-        <v>0.8681</v>
+        <v>0.8257</v>
       </c>
       <c r="J169" t="n">
-        <v>18.2301</v>
+        <v>17.3397</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.34</v>
       </c>
       <c r="I170" t="n">
-        <v>0.8465</v>
+        <v>0.8067</v>
       </c>
       <c r="J170" t="n">
-        <v>17.7765</v>
+        <v>16.9407</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.9</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4463</v>
+        <v>-0.4102</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.372299999999999</v>
+        <v>-8.6142</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.06</v>
       </c>
       <c r="I172" t="n">
-        <v>0.297</v>
+        <v>0.2696</v>
       </c>
       <c r="J172" t="n">
-        <v>6.831</v>
+        <v>6.2008</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.71</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.2877</v>
+        <v>-0.3081</v>
       </c>
       <c r="J173" t="n">
-        <v>-6.6171</v>
+        <v>-7.0863</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.7</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2968</v>
+        <v>-0.317</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.8264</v>
+        <v>-7.291</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.53</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4534</v>
+        <v>-0.4666</v>
       </c>
       <c r="J175" t="n">
-        <v>-10.4282</v>
+        <v>-10.7318</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.46</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5189</v>
+        <v>-0.528</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.9347</v>
+        <v>-12.144</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.92</v>
       </c>
       <c r="I177" t="n">
-        <v>1.5905</v>
+        <v>1.5896</v>
       </c>
       <c r="J177" t="n">
-        <v>36.5815</v>
+        <v>36.5608</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.36</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8834</v>
+        <v>0.8404</v>
       </c>
       <c r="J178" t="n">
-        <v>20.3182</v>
+        <v>19.3292</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.35</v>
       </c>
       <c r="I179" t="n">
-        <v>0.8618</v>
+        <v>0.8214</v>
       </c>
       <c r="J179" t="n">
-        <v>19.8214</v>
+        <v>18.8922</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.26</v>
       </c>
       <c r="I180" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.6424</v>
       </c>
       <c r="J180" t="n">
-        <v>15.1524</v>
+        <v>14.7752</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.24</v>
       </c>
       <c r="I181" t="n">
-        <v>0.6116</v>
+        <v>0.6004</v>
       </c>
       <c r="J181" t="n">
-        <v>14.0668</v>
+        <v>13.8092</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>2.03</v>
       </c>
       <c r="I182" t="n">
-        <v>1.7474</v>
+        <v>1.7484</v>
       </c>
       <c r="J182" t="n">
-        <v>36.6954</v>
+        <v>36.7164</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.55</v>
       </c>
       <c r="I183" t="n">
-        <v>1.1788</v>
+        <v>1.1492</v>
       </c>
       <c r="J183" t="n">
-        <v>24.7548</v>
+        <v>24.1332</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.27</v>
       </c>
       <c r="I184" t="n">
-        <v>0.7039</v>
+        <v>0.6781</v>
       </c>
       <c r="J184" t="n">
-        <v>14.7819</v>
+        <v>14.2401</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.21</v>
       </c>
       <c r="I185" t="n">
-        <v>0.5626</v>
+        <v>0.5521</v>
       </c>
       <c r="J185" t="n">
-        <v>11.8146</v>
+        <v>11.5941</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.52</v>
       </c>
       <c r="I186" t="n">
-        <v>-1.3634</v>
+        <v>-1.2203</v>
       </c>
       <c r="J186" t="n">
-        <v>-28.6314</v>
+        <v>-25.6263</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.98</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.007</v>
+        <v>-0.0203</v>
       </c>
       <c r="J187" t="n">
-        <v>-0.147</v>
+        <v>-0.4263</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.82</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1963</v>
+        <v>-0.215</v>
       </c>
       <c r="J188" t="n">
-        <v>-4.1223</v>
+        <v>-4.515</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.77</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2436</v>
+        <v>-0.2622</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.1156</v>
+        <v>-5.5062</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.76</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2531</v>
+        <v>-0.2716</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.3151</v>
+        <v>-5.7036</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.66</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3481</v>
+        <v>-0.3638</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.3101</v>
+        <v>-7.6398</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.32</v>
       </c>
       <c r="I192" t="n">
-        <v>0.8591</v>
+        <v>0.8069</v>
       </c>
       <c r="J192" t="n">
-        <v>25.773</v>
+        <v>24.207</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.25</v>
       </c>
       <c r="I193" t="n">
-        <v>0.6934</v>
+        <v>0.6614</v>
       </c>
       <c r="J193" t="n">
-        <v>20.802</v>
+        <v>19.842</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.1</v>
       </c>
       <c r="I194" t="n">
-        <v>0.316</v>
+        <v>0.3195</v>
       </c>
       <c r="J194" t="n">
-        <v>9.48</v>
+        <v>9.585000000000001</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.03</v>
       </c>
       <c r="I195" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.1146</v>
       </c>
       <c r="J195" t="n">
-        <v>2.985</v>
+        <v>3.438</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.0333</v>
+        <v>-0.0229</v>
       </c>
       <c r="J196" t="n">
-        <v>-0.999</v>
+        <v>-0.6870000000000001</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.16</v>
       </c>
       <c r="I197" t="n">
-        <v>0.376</v>
+        <v>0.3729</v>
       </c>
       <c r="J197" t="n">
-        <v>11.28</v>
+        <v>11.187</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.16</v>
       </c>
       <c r="I198" t="n">
-        <v>0.376</v>
+        <v>0.3729</v>
       </c>
       <c r="J198" t="n">
-        <v>11.28</v>
+        <v>11.187</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.02</v>
       </c>
       <c r="I199" t="n">
-        <v>0.0733</v>
+        <v>0.0786</v>
       </c>
       <c r="J199" t="n">
-        <v>2.199</v>
+        <v>2.358</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.95</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.0834</v>
       </c>
       <c r="J200" t="n">
-        <v>-2.172</v>
+        <v>-2.502</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.52</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4979</v>
+        <v>-0.5031</v>
       </c>
       <c r="J201" t="n">
-        <v>-14.937</v>
+        <v>-15.093</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.99</v>
       </c>
       <c r="I202" t="n">
-        <v>0.0353</v>
+        <v>0.0098</v>
       </c>
       <c r="J202" t="n">
-        <v>0.8472</v>
+        <v>0.2352</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.89</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.1148</v>
+        <v>-0.1348</v>
       </c>
       <c r="J203" t="n">
-        <v>-2.7552</v>
+        <v>-3.2352</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.72</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2861</v>
+        <v>-0.3049</v>
       </c>
       <c r="J204" t="n">
-        <v>-6.8664</v>
+        <v>-7.3176</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.64</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3613</v>
+        <v>-0.3775</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.671200000000001</v>
+        <v>-9.06</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4361</v>
+        <v>-0.4487</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.4664</v>
+        <v>-10.7688</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.53</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1488</v>
+        <v>1.1181</v>
       </c>
       <c r="J207" t="n">
-        <v>27.5712</v>
+        <v>26.8344</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.51</v>
       </c>
       <c r="I208" t="n">
-        <v>1.1243</v>
+        <v>1.0917</v>
       </c>
       <c r="J208" t="n">
-        <v>26.9832</v>
+        <v>26.2008</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.46</v>
       </c>
       <c r="I209" t="n">
-        <v>1.0626</v>
+        <v>1.0217</v>
       </c>
       <c r="J209" t="n">
-        <v>25.5024</v>
+        <v>24.5208</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.26</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6751</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="J210" t="n">
-        <v>16.2024</v>
+        <v>15.6888</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.97</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2165</v>
+        <v>-0.1957</v>
       </c>
       <c r="J211" t="n">
-        <v>-5.196</v>
+        <v>-4.6968</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.87</v>
       </c>
       <c r="I212" t="n">
-        <v>1.522</v>
+        <v>1.5196</v>
       </c>
       <c r="J212" t="n">
-        <v>30.44</v>
+        <v>30.392</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.64</v>
       </c>
       <c r="I213" t="n">
-        <v>1.2587</v>
+        <v>1.2403</v>
       </c>
       <c r="J213" t="n">
-        <v>25.174</v>
+        <v>24.806</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.55</v>
       </c>
       <c r="I214" t="n">
-        <v>1.1538</v>
+        <v>1.1274</v>
       </c>
       <c r="J214" t="n">
-        <v>23.076</v>
+        <v>22.548</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.24</v>
       </c>
       <c r="I215" t="n">
-        <v>0.6005</v>
+        <v>0.5927</v>
       </c>
       <c r="J215" t="n">
-        <v>12.01</v>
+        <v>11.854</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.1</v>
       </c>
       <c r="I216" t="n">
-        <v>0.24</v>
+        <v>0.2665</v>
       </c>
       <c r="J216" t="n">
-        <v>4.8</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.83</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.1458</v>
+        <v>-0.1734</v>
       </c>
       <c r="J217" t="n">
-        <v>-2.916</v>
+        <v>-3.468</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.75</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.2336</v>
+        <v>-0.2586</v>
       </c>
       <c r="J218" t="n">
-        <v>-4.672</v>
+        <v>-5.172</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.71</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2748</v>
+        <v>-0.2982</v>
       </c>
       <c r="J219" t="n">
-        <v>-5.496</v>
+        <v>-5.964</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.5</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4695</v>
+        <v>-0.4836</v>
       </c>
       <c r="J220" t="n">
-        <v>-9.390000000000001</v>
+        <v>-9.672000000000001</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.33</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6309</v>
+        <v>-0.633</v>
       </c>
       <c r="J221" t="n">
-        <v>-12.618</v>
+        <v>-12.66</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.61</v>
       </c>
       <c r="I222" t="n">
-        <v>1.2399</v>
+        <v>1.2169</v>
       </c>
       <c r="J222" t="n">
-        <v>26.0379</v>
+        <v>25.5549</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.48</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0828</v>
+        <v>1.0465</v>
       </c>
       <c r="J223" t="n">
-        <v>22.7388</v>
+        <v>21.9765</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.43</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0173</v>
+        <v>0.97</v>
       </c>
       <c r="J224" t="n">
-        <v>21.3633</v>
+        <v>20.37</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.37</v>
       </c>
       <c r="I225" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.8642</v>
       </c>
       <c r="J225" t="n">
-        <v>19.1478</v>
+        <v>18.1482</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.0902</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="J226" t="n">
-        <v>-1.8942</v>
+        <v>-1.3167</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.89</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.0939</v>
+        <v>-0.1184</v>
       </c>
       <c r="J227" t="n">
-        <v>-1.9719</v>
+        <v>-2.4864</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.76</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.237</v>
+        <v>-0.2593</v>
       </c>
       <c r="J228" t="n">
-        <v>-4.977</v>
+        <v>-5.4453</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.67</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3217</v>
+        <v>-0.3417</v>
       </c>
       <c r="J229" t="n">
-        <v>-6.7557</v>
+        <v>-7.1757</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.57</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4139</v>
+        <v>-0.4298</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.6919</v>
+        <v>-9.0258</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.51</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4701</v>
+        <v>-0.4826</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.8721</v>
+        <v>-10.1346</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.76</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4196</v>
+        <v>1.4075</v>
       </c>
       <c r="J232" t="n">
-        <v>31.2312</v>
+        <v>30.965</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.37</v>
       </c>
       <c r="I233" t="n">
-        <v>0.9127</v>
+        <v>0.8648</v>
       </c>
       <c r="J233" t="n">
-        <v>20.0794</v>
+        <v>19.0256</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.31</v>
       </c>
       <c r="I234" t="n">
-        <v>0.7845</v>
+        <v>0.7513</v>
       </c>
       <c r="J234" t="n">
-        <v>17.259</v>
+        <v>16.5286</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.29</v>
       </c>
       <c r="I235" t="n">
-        <v>0.7396</v>
+        <v>0.7116</v>
       </c>
       <c r="J235" t="n">
-        <v>16.2712</v>
+        <v>15.6552</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.11</v>
       </c>
       <c r="I236" t="n">
-        <v>0.2918</v>
+        <v>0.3091</v>
       </c>
       <c r="J236" t="n">
-        <v>6.4196</v>
+        <v>6.8002</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.51</v>
       </c>
       <c r="I237" t="n">
-        <v>1.0547</v>
+        <v>0.9986</v>
       </c>
       <c r="J237" t="n">
-        <v>23.2034</v>
+        <v>21.9692</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.77</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.2455</v>
+        <v>-0.2637</v>
       </c>
       <c r="J238" t="n">
-        <v>-5.401</v>
+        <v>-5.8014</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.7</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.3125</v>
+        <v>-0.3291</v>
       </c>
       <c r="J239" t="n">
-        <v>-6.875</v>
+        <v>-7.2402</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.55</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4532</v>
+        <v>-0.4636</v>
       </c>
       <c r="J240" t="n">
-        <v>-9.9704</v>
+        <v>-10.1992</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.54</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4624</v>
+        <v>-0.4723</v>
       </c>
       <c r="J241" t="n">
-        <v>-10.1728</v>
+        <v>-10.3906</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.19</v>
       </c>
       <c r="I242" t="n">
-        <v>0.5816</v>
+        <v>0.5548</v>
       </c>
       <c r="J242" t="n">
-        <v>27.9168</v>
+        <v>26.6304</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.06</v>
       </c>
       <c r="I243" t="n">
-        <v>0.2205</v>
+        <v>0.2246</v>
       </c>
       <c r="J243" t="n">
-        <v>10.584</v>
+        <v>10.7808</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.02</v>
       </c>
       <c r="I244" t="n">
-        <v>0.0882</v>
+        <v>0.0959</v>
       </c>
       <c r="J244" t="n">
-        <v>4.2336</v>
+        <v>4.6032</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.95</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2057</v>
+        <v>-0.2061</v>
       </c>
       <c r="J245" t="n">
-        <v>-9.8736</v>
+        <v>-9.892799999999999</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2377</v>
+        <v>-0.2364</v>
       </c>
       <c r="J246" t="n">
-        <v>-11.4096</v>
+        <v>-11.3472</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.22</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4645</v>
+        <v>0.4597</v>
       </c>
       <c r="J247" t="n">
-        <v>22.296</v>
+        <v>22.0656</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.18</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3918</v>
+        <v>0.3921</v>
       </c>
       <c r="J248" t="n">
-        <v>18.8064</v>
+        <v>18.8208</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.06</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1554</v>
+        <v>0.1656</v>
       </c>
       <c r="J249" t="n">
-        <v>7.4592</v>
+        <v>7.9488</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.93</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1037</v>
+        <v>-0.1143</v>
       </c>
       <c r="J250" t="n">
-        <v>-4.9776</v>
+        <v>-5.4864</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.78</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2628</v>
+        <v>-0.2751</v>
       </c>
       <c r="J251" t="n">
-        <v>-12.6144</v>
+        <v>-13.2048</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2713/event_2713_evp_summary.xlsx
+++ b/database/event/2713/event_2713_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.3497</v>
+        <v>7.3334</v>
       </c>
       <c r="C2" t="n">
-        <v>2.2156</v>
+        <v>2.2107</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7215</v>
+        <v>2.7349</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3497</v>
+        <v>7.3334</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8495</v>
+        <v>2.855</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5002</v>
+        <v>4.4784</v>
       </c>
       <c r="H2" t="n">
-        <v>4.5073</v>
+        <v>4.2765</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4339</v>
+        <v>2.4011</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5002</v>
+        <v>4.4784</v>
       </c>
       <c r="K2" t="n">
         <v>80</v>
@@ -529,7 +529,7 @@
         <v>147</v>
       </c>
       <c r="M2" t="n">
-        <v>6.934100000000001</v>
+        <v>6.8795</v>
       </c>
       <c r="N2" t="n">
         <v>227</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.4943</v>
+        <v>6.3178</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9578</v>
+        <v>1.9045</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3321</v>
+        <v>2.2723</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4943</v>
+        <v>6.3178</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2291</v>
+        <v>1.0633</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2652</v>
+        <v>5.2545</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2291</v>
+        <v>1.0633</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6637</v>
+        <v>0.597</v>
       </c>
       <c r="J3" t="n">
-        <v>5.2652</v>
+        <v>5.2545</v>
       </c>
       <c r="K3" t="n">
         <v>80</v>
@@ -575,7 +575,7 @@
         <v>147</v>
       </c>
       <c r="M3" t="n">
-        <v>5.928900000000001</v>
+        <v>5.8515</v>
       </c>
       <c r="N3" t="n">
         <v>227</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7138</v>
+        <v>5.6392</v>
       </c>
       <c r="C4" t="n">
-        <v>1.7225</v>
+        <v>1.7</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9768</v>
+        <v>1.9631</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7138</v>
+        <v>5.6392</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7923</v>
+        <v>2.781</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9215</v>
+        <v>2.8582</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3186</v>
+        <v>3.9986</v>
       </c>
       <c r="I4" t="n">
-        <v>2.332</v>
+        <v>2.2451</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9215</v>
+        <v>2.8582</v>
       </c>
       <c r="K4" t="n">
         <v>100</v>
@@ -621,7 +621,7 @@
         <v>188</v>
       </c>
       <c r="M4" t="n">
-        <v>5.2535</v>
+        <v>5.1033</v>
       </c>
       <c r="N4" t="n">
         <v>288</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.3507</v>
+        <v>5.3263</v>
       </c>
       <c r="C5" t="n">
-        <v>1.613</v>
+        <v>1.6057</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8115</v>
+        <v>1.8206</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3507</v>
+        <v>5.3263</v>
       </c>
       <c r="F5" t="n">
-        <v>2.633</v>
+        <v>2.8504</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7177</v>
+        <v>2.4759</v>
       </c>
       <c r="H5" t="n">
-        <v>3.793</v>
+        <v>4.259</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0482</v>
+        <v>2.3913</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7177</v>
+        <v>2.4759</v>
       </c>
       <c r="K5" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L5" t="n">
-        <v>188</v>
+        <v>147</v>
       </c>
       <c r="M5" t="n">
-        <v>4.7659</v>
+        <v>4.8672</v>
       </c>
       <c r="N5" t="n">
-        <v>288</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.3491</v>
+        <v>5.3149</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6125</v>
+        <v>1.6022</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8108</v>
+        <v>1.8154</v>
       </c>
       <c r="E6" t="n">
-        <v>5.3491</v>
+        <v>5.3149</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8513</v>
+        <v>2.6887</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4978</v>
+        <v>2.6262</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5132</v>
+        <v>3.652</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4371</v>
+        <v>2.0505</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4978</v>
+        <v>2.6262</v>
       </c>
       <c r="K6" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L6" t="n">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="M6" t="n">
-        <v>4.9349</v>
+        <v>4.6767</v>
       </c>
       <c r="N6" t="n">
-        <v>227</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.8965</v>
+        <v>4.9283</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4761</v>
+        <v>1.4857</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6048</v>
+        <v>1.6393</v>
       </c>
       <c r="E7" t="n">
-        <v>4.8965</v>
+        <v>4.9283</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2485</v>
+        <v>0.2139</v>
       </c>
       <c r="G7" t="n">
-        <v>4.6479</v>
+        <v>4.7144</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2485</v>
+        <v>0.2139</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1342</v>
+        <v>0.1201</v>
       </c>
       <c r="J7" t="n">
-        <v>4.6479</v>
+        <v>4.7144</v>
       </c>
       <c r="K7" t="n">
         <v>80</v>
@@ -759,7 +759,7 @@
         <v>147</v>
       </c>
       <c r="M7" t="n">
-        <v>4.7821</v>
+        <v>4.8345</v>
       </c>
       <c r="N7" t="n">
         <v>227</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.041</v>
+        <v>3.8143</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2182</v>
+        <v>1.1498</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2153</v>
+        <v>1.1318</v>
       </c>
       <c r="E8" t="n">
-        <v>4.041</v>
+        <v>3.8143</v>
       </c>
       <c r="F8" t="n">
-        <v>4.295</v>
+        <v>4.0946</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.254</v>
+        <v>-0.2803</v>
       </c>
       <c r="H8" t="n">
-        <v>9.2766</v>
+        <v>8.930199999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>5.0093</v>
+        <v>5.014</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.254</v>
+        <v>-0.2803</v>
       </c>
       <c r="K8" t="n">
         <v>140</v>
@@ -805,7 +805,7 @@
         <v>40</v>
       </c>
       <c r="M8" t="n">
-        <v>4.7553</v>
+        <v>4.733700000000001</v>
       </c>
       <c r="N8" t="n">
         <v>180</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7033</v>
+        <v>3.594</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1164</v>
+        <v>1.0834</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0616</v>
+        <v>1.0315</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7033</v>
+        <v>3.594</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4457</v>
+        <v>3.4161</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2576</v>
+        <v>0.1779</v>
       </c>
       <c r="H9" t="n">
-        <v>6.4745</v>
+        <v>6.3827</v>
       </c>
       <c r="I9" t="n">
-        <v>3.4962</v>
+        <v>3.5837</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2576</v>
+        <v>0.1779</v>
       </c>
       <c r="K9" t="n">
         <v>91</v>
@@ -851,7 +851,7 @@
         <v>81</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7538</v>
+        <v>3.7616</v>
       </c>
       <c r="N9" t="n">
         <v>172</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5202</v>
+        <v>3.4843</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0612</v>
+        <v>1.0504</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9815</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5202</v>
+        <v>3.4843</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4157</v>
+        <v>3.368</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1045</v>
+        <v>0.1163</v>
       </c>
       <c r="H10" t="n">
-        <v>6.3755</v>
+        <v>6.2025</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4427</v>
+        <v>3.4825</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1045</v>
+        <v>0.1163</v>
       </c>
       <c r="K10" t="n">
         <v>91</v>
@@ -897,7 +897,7 @@
         <v>81</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5472</v>
+        <v>3.5988</v>
       </c>
       <c r="N10" t="n">
         <v>172</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2956</v>
+        <v>3.2893</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9935</v>
+        <v>0.9916</v>
       </c>
       <c r="D11" t="n">
-        <v>0.876</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2956</v>
+        <v>3.2893</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8771</v>
+        <v>2.8805</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4185</v>
+        <v>0.4088</v>
       </c>
       <c r="H11" t="n">
-        <v>4.5986</v>
+        <v>4.3719</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4832</v>
+        <v>2.4547</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4185</v>
+        <v>0.4088</v>
       </c>
       <c r="K11" t="n">
         <v>91</v>
@@ -943,7 +943,7 @@
         <v>81</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9017</v>
+        <v>2.8635</v>
       </c>
       <c r="N11" t="n">
         <v>172</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8554</v>
+        <v>2.8788</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8608</v>
+        <v>0.8678</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6756</v>
+        <v>0.7056</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8554</v>
+        <v>2.8788</v>
       </c>
       <c r="F12" t="n">
-        <v>3.0073</v>
+        <v>2.835</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1519</v>
+        <v>0.0438</v>
       </c>
       <c r="H12" t="n">
-        <v>5.028</v>
+        <v>4.2013</v>
       </c>
       <c r="I12" t="n">
-        <v>2.7151</v>
+        <v>2.3589</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1519</v>
+        <v>0.0438</v>
       </c>
       <c r="K12" t="n">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="L12" t="n">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5632</v>
+        <v>2.4027</v>
       </c>
       <c r="N12" t="n">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7993</v>
+        <v>2.8118</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8439</v>
+        <v>0.8476</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6501</v>
+        <v>0.6751</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7993</v>
+        <v>2.8118</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8289</v>
+        <v>2.9939</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0296</v>
+        <v>-0.1821</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4393</v>
+        <v>4.7976</v>
       </c>
       <c r="I13" t="n">
-        <v>2.3972</v>
+        <v>2.6937</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0296</v>
+        <v>-0.1821</v>
       </c>
       <c r="K13" t="n">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="L13" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3676</v>
+        <v>2.5116</v>
       </c>
       <c r="N13" t="n">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5325</v>
+        <v>2.5539</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7634</v>
+        <v>0.7699</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5286</v>
+        <v>0.5576</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5325</v>
+        <v>2.5539</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7214</v>
+        <v>2.7487</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1889</v>
+        <v>-0.1948</v>
       </c>
       <c r="H14" t="n">
-        <v>4.0847</v>
+        <v>3.8773</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2057</v>
+        <v>2.177</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1889</v>
+        <v>-0.1948</v>
       </c>
       <c r="K14" t="n">
         <v>91</v>
@@ -1081,7 +1081,7 @@
         <v>81</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0168</v>
+        <v>1.9822</v>
       </c>
       <c r="N14" t="n">
         <v>172</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3794</v>
+        <v>2.5468</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7173</v>
+        <v>0.7678</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4589</v>
+        <v>0.5544</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3794</v>
+        <v>2.5468</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2448</v>
+        <v>2.3979</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1346</v>
+        <v>0.1489</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5123</v>
+        <v>2.5602</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3566</v>
+        <v>1.4375</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1346</v>
+        <v>0.1489</v>
       </c>
       <c r="K15" t="n">
         <v>100</v>
@@ -1127,7 +1127,7 @@
         <v>188</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4912</v>
+        <v>1.5864</v>
       </c>
       <c r="N15" t="n">
         <v>288</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2914</v>
+        <v>2.3426</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6908</v>
+        <v>0.7062</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4189</v>
+        <v>0.4614</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2914</v>
+        <v>2.3426</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2914</v>
+        <v>2.3426</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2914</v>
+        <v>2.4183</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2914</v>
+        <v>2.4183</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.2914</v>
+        <v>2.4183</v>
       </c>
       <c r="N16" t="n">
         <v>117</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1731</v>
+        <v>2.2288</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6551</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.365</v>
+        <v>0.4095</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1731</v>
+        <v>2.2288</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3111</v>
+        <v>2.38</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.138</v>
+        <v>-0.1512</v>
       </c>
       <c r="H17" t="n">
-        <v>2.731</v>
+        <v>2.4929</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4747</v>
+        <v>1.3997</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.138</v>
+        <v>-0.1512</v>
       </c>
       <c r="K17" t="n">
         <v>100</v>
@@ -1219,7 +1219,7 @@
         <v>188</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3367</v>
+        <v>1.2485</v>
       </c>
       <c r="N17" t="n">
         <v>288</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9369</v>
+        <v>1.9077</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5839</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2575</v>
+        <v>0.2633</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9369</v>
+        <v>1.9077</v>
       </c>
       <c r="F18" t="n">
-        <v>2.9369</v>
+        <v>2.9077</v>
       </c>
       <c r="G18" t="n">
         <v>-1</v>
       </c>
       <c r="H18" t="n">
-        <v>4.7956</v>
+        <v>4.474</v>
       </c>
       <c r="I18" t="n">
-        <v>2.5896</v>
+        <v>2.512</v>
       </c>
       <c r="J18" t="n">
         <v>-1</v>
@@ -1265,7 +1265,7 @@
         <v>40</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5896</v>
+        <v>1.512</v>
       </c>
       <c r="N18" t="n">
         <v>180</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.7808</v>
+        <v>1.7911</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5399</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1865</v>
+        <v>0.2101</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7808</v>
+        <v>1.7911</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2076</v>
+        <v>2.5296</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4268</v>
+        <v>-0.7385</v>
       </c>
       <c r="H19" t="n">
-        <v>2.3895</v>
+        <v>3.0547</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2903</v>
+        <v>1.7151</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4268</v>
+        <v>-0.7385</v>
       </c>
       <c r="K19" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="L19" t="n">
-        <v>147</v>
+        <v>40</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8634999999999999</v>
+        <v>0.9766</v>
       </c>
       <c r="N19" t="n">
-        <v>227</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.6933</v>
+        <v>1.692</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5105</v>
+        <v>0.5101</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1466</v>
+        <v>0.165</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6933</v>
+        <v>1.692</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4502</v>
+        <v>2.1446</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7569</v>
+        <v>-0.4526</v>
       </c>
       <c r="H20" t="n">
-        <v>3.19</v>
+        <v>2.1446</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7226</v>
+        <v>1.2041</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7569</v>
+        <v>-0.4526</v>
       </c>
       <c r="K20" t="n">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="L20" t="n">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9656999999999999</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>180</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21">
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0605</v>
+        <v>1.1024</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3197</v>
+        <v>0.3323</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1414</v>
+        <v>-0.1036</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0605</v>
+        <v>1.1024</v>
       </c>
       <c r="F21" t="n">
-        <v>2.5116</v>
+        <v>2.5652</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4511</v>
+        <v>-1.4628</v>
       </c>
       <c r="H21" t="n">
-        <v>3.3926</v>
+        <v>3.1882</v>
       </c>
       <c r="I21" t="n">
-        <v>1.832</v>
+        <v>1.7901</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4511</v>
+        <v>-1.4628</v>
       </c>
       <c r="K21" t="n">
         <v>100</v>
@@ -1403,7 +1403,7 @@
         <v>188</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3809</v>
+        <v>0.3272999999999999</v>
       </c>
       <c r="N21" t="n">
         <v>288</v>
@@ -1412,93 +1412,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>USTILO</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0245</v>
+        <v>1.0002</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3088</v>
+        <v>0.3015</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1578</v>
+        <v>-0.1501</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0245</v>
+        <v>1.0002</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0245</v>
+        <v>1.0002</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0245</v>
+        <v>1.0002</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0245</v>
+        <v>1.0002</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0245</v>
+        <v>1.0002</v>
       </c>
       <c r="N22" t="n">
-        <v>142</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>USTILO</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9329</v>
+        <v>0.902</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2812</v>
+        <v>0.2719</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1995</v>
+        <v>-0.1949</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9329</v>
+        <v>0.902</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9329</v>
+        <v>0.902</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9329</v>
+        <v>0.902</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9329</v>
+        <v>0.902</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9329</v>
+        <v>0.902</v>
       </c>
       <c r="N23" t="n">
-        <v>81</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8253</v>
+        <v>0.6717</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2488</v>
+        <v>0.2025</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2485</v>
+        <v>-0.2998</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8253</v>
+        <v>0.6717</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8253</v>
+        <v>0.6717</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8253</v>
+        <v>0.6717</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8253</v>
+        <v>0.6717</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8253</v>
+        <v>0.6717</v>
       </c>
       <c r="N24" t="n">
         <v>142</v>
@@ -1550,185 +1550,185 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>aliStair</t>
+          <t>aumaN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7016</v>
+        <v>0.6414</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2115</v>
+        <v>0.1934</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3048</v>
+        <v>-0.3136</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7016</v>
+        <v>0.6414</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7016</v>
+        <v>0.6414</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7016</v>
+        <v>0.6414</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7016</v>
+        <v>0.6414</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7016</v>
+        <v>0.6414</v>
       </c>
       <c r="N25" t="n">
-        <v>117</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>aumaN</t>
+          <t>aliStair</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.6304</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1904</v>
+        <v>0.19</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3367</v>
+        <v>-0.3186</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.6304</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.6304</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.6304</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.6304</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.6304</v>
       </c>
       <c r="N26" t="n">
-        <v>67</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.089</v>
+        <v>0.0269</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0268</v>
+        <v>0.0081</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5837</v>
+        <v>-0.5935</v>
       </c>
       <c r="E27" t="n">
-        <v>0.089</v>
+        <v>0.0269</v>
       </c>
       <c r="F27" t="n">
-        <v>0.089</v>
+        <v>0.0269</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.089</v>
+        <v>0.0269</v>
       </c>
       <c r="I27" t="n">
-        <v>0.089</v>
+        <v>0.0269</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.089</v>
+        <v>0.0269</v>
       </c>
       <c r="N27" t="n">
-        <v>142</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0002</v>
+        <v>0.0032</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0001</v>
+        <v>0.001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6241</v>
+        <v>-0.6042999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0002</v>
+        <v>0.0032</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0002</v>
+        <v>0.0032</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0002</v>
+        <v>0.0032</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0002</v>
+        <v>0.0032</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0002</v>
+        <v>0.0032</v>
       </c>
       <c r="N28" t="n">
-        <v>81</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0587</v>
+        <v>-0.0674</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0177</v>
+        <v>-0.0203</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6509</v>
+        <v>-0.6365</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0587</v>
+        <v>-0.0674</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0587</v>
+        <v>-0.0674</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0587</v>
+        <v>-0.0674</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0587</v>
+        <v>-0.0674</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0587</v>
+        <v>-0.0674</v>
       </c>
       <c r="N29" t="n">
         <v>142</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2187</v>
+        <v>-0.2256</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0659</v>
+        <v>-0.068</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7238</v>
+        <v>-0.7086</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2187</v>
+        <v>-0.2256</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2187</v>
+        <v>-0.2256</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2187</v>
+        <v>-0.2256</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2187</v>
+        <v>-0.2256</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2187</v>
+        <v>-0.2256</v>
       </c>
       <c r="N30" t="n">
         <v>142</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3903</v>
+        <v>-0.4269</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1177</v>
+        <v>-0.1287</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8018999999999999</v>
+        <v>-0.8003</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3903</v>
+        <v>-0.4269</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3903</v>
+        <v>-0.4269</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3903</v>
+        <v>-0.4269</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3903</v>
+        <v>-0.4269</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3903</v>
+        <v>-0.4269</v>
       </c>
       <c r="N31" t="n">
         <v>117</v>
@@ -1872,185 +1872,185 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Nifty</t>
+          <t>hazed</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4475</v>
+        <v>-0.4434</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1349</v>
+        <v>-0.1337</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8279</v>
+        <v>-0.8078</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4475</v>
+        <v>-0.4434</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4475</v>
+        <v>0.5566</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4475</v>
+        <v>0.5566</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4475</v>
+        <v>0.3125</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K32" t="n">
-        <v>81</v>
+        <v>140</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4475</v>
+        <v>-0.6875</v>
       </c>
       <c r="N32" t="n">
-        <v>81</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>hazed</t>
+          <t>Nifty</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6131</v>
+        <v>-0.4441</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1848</v>
+        <v>-0.1339</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9033</v>
+        <v>-0.8081</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6131</v>
+        <v>-0.4441</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3869</v>
+        <v>-0.4441</v>
       </c>
       <c r="G33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3869</v>
+        <v>-0.4441</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2089</v>
+        <v>-0.4441</v>
       </c>
       <c r="J33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="L33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7911</v>
+        <v>-0.4441</v>
       </c>
       <c r="N33" t="n">
-        <v>180</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>zhokiNg</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6469</v>
+        <v>-0.6745</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.195</v>
+        <v>-0.2033</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9187</v>
+        <v>-0.9131</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6469</v>
+        <v>-0.6745</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6469</v>
+        <v>-0.6745</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6469</v>
+        <v>-0.6745</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6469</v>
+        <v>-0.6745</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6469</v>
+        <v>-0.6745</v>
       </c>
       <c r="N34" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>zhokiNg</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6597</v>
+        <v>-0.6784</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1989</v>
+        <v>-0.2045</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9245</v>
+        <v>-0.9147999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6597</v>
+        <v>-0.6784</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6597</v>
+        <v>-0.6784</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6597</v>
+        <v>-0.6784</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6597</v>
+        <v>-0.6784</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6597</v>
+        <v>-0.6784</v>
       </c>
       <c r="N35" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7786999999999999</v>
+        <v>-0.7288</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2347</v>
+        <v>-0.2197</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9787</v>
+        <v>-0.9378</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7786999999999999</v>
+        <v>-0.7288</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7786999999999999</v>
+        <v>-0.7288</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7786999999999999</v>
+        <v>-0.7288</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7786999999999999</v>
+        <v>-0.7288</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7786999999999999</v>
+        <v>-0.7288</v>
       </c>
       <c r="N36" t="n">
         <v>67</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8136</v>
+        <v>-0.7678</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2453</v>
+        <v>-0.2315</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9946</v>
+        <v>-0.9556</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8136</v>
+        <v>-0.7678</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8136</v>
+        <v>-0.7678</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8136</v>
+        <v>-0.7678</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8136</v>
+        <v>-0.7678</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8136</v>
+        <v>-0.7678</v>
       </c>
       <c r="N37" t="n">
         <v>67</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2043</v>
+        <v>-1.1859</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.363</v>
+        <v>-0.3575</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1724</v>
+        <v>-1.146</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2043</v>
+        <v>-1.1859</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2043</v>
+        <v>-1.1859</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2043</v>
+        <v>-1.1859</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2043</v>
+        <v>-1.1859</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2043</v>
+        <v>-1.1859</v>
       </c>
       <c r="N38" t="n">
         <v>117</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3248</v>
+        <v>-1.3021</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3994</v>
+        <v>-0.3925</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2273</v>
+        <v>-1.199</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3248</v>
+        <v>-1.3021</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.3248</v>
+        <v>-1.3021</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.3248</v>
+        <v>-1.3021</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.3248</v>
+        <v>-1.3021</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.3248</v>
+        <v>-1.3021</v>
       </c>
       <c r="N39" t="n">
         <v>67</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.541</v>
+        <v>-1.4809</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4645</v>
+        <v>-0.4464</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3257</v>
+        <v>-1.2804</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.541</v>
+        <v>-1.4809</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.541</v>
+        <v>-1.4809</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.541</v>
+        <v>-1.4809</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.541</v>
+        <v>-1.4809</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.541</v>
+        <v>-1.4809</v>
       </c>
       <c r="N40" t="n">
         <v>81</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8509</v>
+        <v>-1.9063</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5747</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4668</v>
+        <v>-1.4742</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8509</v>
+        <v>-1.9063</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.8509</v>
+        <v>-1.9063</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.8509</v>
+        <v>-1.9063</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.8509</v>
+        <v>-1.9063</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.8509</v>
+        <v>-1.9063</v>
       </c>
       <c r="N41" t="n">
         <v>117</v>
@@ -2429,10 +2429,10 @@
         <v>1.47</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0786</v>
+        <v>1.079</v>
       </c>
       <c r="J2" t="n">
-        <v>30.2008</v>
+        <v>30.212</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.24</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6271</v>
+        <v>0.5957</v>
       </c>
       <c r="J3" t="n">
-        <v>17.5588</v>
+        <v>16.6796</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.14</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4072</v>
+        <v>0.3734</v>
       </c>
       <c r="J4" t="n">
-        <v>11.4016</v>
+        <v>10.4552</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.14</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4072</v>
+        <v>0.3734</v>
       </c>
       <c r="J5" t="n">
-        <v>11.4016</v>
+        <v>10.4552</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3073</v>
+        <v>0.275</v>
       </c>
       <c r="J6" t="n">
-        <v>8.6044</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.15</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3721</v>
+        <v>0.3186</v>
       </c>
       <c r="J7" t="n">
-        <v>10.4188</v>
+        <v>8.9208</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.9</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1393</v>
+        <v>-0.1218</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.9004</v>
+        <v>-3.4104</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.87</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1714</v>
+        <v>-0.1525</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.7992</v>
+        <v>-4.27</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2329</v>
+        <v>-0.2131</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.5212</v>
+        <v>-5.9668</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.76</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2816</v>
+        <v>-0.2629</v>
       </c>
       <c r="J11" t="n">
-        <v>-7.8848</v>
+        <v>-7.3612</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.71</v>
       </c>
       <c r="I12" t="n">
-        <v>1.486</v>
+        <v>1.5199</v>
       </c>
       <c r="J12" t="n">
-        <v>34.178</v>
+        <v>34.9577</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.44</v>
       </c>
       <c r="I13" t="n">
-        <v>1.008</v>
+        <v>1.0027</v>
       </c>
       <c r="J13" t="n">
-        <v>23.184</v>
+        <v>23.0621</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.31</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7601</v>
+        <v>0.7373</v>
       </c>
       <c r="J14" t="n">
-        <v>17.4823</v>
+        <v>16.9579</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.98</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1485</v>
+        <v>-0.1224</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.4155</v>
+        <v>-2.8152</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.96</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.219</v>
+        <v>-0.186</v>
       </c>
       <c r="J16" t="n">
-        <v>-5.037</v>
+        <v>-4.278</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.46</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8783</v>
+        <v>0.8403</v>
       </c>
       <c r="J17" t="n">
-        <v>20.2009</v>
+        <v>19.3269</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.0785</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.1344</v>
+        <v>-1.8055</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.92</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1172</v>
+        <v>-0.1009</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.6956</v>
+        <v>-2.3207</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.7</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3388</v>
+        <v>-0.3229</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.7924</v>
+        <v>-7.4267</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.51</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.507</v>
+        <v>-0.5084</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.661</v>
+        <v>-11.6932</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.27</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4413</v>
+        <v>0.4445</v>
       </c>
       <c r="J22" t="n">
-        <v>12.7977</v>
+        <v>12.8905</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.18</v>
       </c>
       <c r="I23" t="n">
-        <v>0.322</v>
+        <v>0.3119</v>
       </c>
       <c r="J23" t="n">
-        <v>9.337999999999999</v>
+        <v>9.0451</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.87</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1759</v>
+        <v>-0.1559</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.1011</v>
+        <v>-4.5211</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.75</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2965</v>
+        <v>-0.2782</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.5985</v>
+        <v>-8.0678</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3525</v>
+        <v>-0.3377</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.2225</v>
+        <v>-9.7933</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.59</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7372</v>
+        <v>0.6679</v>
       </c>
       <c r="J27" t="n">
-        <v>21.3788</v>
+        <v>19.3691</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.26</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3802</v>
+        <v>0.3183</v>
       </c>
       <c r="J28" t="n">
-        <v>11.0258</v>
+        <v>9.230700000000001</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.01</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0245</v>
+        <v>0.0161</v>
       </c>
       <c r="J29" t="n">
-        <v>0.7105</v>
+        <v>0.4669</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.99</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0321</v>
+        <v>-0.0231</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.6699000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.63</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4183</v>
+        <v>-0.4111</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.1307</v>
+        <v>-11.9219</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.6</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2998</v>
+        <v>1.3278</v>
       </c>
       <c r="J32" t="n">
-        <v>35.0946</v>
+        <v>35.8506</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.6</v>
       </c>
       <c r="I33" t="n">
-        <v>1.2998</v>
+        <v>1.3278</v>
       </c>
       <c r="J33" t="n">
-        <v>35.0946</v>
+        <v>35.8506</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.25</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6423</v>
+        <v>0.6143</v>
       </c>
       <c r="J34" t="n">
-        <v>17.3421</v>
+        <v>16.5861</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.17</v>
       </c>
       <c r="I35" t="n">
-        <v>0.469</v>
+        <v>0.4371</v>
       </c>
       <c r="J35" t="n">
-        <v>12.663</v>
+        <v>11.8017</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.75</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7488</v>
+        <v>-0.7261</v>
       </c>
       <c r="J36" t="n">
-        <v>-20.2176</v>
+        <v>-19.6047</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.29</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6286</v>
+        <v>0.578</v>
       </c>
       <c r="J37" t="n">
-        <v>16.9722</v>
+        <v>15.606</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.99</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0126</v>
+        <v>-0.0083</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.3402</v>
+        <v>-0.2241</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.75</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2877</v>
+        <v>-0.2694</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.7679</v>
+        <v>-7.2738</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.7</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3345</v>
+        <v>-0.3183</v>
       </c>
       <c r="J40" t="n">
-        <v>-9.031499999999999</v>
+        <v>-8.594099999999999</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.59</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4336</v>
+        <v>-0.4256</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.7072</v>
+        <v>-11.4912</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.61</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0866</v>
+        <v>1.0772</v>
       </c>
       <c r="J42" t="n">
-        <v>31.5114</v>
+        <v>31.2388</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.44</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8591</v>
+        <v>0.8449</v>
       </c>
       <c r="J43" t="n">
-        <v>24.9139</v>
+        <v>24.5021</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.37</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7616000000000001</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>22.0864</v>
+        <v>21.7065</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.22</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.5376</v>
       </c>
       <c r="J45" t="n">
-        <v>15.7122</v>
+        <v>15.5904</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.78</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.6564</v>
       </c>
       <c r="J46" t="n">
-        <v>-19.836</v>
+        <v>-19.0356</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.34</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6252</v>
+        <v>0.5995</v>
       </c>
       <c r="J47" t="n">
-        <v>18.1308</v>
+        <v>17.3855</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.93</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1055</v>
+        <v>-0.09</v>
       </c>
       <c r="J48" t="n">
-        <v>-3.0595</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.9</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1398</v>
+        <v>-0.122</v>
       </c>
       <c r="J49" t="n">
-        <v>-4.0542</v>
+        <v>-3.538</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.74</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3019</v>
+        <v>-0.2839</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.755100000000001</v>
+        <v>-8.2331</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.64</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3938</v>
+        <v>-0.3821</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.4202</v>
+        <v>-11.0809</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.33</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5133</v>
+        <v>0.5475</v>
       </c>
       <c r="J52" t="n">
-        <v>13.8591</v>
+        <v>14.7825</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.84</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2007</v>
+        <v>-0.1815</v>
       </c>
       <c r="J53" t="n">
-        <v>-5.4189</v>
+        <v>-4.9005</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.8</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2406</v>
+        <v>-0.2213</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.4962</v>
+        <v>-5.9751</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.8</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2406</v>
+        <v>-0.2213</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.4962</v>
+        <v>-5.9751</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.61</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4171</v>
+        <v>-0.4075</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.2617</v>
+        <v>-11.0025</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.68</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7081</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>19.1187</v>
+        <v>17.8956</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.23</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3336</v>
+        <v>0.2777</v>
       </c>
       <c r="J58" t="n">
-        <v>9.007199999999999</v>
+        <v>7.4979</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.17</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2628</v>
+        <v>0.2146</v>
       </c>
       <c r="J59" t="n">
-        <v>7.0956</v>
+        <v>5.7942</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.12</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1978</v>
+        <v>0.1577</v>
       </c>
       <c r="J60" t="n">
-        <v>5.3406</v>
+        <v>4.2579</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.82</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2491</v>
+        <v>-0.2306</v>
       </c>
       <c r="J61" t="n">
-        <v>-6.7257</v>
+        <v>-6.2262</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.41</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8316</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="J62" t="n">
-        <v>20.79</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.36</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7598</v>
+        <v>0.7446</v>
       </c>
       <c r="J63" t="n">
-        <v>18.995</v>
+        <v>18.615</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.2</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5175</v>
+        <v>0.5078</v>
       </c>
       <c r="J64" t="n">
-        <v>12.9375</v>
+        <v>12.695</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.11</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3363</v>
+        <v>0.3029</v>
       </c>
       <c r="J65" t="n">
-        <v>8.407500000000001</v>
+        <v>7.5725</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.91</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3528</v>
+        <v>-0.312</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.82</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.11</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2967</v>
+        <v>0.2472</v>
       </c>
       <c r="J67" t="n">
-        <v>7.4175</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0917</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.2925</v>
+        <v>-1.9425</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.89</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1498</v>
+        <v>-0.132</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.745</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.77</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2716</v>
+        <v>-0.2526</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.79</v>
+        <v>-6.315</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.76</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2812</v>
+        <v>-0.2625</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.03</v>
+        <v>-6.5625</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>2.07</v>
       </c>
       <c r="I72" t="n">
-        <v>1.577</v>
+        <v>1.6012</v>
       </c>
       <c r="J72" t="n">
-        <v>26.809</v>
+        <v>27.2204</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.79</v>
       </c>
       <c r="I73" t="n">
-        <v>1.256</v>
+        <v>1.2593</v>
       </c>
       <c r="J73" t="n">
-        <v>21.352</v>
+        <v>21.4081</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.68</v>
       </c>
       <c r="I74" t="n">
-        <v>1.1262</v>
+        <v>1.1253</v>
       </c>
       <c r="J74" t="n">
-        <v>19.1454</v>
+        <v>19.1301</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.53</v>
       </c>
       <c r="I75" t="n">
-        <v>0.9442</v>
+        <v>0.9405</v>
       </c>
       <c r="J75" t="n">
-        <v>16.0514</v>
+        <v>15.9885</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.09</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2199</v>
+        <v>0.1831</v>
       </c>
       <c r="J76" t="n">
-        <v>3.7383</v>
+        <v>3.1127</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.89</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.0309</v>
+        <v>0.0344</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.5253</v>
+        <v>0.5848</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.59</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.3766</v>
+        <v>-0.3712</v>
       </c>
       <c r="J78" t="n">
-        <v>-6.4022</v>
+        <v>-6.3104</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.4059</v>
+        <v>-0.4031</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.9003</v>
+        <v>-6.8527</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.16</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.7681</v>
+        <v>-0.8117</v>
       </c>
       <c r="J80" t="n">
-        <v>-13.0577</v>
+        <v>-13.7989</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.15</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7775</v>
+        <v>-0.8235</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.2175</v>
+        <v>-13.9995</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.77</v>
       </c>
       <c r="I82" t="n">
-        <v>1.2852</v>
+        <v>1.287</v>
       </c>
       <c r="J82" t="n">
-        <v>29.5596</v>
+        <v>29.601</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.53</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9765</v>
+        <v>0.9639</v>
       </c>
       <c r="J83" t="n">
-        <v>22.4595</v>
+        <v>22.1697</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.21</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5231</v>
+        <v>0.5183</v>
       </c>
       <c r="J84" t="n">
-        <v>12.0313</v>
+        <v>11.9209</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.07</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2104</v>
+        <v>0.1812</v>
       </c>
       <c r="J85" t="n">
-        <v>4.8392</v>
+        <v>4.1676</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.97</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.19</v>
+        <v>-0.1605</v>
       </c>
       <c r="J86" t="n">
-        <v>-4.37</v>
+        <v>-3.6915</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.03</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1519</v>
+        <v>0.1228</v>
       </c>
       <c r="J87" t="n">
-        <v>3.4937</v>
+        <v>2.8244</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.99</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0013</v>
+        <v>0.0094</v>
       </c>
       <c r="J88" t="n">
-        <v>0.0299</v>
+        <v>0.2162</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.64</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3803</v>
+        <v>-0.3673</v>
       </c>
       <c r="J89" t="n">
-        <v>-8.7469</v>
+        <v>-8.447900000000001</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.64</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3803</v>
+        <v>-0.3673</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.7469</v>
+        <v>-8.447900000000001</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.62</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3982</v>
+        <v>-0.3866</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.1586</v>
+        <v>-8.8918</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.84</v>
       </c>
       <c r="I92" t="n">
-        <v>1.5085</v>
+        <v>1.541</v>
       </c>
       <c r="J92" t="n">
-        <v>39.221</v>
+        <v>40.066</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.59</v>
       </c>
       <c r="I93" t="n">
-        <v>1.1947</v>
+        <v>1.2102</v>
       </c>
       <c r="J93" t="n">
-        <v>31.0622</v>
+        <v>31.4652</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.3</v>
       </c>
       <c r="I94" t="n">
-        <v>0.7331</v>
+        <v>0.7127</v>
       </c>
       <c r="J94" t="n">
-        <v>19.0606</v>
+        <v>18.5302</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.17</v>
       </c>
       <c r="I95" t="n">
-        <v>0.4564</v>
+        <v>0.4257</v>
       </c>
       <c r="J95" t="n">
-        <v>11.8664</v>
+        <v>11.0682</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.88</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4573</v>
+        <v>-0.4212</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.8898</v>
+        <v>-10.9512</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.02</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1436</v>
+        <v>0.1217</v>
       </c>
       <c r="J97" t="n">
-        <v>3.7336</v>
+        <v>3.1642</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.9</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1182</v>
+        <v>-0.103</v>
       </c>
       <c r="J98" t="n">
-        <v>-3.0732</v>
+        <v>-2.678</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.84</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1862</v>
+        <v>-0.1706</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.8412</v>
+        <v>-4.4356</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.5</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4982</v>
+        <v>-0.4965</v>
       </c>
       <c r="J100" t="n">
-        <v>-12.9532</v>
+        <v>-12.909</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.41</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5760999999999999</v>
+        <v>-0.5855</v>
       </c>
       <c r="J101" t="n">
-        <v>-14.9786</v>
+        <v>-15.223</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>0.58</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.3805</v>
+        <v>-0.3753</v>
       </c>
       <c r="J102" t="n">
-        <v>-7.2295</v>
+        <v>-7.1307</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.53</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.4295</v>
+        <v>-0.4288</v>
       </c>
       <c r="J103" t="n">
-        <v>-8.160500000000001</v>
+        <v>-8.1472</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.44</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.5084</v>
+        <v>-0.5112</v>
       </c>
       <c r="J104" t="n">
-        <v>-9.659599999999999</v>
+        <v>-9.7128</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.44</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5084</v>
+        <v>-0.5112</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.659599999999999</v>
+        <v>-9.7128</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.27</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.662</v>
+        <v>-0.6819</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.578</v>
+        <v>-12.9561</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.96</v>
       </c>
       <c r="I107" t="n">
-        <v>1.601</v>
+        <v>1.6409</v>
       </c>
       <c r="J107" t="n">
-        <v>30.419</v>
+        <v>31.1771</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.81</v>
       </c>
       <c r="I108" t="n">
-        <v>1.4276</v>
+        <v>1.4573</v>
       </c>
       <c r="J108" t="n">
-        <v>27.1244</v>
+        <v>27.6887</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.59</v>
       </c>
       <c r="I109" t="n">
-        <v>1.167</v>
+        <v>1.1894</v>
       </c>
       <c r="J109" t="n">
-        <v>22.173</v>
+        <v>22.5986</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.41</v>
       </c>
       <c r="I110" t="n">
-        <v>0.9087</v>
+        <v>0.9089</v>
       </c>
       <c r="J110" t="n">
-        <v>17.2653</v>
+        <v>17.2691</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.35</v>
       </c>
       <c r="I111" t="n">
-        <v>0.7953</v>
+        <v>0.7855</v>
       </c>
       <c r="J111" t="n">
-        <v>15.1107</v>
+        <v>14.9245</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.49</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0659</v>
+        <v>1.0758</v>
       </c>
       <c r="J112" t="n">
-        <v>23.4498</v>
+        <v>23.6676</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.41</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9409</v>
+        <v>0.9334</v>
       </c>
       <c r="J113" t="n">
-        <v>20.6998</v>
+        <v>20.5348</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.35</v>
       </c>
       <c r="I114" t="n">
-        <v>0.8303</v>
+        <v>0.8143</v>
       </c>
       <c r="J114" t="n">
-        <v>18.2666</v>
+        <v>17.9146</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.23</v>
       </c>
       <c r="I115" t="n">
-        <v>0.592</v>
+        <v>0.5648</v>
       </c>
       <c r="J115" t="n">
-        <v>13.024</v>
+        <v>12.4256</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.21</v>
       </c>
       <c r="I116" t="n">
-        <v>0.5488</v>
+        <v>0.5203</v>
       </c>
       <c r="J116" t="n">
-        <v>12.0736</v>
+        <v>11.4466</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.07</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2648</v>
+        <v>0.228</v>
       </c>
       <c r="J117" t="n">
-        <v>5.8256</v>
+        <v>5.016</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.97</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0268</v>
+        <v>-0.0162</v>
       </c>
       <c r="J118" t="n">
-        <v>-0.5896</v>
+        <v>-0.3564</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.71</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3128</v>
+        <v>-0.2973</v>
       </c>
       <c r="J119" t="n">
-        <v>-6.8816</v>
+        <v>-6.5406</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.55</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4561</v>
+        <v>-0.4497</v>
       </c>
       <c r="J120" t="n">
-        <v>-10.0342</v>
+        <v>-9.8934</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.44</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5518</v>
+        <v>-0.5576</v>
       </c>
       <c r="J121" t="n">
-        <v>-12.1396</v>
+        <v>-12.2672</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.41</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7508</v>
+        <v>0.6949</v>
       </c>
       <c r="J122" t="n">
-        <v>21.7732</v>
+        <v>20.1521</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.18</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3891</v>
+        <v>0.3336</v>
       </c>
       <c r="J123" t="n">
-        <v>11.2839</v>
+        <v>9.6744</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.07</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1849</v>
+        <v>0.1472</v>
       </c>
       <c r="J124" t="n">
-        <v>5.3621</v>
+        <v>4.2688</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.04</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1198</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="J125" t="n">
-        <v>3.4742</v>
+        <v>2.6622</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.55</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4842</v>
+        <v>-0.4844</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.0418</v>
+        <v>-14.0476</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.55</v>
       </c>
       <c r="I127" t="n">
-        <v>1.1869</v>
+        <v>1.2025</v>
       </c>
       <c r="J127" t="n">
-        <v>34.4201</v>
+        <v>34.8725</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.36</v>
       </c>
       <c r="I128" t="n">
-        <v>0.8869</v>
+        <v>0.8677</v>
       </c>
       <c r="J128" t="n">
-        <v>25.7201</v>
+        <v>25.1633</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.2</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5528</v>
+        <v>0.5157</v>
       </c>
       <c r="J129" t="n">
-        <v>16.0312</v>
+        <v>14.9553</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.03</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1143</v>
+        <v>0.0931</v>
       </c>
       <c r="J130" t="n">
-        <v>3.3147</v>
+        <v>2.6999</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.57</v>
       </c>
       <c r="I131" t="n">
-        <v>-1.1014</v>
+        <v>-1.1155</v>
       </c>
       <c r="J131" t="n">
-        <v>-31.9406</v>
+        <v>-32.3495</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.45</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0641</v>
+        <v>1.0731</v>
       </c>
       <c r="J132" t="n">
-        <v>29.7948</v>
+        <v>30.0468</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.12</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3775</v>
+        <v>0.3375</v>
       </c>
       <c r="J133" t="n">
-        <v>10.57</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.06</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2195</v>
+        <v>0.1871</v>
       </c>
       <c r="J134" t="n">
-        <v>6.146</v>
+        <v>5.2388</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2195</v>
+        <v>0.1871</v>
       </c>
       <c r="J135" t="n">
-        <v>6.146</v>
+        <v>5.2388</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.8452</v>
+        <v>-0.8258</v>
       </c>
       <c r="J136" t="n">
-        <v>-23.6656</v>
+        <v>-23.1224</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.14</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3364</v>
+        <v>0.2833</v>
       </c>
       <c r="J137" t="n">
-        <v>9.4192</v>
+        <v>7.9324</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1</v>
       </c>
       <c r="I138" t="n">
-        <v>0.0041</v>
+        <v>0.0021</v>
       </c>
       <c r="J138" t="n">
-        <v>0.1148</v>
+        <v>0.0588</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.99</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0232</v>
+        <v>-0.0171</v>
       </c>
       <c r="J139" t="n">
-        <v>-0.6496</v>
+        <v>-0.4788</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.0803</v>
       </c>
       <c r="J140" t="n">
-        <v>-2.6936</v>
+        <v>-2.2484</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.74</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3069</v>
+        <v>-0.2892</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.5932</v>
+        <v>-8.0976</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.09</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2367</v>
+        <v>0.1914</v>
       </c>
       <c r="J142" t="n">
-        <v>8.2845</v>
+        <v>6.699</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0762</v>
+        <v>0.0541</v>
       </c>
       <c r="J143" t="n">
-        <v>2.667</v>
+        <v>1.8935</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1</v>
       </c>
       <c r="I144" t="n">
-        <v>0.002</v>
+        <v>0.0009</v>
       </c>
       <c r="J144" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0315</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.99</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0243</v>
+        <v>-0.0177</v>
       </c>
       <c r="J145" t="n">
-        <v>-0.8505</v>
+        <v>-0.6195000000000001</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.79</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2603</v>
+        <v>-0.2406</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.1105</v>
+        <v>-8.420999999999999</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.4</v>
       </c>
       <c r="I147" t="n">
-        <v>0.9656</v>
+        <v>0.9563</v>
       </c>
       <c r="J147" t="n">
-        <v>33.796</v>
+        <v>33.4705</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.22</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5981</v>
+        <v>0.5617</v>
       </c>
       <c r="J148" t="n">
-        <v>20.9335</v>
+        <v>19.6595</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.18</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5095</v>
+        <v>0.4715</v>
       </c>
       <c r="J149" t="n">
-        <v>17.8325</v>
+        <v>16.5025</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.03</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1157</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="J150" t="n">
-        <v>4.0495</v>
+        <v>3.3005</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.84</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.4794</v>
       </c>
       <c r="J151" t="n">
-        <v>-18.1895</v>
+        <v>-16.779</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>2.08</v>
       </c>
       <c r="I152" t="n">
-        <v>1.7522</v>
+        <v>1.8046</v>
       </c>
       <c r="J152" t="n">
-        <v>35.044</v>
+        <v>36.092</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.62</v>
       </c>
       <c r="I153" t="n">
-        <v>1.2089</v>
+        <v>1.2292</v>
       </c>
       <c r="J153" t="n">
-        <v>24.178</v>
+        <v>24.584</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.46</v>
       </c>
       <c r="I154" t="n">
-        <v>1.003</v>
+        <v>1.013</v>
       </c>
       <c r="J154" t="n">
-        <v>20.06</v>
+        <v>20.26</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.29</v>
       </c>
       <c r="I155" t="n">
-        <v>0.6879</v>
+        <v>0.6693</v>
       </c>
       <c r="J155" t="n">
-        <v>13.758</v>
+        <v>13.386</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.25</v>
       </c>
       <c r="I156" t="n">
-        <v>0.6054</v>
+        <v>0.5816</v>
       </c>
       <c r="J156" t="n">
-        <v>12.108</v>
+        <v>11.632</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>0.87</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.0959</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="J157" t="n">
-        <v>-1.918</v>
+        <v>-1.314</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.57</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.4122</v>
+        <v>-0.4076</v>
       </c>
       <c r="J158" t="n">
-        <v>-8.244</v>
+        <v>-8.151999999999999</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.48</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.4882</v>
+        <v>-0.4864</v>
       </c>
       <c r="J159" t="n">
-        <v>-9.763999999999999</v>
+        <v>-9.728</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.45</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.5148</v>
       </c>
       <c r="J160" t="n">
-        <v>-10.292</v>
+        <v>-10.296</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.33</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.6217</v>
+        <v>-0.6358</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.434</v>
+        <v>-12.716</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.04</v>
       </c>
       <c r="I162" t="n">
-        <v>0.1901</v>
+        <v>0.1592</v>
       </c>
       <c r="J162" t="n">
-        <v>3.9921</v>
+        <v>3.3432</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.82</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.2101</v>
+        <v>-0.1942</v>
       </c>
       <c r="J163" t="n">
-        <v>-4.4121</v>
+        <v>-4.0782</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.67</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.3497</v>
+        <v>-0.3353</v>
       </c>
       <c r="J164" t="n">
-        <v>-7.3437</v>
+        <v>-7.0413</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.64</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3768</v>
+        <v>-0.3638</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.9128</v>
+        <v>-7.6398</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.6</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4125</v>
+        <v>-0.4021</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.6625</v>
+        <v>-8.444100000000001</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.99</v>
       </c>
       <c r="I167" t="n">
-        <v>1.6809</v>
+        <v>1.7283</v>
       </c>
       <c r="J167" t="n">
-        <v>35.2989</v>
+        <v>36.2943</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.37</v>
       </c>
       <c r="I168" t="n">
-        <v>0.8631</v>
+        <v>0.8518</v>
       </c>
       <c r="J168" t="n">
-        <v>18.1251</v>
+        <v>17.8878</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.35</v>
       </c>
       <c r="I169" t="n">
-        <v>0.8257</v>
+        <v>0.8121</v>
       </c>
       <c r="J169" t="n">
-        <v>17.3397</v>
+        <v>17.0541</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.34</v>
       </c>
       <c r="I170" t="n">
-        <v>0.8067</v>
+        <v>0.7919</v>
       </c>
       <c r="J170" t="n">
-        <v>16.9407</v>
+        <v>16.6299</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.9</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4102</v>
+        <v>-0.3748</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.6142</v>
+        <v>-7.8708</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.06</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2696</v>
+        <v>0.2413</v>
       </c>
       <c r="J172" t="n">
-        <v>6.2008</v>
+        <v>5.5499</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.71</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.3081</v>
+        <v>-0.2947</v>
       </c>
       <c r="J173" t="n">
-        <v>-7.0863</v>
+        <v>-6.7781</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.7</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.317</v>
+        <v>-0.3036</v>
       </c>
       <c r="J174" t="n">
-        <v>-7.291</v>
+        <v>-6.9828</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.53</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4666</v>
+        <v>-0.4612</v>
       </c>
       <c r="J175" t="n">
-        <v>-10.7318</v>
+        <v>-10.6076</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.46</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.528</v>
+        <v>-0.5296999999999999</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.144</v>
+        <v>-12.1831</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.92</v>
       </c>
       <c r="I177" t="n">
-        <v>1.5896</v>
+        <v>1.628</v>
       </c>
       <c r="J177" t="n">
-        <v>36.5608</v>
+        <v>37.444</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.36</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8404</v>
+        <v>0.8293</v>
       </c>
       <c r="J178" t="n">
-        <v>19.3292</v>
+        <v>19.0739</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.35</v>
       </c>
       <c r="I179" t="n">
-        <v>0.8214</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="J179" t="n">
-        <v>18.8922</v>
+        <v>18.607</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.26</v>
       </c>
       <c r="I180" t="n">
-        <v>0.6424</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="J180" t="n">
-        <v>14.7752</v>
+        <v>14.2485</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.24</v>
       </c>
       <c r="I181" t="n">
-        <v>0.6004</v>
+        <v>0.5755</v>
       </c>
       <c r="J181" t="n">
-        <v>13.8092</v>
+        <v>13.2365</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>2.03</v>
       </c>
       <c r="I182" t="n">
-        <v>1.7484</v>
+        <v>1.8057</v>
       </c>
       <c r="J182" t="n">
-        <v>36.7164</v>
+        <v>37.9197</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.55</v>
       </c>
       <c r="I183" t="n">
-        <v>1.1492</v>
+        <v>1.1629</v>
       </c>
       <c r="J183" t="n">
-        <v>24.1332</v>
+        <v>24.4209</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.27</v>
       </c>
       <c r="I184" t="n">
-        <v>0.6781</v>
+        <v>0.6534</v>
       </c>
       <c r="J184" t="n">
-        <v>14.2401</v>
+        <v>13.7214</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.21</v>
       </c>
       <c r="I185" t="n">
-        <v>0.5521</v>
+        <v>0.523</v>
       </c>
       <c r="J185" t="n">
-        <v>11.5941</v>
+        <v>10.983</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.52</v>
       </c>
       <c r="I186" t="n">
-        <v>-1.2203</v>
+        <v>-1.2577</v>
       </c>
       <c r="J186" t="n">
-        <v>-25.6263</v>
+        <v>-26.4117</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.98</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.0203</v>
+        <v>-0.0128</v>
       </c>
       <c r="J187" t="n">
-        <v>-0.4263</v>
+        <v>-0.2688</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.82</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.215</v>
+        <v>-0.1979</v>
       </c>
       <c r="J188" t="n">
-        <v>-4.515</v>
+        <v>-4.1559</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.77</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2622</v>
+        <v>-0.2447</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.5062</v>
+        <v>-5.1387</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.76</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2716</v>
+        <v>-0.2541</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.7036</v>
+        <v>-5.3361</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.66</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3638</v>
+        <v>-0.3497</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.6398</v>
+        <v>-7.3437</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.32</v>
       </c>
       <c r="I192" t="n">
-        <v>0.8069</v>
+        <v>0.7813</v>
       </c>
       <c r="J192" t="n">
-        <v>24.207</v>
+        <v>23.439</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.25</v>
       </c>
       <c r="I193" t="n">
-        <v>0.6614</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="J193" t="n">
-        <v>19.842</v>
+        <v>18.825</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.1</v>
       </c>
       <c r="I194" t="n">
-        <v>0.3195</v>
+        <v>0.2846</v>
       </c>
       <c r="J194" t="n">
-        <v>9.585000000000001</v>
+        <v>8.538</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.03</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1146</v>
+        <v>0.0934</v>
       </c>
       <c r="J195" t="n">
-        <v>3.438</v>
+        <v>2.802</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.0229</v>
+        <v>-0.0176</v>
       </c>
       <c r="J196" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.528</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.16</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3729</v>
+        <v>0.3179</v>
       </c>
       <c r="J197" t="n">
-        <v>11.187</v>
+        <v>9.537000000000001</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.16</v>
       </c>
       <c r="I198" t="n">
-        <v>0.3729</v>
+        <v>0.3179</v>
       </c>
       <c r="J198" t="n">
-        <v>11.187</v>
+        <v>9.537000000000001</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.02</v>
       </c>
       <c r="I199" t="n">
-        <v>0.0786</v>
+        <v>0.0558</v>
       </c>
       <c r="J199" t="n">
-        <v>2.358</v>
+        <v>1.674</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.95</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.0834</v>
+        <v>-0.0687</v>
       </c>
       <c r="J200" t="n">
-        <v>-2.502</v>
+        <v>-2.061</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.52</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5031</v>
+        <v>-0.5047</v>
       </c>
       <c r="J201" t="n">
-        <v>-15.093</v>
+        <v>-15.141</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.99</v>
       </c>
       <c r="I202" t="n">
-        <v>0.0098</v>
+        <v>0.0186</v>
       </c>
       <c r="J202" t="n">
-        <v>0.2352</v>
+        <v>0.4464</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.89</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.1348</v>
+        <v>-0.1196</v>
       </c>
       <c r="J203" t="n">
-        <v>-3.2352</v>
+        <v>-2.8704</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.72</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3049</v>
+        <v>-0.2889</v>
       </c>
       <c r="J204" t="n">
-        <v>-7.3176</v>
+        <v>-6.9336</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.64</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3775</v>
+        <v>-0.3645</v>
       </c>
       <c r="J205" t="n">
-        <v>-9.06</v>
+        <v>-8.747999999999999</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4487</v>
+        <v>-0.4416</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.7688</v>
+        <v>-10.5984</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.53</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1181</v>
+        <v>1.1316</v>
       </c>
       <c r="J207" t="n">
-        <v>26.8344</v>
+        <v>27.1584</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.51</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0917</v>
+        <v>1.1041</v>
       </c>
       <c r="J208" t="n">
-        <v>26.2008</v>
+        <v>26.4984</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.46</v>
       </c>
       <c r="I209" t="n">
-        <v>1.0217</v>
+        <v>1.026</v>
       </c>
       <c r="J209" t="n">
-        <v>24.5208</v>
+        <v>24.624</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.26</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6292</v>
       </c>
       <c r="J210" t="n">
-        <v>15.6888</v>
+        <v>15.1008</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.97</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.1957</v>
+        <v>-0.167</v>
       </c>
       <c r="J211" t="n">
-        <v>-4.6968</v>
+        <v>-4.008</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.87</v>
       </c>
       <c r="I212" t="n">
-        <v>1.5196</v>
+        <v>1.5525</v>
       </c>
       <c r="J212" t="n">
-        <v>30.392</v>
+        <v>31.05</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.64</v>
       </c>
       <c r="I213" t="n">
-        <v>1.2403</v>
+        <v>1.2595</v>
       </c>
       <c r="J213" t="n">
-        <v>24.806</v>
+        <v>25.19</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.55</v>
       </c>
       <c r="I214" t="n">
-        <v>1.1274</v>
+        <v>1.1447</v>
       </c>
       <c r="J214" t="n">
-        <v>22.548</v>
+        <v>22.894</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.24</v>
       </c>
       <c r="I215" t="n">
-        <v>0.5927</v>
+        <v>0.5679</v>
       </c>
       <c r="J215" t="n">
-        <v>11.854</v>
+        <v>11.358</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.1</v>
       </c>
       <c r="I216" t="n">
-        <v>0.2665</v>
+        <v>0.2332</v>
       </c>
       <c r="J216" t="n">
-        <v>5.33</v>
+        <v>4.664</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.83</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.1734</v>
+        <v>-0.1558</v>
       </c>
       <c r="J217" t="n">
-        <v>-3.468</v>
+        <v>-3.116</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.75</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.2586</v>
+        <v>-0.2452</v>
       </c>
       <c r="J218" t="n">
-        <v>-5.172</v>
+        <v>-4.904</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.71</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2982</v>
+        <v>-0.2865</v>
       </c>
       <c r="J219" t="n">
-        <v>-5.964</v>
+        <v>-5.73</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.5</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4836</v>
+        <v>-0.4801</v>
       </c>
       <c r="J220" t="n">
-        <v>-9.672000000000001</v>
+        <v>-9.602</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.33</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.633</v>
+        <v>-0.6504</v>
       </c>
       <c r="J221" t="n">
-        <v>-12.66</v>
+        <v>-13.008</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.61</v>
       </c>
       <c r="I222" t="n">
-        <v>1.2169</v>
+        <v>1.2333</v>
       </c>
       <c r="J222" t="n">
-        <v>25.5549</v>
+        <v>25.8993</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.48</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0465</v>
+        <v>1.0555</v>
       </c>
       <c r="J223" t="n">
-        <v>21.9765</v>
+        <v>22.1655</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.43</v>
       </c>
       <c r="I224" t="n">
-        <v>0.97</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="J224" t="n">
-        <v>20.37</v>
+        <v>20.3322</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.37</v>
       </c>
       <c r="I225" t="n">
-        <v>0.8642</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="J225" t="n">
-        <v>18.1482</v>
+        <v>17.8983</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.0598</v>
       </c>
       <c r="J226" t="n">
-        <v>-1.3167</v>
+        <v>-1.2558</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.89</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.1184</v>
+        <v>-0.1015</v>
       </c>
       <c r="J227" t="n">
-        <v>-2.4864</v>
+        <v>-2.1315</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.76</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.2593</v>
+        <v>-0.2454</v>
       </c>
       <c r="J228" t="n">
-        <v>-5.4453</v>
+        <v>-5.1534</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.67</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3417</v>
+        <v>-0.3292</v>
       </c>
       <c r="J229" t="n">
-        <v>-7.1757</v>
+        <v>-6.9132</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.57</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4298</v>
+        <v>-0.4212</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.0258</v>
+        <v>-8.8452</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.51</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4826</v>
+        <v>-0.4789</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.1346</v>
+        <v>-10.0569</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.76</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4075</v>
+        <v>1.4327</v>
       </c>
       <c r="J232" t="n">
-        <v>30.965</v>
+        <v>31.5194</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.37</v>
       </c>
       <c r="I233" t="n">
-        <v>0.8648</v>
+        <v>0.8525</v>
       </c>
       <c r="J233" t="n">
-        <v>19.0256</v>
+        <v>18.755</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.31</v>
       </c>
       <c r="I234" t="n">
-        <v>0.7513</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="J234" t="n">
-        <v>16.5286</v>
+        <v>16.1128</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.29</v>
       </c>
       <c r="I235" t="n">
-        <v>0.7116</v>
+        <v>0.6907</v>
       </c>
       <c r="J235" t="n">
-        <v>15.6552</v>
+        <v>15.1954</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.11</v>
       </c>
       <c r="I236" t="n">
-        <v>0.3091</v>
+        <v>0.2771</v>
       </c>
       <c r="J236" t="n">
-        <v>6.8002</v>
+        <v>6.0962</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.51</v>
       </c>
       <c r="I237" t="n">
-        <v>0.9986</v>
+        <v>0.9936</v>
       </c>
       <c r="J237" t="n">
-        <v>21.9692</v>
+        <v>21.8592</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.77</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.2637</v>
+        <v>-0.2457</v>
       </c>
       <c r="J238" t="n">
-        <v>-5.8014</v>
+        <v>-5.4054</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.7</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.3291</v>
+        <v>-0.3129</v>
       </c>
       <c r="J239" t="n">
-        <v>-7.2402</v>
+        <v>-6.8838</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.55</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4636</v>
+        <v>-0.4584</v>
       </c>
       <c r="J240" t="n">
-        <v>-10.1992</v>
+        <v>-10.0848</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.54</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4723</v>
+        <v>-0.4681</v>
       </c>
       <c r="J241" t="n">
-        <v>-10.3906</v>
+        <v>-10.2982</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.19</v>
       </c>
       <c r="I242" t="n">
-        <v>0.5548</v>
+        <v>0.5144</v>
       </c>
       <c r="J242" t="n">
-        <v>26.6304</v>
+        <v>24.6912</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.06</v>
       </c>
       <c r="I243" t="n">
-        <v>0.2246</v>
+        <v>0.1896</v>
       </c>
       <c r="J243" t="n">
-        <v>10.7808</v>
+        <v>9.1008</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.02</v>
       </c>
       <c r="I244" t="n">
-        <v>0.0959</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="J244" t="n">
-        <v>4.6032</v>
+        <v>3.5904</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.95</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2061</v>
+        <v>-0.1704</v>
       </c>
       <c r="J245" t="n">
-        <v>-9.892799999999999</v>
+        <v>-8.1792</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2364</v>
+        <v>-0.1986</v>
       </c>
       <c r="J246" t="n">
-        <v>-11.3472</v>
+        <v>-9.5328</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.22</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4597</v>
+        <v>0.4013</v>
       </c>
       <c r="J247" t="n">
-        <v>22.0656</v>
+        <v>19.2624</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.18</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3921</v>
+        <v>0.3363</v>
       </c>
       <c r="J248" t="n">
-        <v>18.8208</v>
+        <v>16.1424</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.06</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1656</v>
+        <v>0.13</v>
       </c>
       <c r="J249" t="n">
-        <v>7.9488</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.93</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1143</v>
+        <v>-0.0961</v>
       </c>
       <c r="J250" t="n">
-        <v>-5.4864</v>
+        <v>-4.6128</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.78</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2751</v>
+        <v>-0.2562</v>
       </c>
       <c r="J251" t="n">
-        <v>-13.2048</v>
+        <v>-12.2976</v>
       </c>
     </row>
   </sheetData>
